--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="78531" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="81754" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>
@@ -2639,6 +2639,1077 @@
   </si>
   <si>
     <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_203116_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\compression\COMPRESSION_20260406_90517_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\compression\COMPRESSION_20260406_90517_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\fracture\Fracture_20260406_91742_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\fracture\Fracture_20260406_91742_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\fracture\Fracture_20260406_91742_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\fracture\Fracture_20260406_91742_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\fracture\Fracture_20260406_91742_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\fracture\Fracture_20260406_91742_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\fracture\Fracture_20260406_91742_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\fracture\Fracture_20260406_91742_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\compression\COMPRESSION_20260406_170533_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\compression\COMPRESSION_20260406_153036_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\tension\TENSION_20260406_164703_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\tension\TENSION_20260406_163348_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\fracture\Fracture_20260406_171519_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\fracture\Fracture_20260406_171519_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\fracture\Fracture_20260406_171519_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\fracture\Fracture_20260406_171519_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\fracture\Fracture_20260406_175021_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\fracture\Fracture_20260406_171519_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\fracture\Fracture_20260406_171519_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\fracture\Fracture_20260406_171519_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\compression\COMPRESSION_20260407_174032_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\compression\COMPRESSION_20260407_173344_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\tension\TENSION_20260407_181007_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\tension\TENSION_20260407_175922_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\fracture\Fracture_20260407_182625_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\fracture\Fracture_20260407_182625_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\fracture\Fracture_20260407_182625_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\fracture\Fracture_20260407_182625_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\fracture\Fracture_20260407_182625_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\fracture\Fracture_20260407_182625_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\fracture\Fracture_20260407_182625_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\fracture\Fracture_20260407_182625_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\compression\COMPRESSION_20260407_144614_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\tension\TENSION_20260407_150234_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\fracture\Fracture_20260407_152303_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\fracture\Fracture_20260407_152303_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\fracture\Fracture_20260407_152303_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\fracture\Fracture_20260407_152303_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\fracture\Fracture_20260407_152303_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\fracture\Fracture_20260407_152303_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\fracture\Fracture_20260407_152303_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\fracture\Fracture_20260407_152303_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\compression\COMPRESSION_20260408_164418_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\compression\COMPRESSION_20260408_164418_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\fracture\Fracture_20260408_173538_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\fracture\Fracture_20260408_173538_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\fracture\Fracture_20260408_173538_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\fracture\Fracture_20260408_173538_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\fracture\Fracture_20260408_173538_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\fracture\Fracture_20260408_173538_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\fracture\Fracture_20260408_173538_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\fracture\Fracture_20260408_173538_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\compression\COMPRESSION_20260408_134837_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\compression\COMPRESSION_20260408_134837_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\tension\TENSION_20260408_142846_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\tension\TENSION_20260408_142846_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\fracture\Fracture_20260408_150444_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\fracture\Fracture_20260408_150444_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\fracture\Fracture_20260408_150444_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\fracture\Fracture_20260408_150444_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\fracture\Fracture_20260408_150444_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\fracture\Fracture_20260408_150444_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\fracture\Fracture_20260408_150444_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\fracture\Fracture_20260408_150444_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\compression\COMPRESSION_20260408_195727_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\compression\COMPRESSION_20260408_193748_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\tension\TENSION_20260424_180221_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\tension\TENSION_20260424_180221_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_204135_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_204450_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_203511_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_205038_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_205315_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_204740_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_203829_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\fracture\Fracture_20260408_203116_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\compression\COMPRESSION_20260409_172654_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\compression\COMPRESSION_20260409_172037_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\tension\TENSION_20260409_174654_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\tension\TENSION_20260409_175433_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\fracture\Fracture_20260409_180250_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\fracture\Fracture_20260409_180250_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\fracture\Fracture_20260409_180250_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\fracture\Fracture_20260409_180250_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\fracture\Fracture_20260409_180250_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\fracture\Fracture_20260409_180250_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\fracture\Fracture_20260409_180250_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\fracture\Fracture_20260409_180250_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\compression\COMPRESSION_20260409_142206_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\compression\COMPRESSION_20260409_140753_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\fracture\Fracture_20260409_150439_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\fracture\Fracture_20260409_150730_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\fracture\Fracture_20260409_150146_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\fracture\Fracture_20260409_145151_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\fracture\Fracture_20260409_145459_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\fracture\Fracture_20260409_145811_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\fracture\Fracture_20260409_144947_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\fracture\Fracture_20260409_150948_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\compression\COMPRESSION_20260409_110850_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\tension\TENSION_20260409_113006_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\tension\TENSION_20260409_113006_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\fracture\Fracture_20260409_115743_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\fracture\Fracture_20260409_115743_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\fracture\Fracture_20260409_115743_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\fracture\Fracture_20260409_115743_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\fracture\Fracture_20260409_115743_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\fracture\Fracture_20260409_115743_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\fracture\Fracture_20260409_115743_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\fracture\Fracture_20260409_115743_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\compression\COMPRESSION_20260410_82205_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\compression\COMPRESSION_20260410_82205_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\tension\TENSION_20260410_85954_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\tension\TENSION_20260410_85954_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\fracture\Fracture_20260410_91307_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\fracture\Fracture_20260410_91307_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\fracture\Fracture_20260410_91307_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\fracture\Fracture_20260410_91307_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\fracture\Fracture_20260410_91307_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\fracture\Fracture_20260410_91307_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\fracture\Fracture_20260410_91307_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\compression\COMPRESSION_20260410_174614_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\tension\TENSION_20260410_182528_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\tension\TENSION_20260410_182528_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\fracture\Fracture_20260410_184209_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\fracture\Fracture_20260410_184209_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\fracture\Fracture_20260410_184209_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\fracture\Fracture_20260410_184209_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\fracture\Fracture_20260410_184209_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\fracture\Fracture_20260410_184209_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\fracture\Fracture_20260410_184209_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\fracture\Fracture_20260410_184209_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\compression\COMPRESSION_20260410_115513_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\compression\COMPRESSION_20260410_115513_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\tension\TENSION_20260410_113512_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\fracture\Fracture_20260410_120941_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\fracture\Fracture_20260410_120941_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\fracture\Fracture_20260410_120941_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\fracture\Fracture_20260410_120941_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\fracture\Fracture_20260410_120941_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\fracture\Fracture_20260410_120941_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\fracture\Fracture_20260410_120941_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\fracture\Fracture_20260410_120941_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\compression\COMPRESSION_20260410_161007_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\compression\COMPRESSION_20260410_161410_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\tension\TENSION_20260410_165112_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\tension\TENSION_20260410_165112_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\fracture\Fracture_20260410_162641_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\fracture\Fracture_20260410_162641_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\fracture\Fracture_20260410_162641_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\fracture\Fracture_20260410_162641_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\fracture\Fracture_20260410_162641_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\fracture\Fracture_20260410_162641_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\fracture\Fracture_20260410_162641_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\compression\COMPRESSION_20260420_183618_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\tension\TENSION_20260420_185903_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\tension\TENSION_20260420_185903_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\fracture\Fracture_20260420_191241_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\fracture\Fracture_20260420_191241_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\fracture\Fracture_20260420_191241_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\fracture\Fracture_20260420_191241_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\fracture\Fracture_20260420_191241_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\fracture\Fracture_20260420_191241_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\fracture\Fracture_20260420_191241_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\compression\COMPRESSION_20260420_81741_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\compression\COMPRESSION_20260420_81741_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\tension\TENSION_20260420_83635_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\tension\TENSION_20260420_83635_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\fracture\Fracture_20260420_85027_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\fracture\Fracture_20260420_85027_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\fracture\Fracture_20260420_85027_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\fracture\Fracture_20260420_85027_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\fracture\Fracture_20260420_85027_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\fracture\Fracture_20260420_85027_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\fracture\Fracture_20260420_85027_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\fracture\Fracture_20260420_85027_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\compression\COMPRESSION_20260420_165050_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\tension\TENSION_20260420_155824_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\tension\TENSION_20260420_155824_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\fracture\Fracture_20260420_170411_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\fracture\Fracture_20260420_170411_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\fracture\Fracture_20260420_170411_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\fracture\Fracture_20260420_170411_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\fracture\Fracture_20260420_170411_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\fracture\Fracture_20260420_170411_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\fracture\Fracture_20260420_170411_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\fracture\Fracture_20260420_170411_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\compression\COMPRESSION_20260421_171521_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\compression\COMPRESSION_20260421_170933_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\tension\TENSION_20260421_142756_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\tension\TENSION_20260421_142756_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\fracture\Fracture_20260421_174103_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\fracture\Fracture_20260421_174103_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\fracture\Fracture_20260421_174103_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\fracture\Fracture_20260421_174103_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\fracture\Fracture_20260421_174103_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\fracture\Fracture_20260421_174103_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\fracture\Fracture_20260421_174103_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\fracture\Fracture_20260421_174103_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\compression\COMPRESSION_20260421_141116_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\compression\COMPRESSION_20260421_141116_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\tension\TENSION_20260421_142756_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\fracture\Fracture_20260421_143605_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\fracture\Fracture_20260421_143605_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\fracture\Fracture_20260421_143605_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\fracture\Fracture_20260421_143605_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\fracture\Fracture_20260421_143605_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\fracture\Fracture_20260421_143605_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\fracture\Fracture_20260421_143605_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\fracture\Fracture_20260421_143605_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\compression\COMPRESSION_20260421_111311_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\compression\COMPRESSION_20260421_111311_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\tension\TENSION_20260421_113804_3.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\fracture\Fracture_20260421_115943_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\fracture\Fracture_20260421_115943_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\fracture\Fracture_20260421_115943_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\fracture\Fracture_20260421_115943_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\fracture\Fracture_20260421_115943_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\fracture\Fracture_20260421_115943_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\fracture\Fracture_20260421_115943_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\fracture\Fracture_20260421_115943_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\compression\COMPRESSION_20260421_90601_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\compression\COMPRESSION_20260421_90601_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\tension\TENSION_20260421_101138_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\fracture\Fracture_20260421_92707_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\fracture\Fracture_20260421_92707_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\fracture\Fracture_20260421_92707_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\fracture\Fracture_20260421_92707_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\fracture\Fracture_20260421_92707_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\fracture\Fracture_20260421_92707_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\fracture\Fracture_20260421_92707_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\compression\COMPRESSION_20260422_163210_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\compression\COMPRESSION_20260422_163210_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\tension\TENSION_20260422_164517_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\tension\TENSION_20260422_164517_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\compression\COMPRESSION_20260422_133560_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\compression\COMPRESSION_20260422_133560_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\tension\TENSION_20260422_135940_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\tension\TENSION_20260422_135940_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\compression\COMPRESSION_20260422_193341_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\compression\COMPRESSION_20260422_194554_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\tension\TENSION_20260422_195602_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\tension\TENSION_20260422_200525_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_202647_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_201627_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_202917_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_201454_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_201902_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_202534_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_202154_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_203122_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\compression\COMPRESSION_20260423_175437_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\compression\COMPRESSION_20260423_175134_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\tension\TENSION_20260423_182424_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\tension\TENSION_20260423_181633_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\fracture\Fracture_20260423_184148_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\fracture\Fracture_20260423_184148_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\fracture\Fracture_20260423_184148_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\fracture\Fracture_20260423_184148_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\fracture\Fracture_20260423_184148_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\fracture\Fracture_20260423_184148_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\fracture\Fracture_20260423_184148_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\fracture\Fracture_20260423_184148_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\compression\COMPRESSION_20260409_142206_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\compression\COMPRESSION_20260409_140753_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\fracture\Fracture_20260409_150439_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\fracture\Fracture_20260409_150730_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\fracture\Fracture_20260409_150146_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\fracture\Fracture_20260409_145151_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\fracture\Fracture_20260409_145459_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\fracture\Fracture_20260409_145811_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\fracture\Fracture_20260409_144947_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\fracture\Fracture_20260409_150948_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\compression\COMPRESSION_20260423_110609_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\compression\COMPRESSION_20260423_110609_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\tension\TENSION_20260423_111551_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\tension\TENSION_20260423_111551_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\fracture\Fracture_20260423_113204_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\fracture\Fracture_20260423_113204_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\fracture\Fracture_20260423_113204_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\fracture\Fracture_20260423_113204_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\fracture\Fracture_20260423_113204_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\fracture\Fracture_20260423_113204_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\fracture\Fracture_20260423_113204_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\fracture\Fracture_20260423_113204_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\compression\COMPRESSION_20260423_81011_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\compression\COMPRESSION_20260423_81011_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\tension\TENSION_20260423_82926_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\tension\TENSION_20260423_82926_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\fracture\Fracture_20260423_84622_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\fracture\Fracture_20260423_84622_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\fracture\Fracture_20260423_84622_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\fracture\Fracture_20260423_84622_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\fracture\Fracture_20260423_84622_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\fracture\Fracture_20260423_84622_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\fracture\Fracture_20260423_84622_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\fracture\Fracture_20260423_90355_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\compression\COMPRESSION_20260424_80730_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\compression\COMPRESSION_20260424_80730_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\tension\TENSION_20260424_83721_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\tension\TENSION_20260424_83721_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\fracture\Fracture_20260424_85221_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\fracture\Fracture_20260424_85221_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\fracture\Fracture_20260424_85221_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\fracture\Fracture_20260424_85221_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\fracture\Fracture_20260424_85221_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\fracture\Fracture_20260424_85221_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\fracture\Fracture_20260424_85221_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\compression\COMPRESSION_20260424_174058_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\compression\COMPRESSION_20260424_174058_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\tension\TENSION_20260424_180221_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\tension\TENSION_20260424_180221_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\fracture\Fracture_20260424_181359_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\fracture\Fracture_20260424_181359_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\fracture\Fracture_20260424_181359_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\fracture\Fracture_20260424_181359_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\fracture\Fracture_20260424_181359_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\fracture\Fracture_20260424_181359_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\fracture\Fracture_20260424_181359_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\fracture\Fracture_20260424_181359_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\compression\COMPRESSION_20260424_112945_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\compression\COMPRESSION_20260424_112945_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\fracture\Fracture_20260424_120102_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\fracture\Fracture_20260424_120102_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\fracture\Fracture_20260424_120102_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\fracture\Fracture_20260424_120102_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\fracture\Fracture_20260424_120102_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\fracture\Fracture_20260424_120102_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\fracture\Fracture_20260424_120102_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\fracture\Fracture_20260424_120102_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\compression\COMPRESSION_20260424_145207_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\compression\COMPRESSION_20260424_145207_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\tension\TENSION_20260424_154825_3.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\fracture\Fracture_20260424_151606_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\fracture\Fracture_20260424_151606_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\fracture\Fracture_20260424_151606_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\fracture\Fracture_20260424_151606_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\fracture\Fracture_20260424_151606_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\fracture\Fracture_20260424_151606_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\fracture\Fracture_20260424_151606_8_2.csv</t>
   </si>
 </sst>
 </file>
@@ -2687,16 +3758,16 @@
   <dimension ref="A1:J385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="16.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="167.54296875" customWidth="true"/>
-    <col min="10" max="10" width="9.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="17.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="147" customWidth="true"/>
+    <col min="10" max="10" width="9.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2757,7 +3828,7 @@
         <v>43</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>342</v>
+        <v>875</v>
       </c>
       <c r="J2" s="0">
         <v>5104.9130999999998</v>
@@ -2789,7 +3860,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>343</v>
+        <v>876</v>
       </c>
       <c r="J3" s="0">
         <v>3263.4158000000002</v>
@@ -2821,7 +3892,7 @@
         <v>47</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>346</v>
+        <v>877</v>
       </c>
       <c r="J4" s="0">
         <v>443.3879</v>
@@ -2853,7 +3924,7 @@
         <v>48</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>347</v>
+        <v>878</v>
       </c>
       <c r="J5" s="0">
         <v>410.7122</v>
@@ -2885,7 +3956,7 @@
         <v>49</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>348</v>
+        <v>879</v>
       </c>
       <c r="J6" s="0">
         <v>393.60379999999998</v>
@@ -2917,7 +3988,7 @@
         <v>50</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>349</v>
+        <v>880</v>
       </c>
       <c r="J7" s="0">
         <v>378.97039999999998</v>
@@ -2949,7 +4020,7 @@
         <v>51</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>350</v>
+        <v>881</v>
       </c>
       <c r="J8" s="0">
         <v>353.012</v>
@@ -2981,7 +4052,7 @@
         <v>52</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>351</v>
+        <v>882</v>
       </c>
       <c r="J9" s="0">
         <v>323.56819999999999</v>
@@ -3013,7 +4084,7 @@
         <v>53</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>352</v>
+        <v>883</v>
       </c>
       <c r="J10" s="0">
         <v>292.92790000000002</v>
@@ -3045,7 +4116,7 @@
         <v>54</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>353</v>
+        <v>884</v>
       </c>
       <c r="J11" s="0">
         <v>218.8537</v>
@@ -3077,7 +4148,7 @@
         <v>55</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>354</v>
+        <v>885</v>
       </c>
       <c r="J12" s="0">
         <v>5212.9053000000004</v>
@@ -3109,7 +4180,7 @@
         <v>56</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>355</v>
+        <v>886</v>
       </c>
       <c r="J13" s="0">
         <v>1797.9413</v>
@@ -3141,7 +4212,7 @@
         <v>57</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>356</v>
+        <v>887</v>
       </c>
       <c r="J14" s="0">
         <v>942.65679999999998</v>
@@ -3173,7 +4244,7 @@
         <v>58</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>357</v>
+        <v>888</v>
       </c>
       <c r="J15" s="0">
         <v>813.27890000000002</v>
@@ -3205,7 +4276,7 @@
         <v>59</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>358</v>
+        <v>889</v>
       </c>
       <c r="J16" s="0">
         <v>394.9126</v>
@@ -3237,7 +4308,7 @@
         <v>60</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>359</v>
+        <v>890</v>
       </c>
       <c r="J17" s="0">
         <v>393.85860000000002</v>
@@ -3269,7 +4340,7 @@
         <v>61</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>360</v>
+        <v>891</v>
       </c>
       <c r="J18" s="0">
         <v>391.5865</v>
@@ -3301,7 +4372,7 @@
         <v>62</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>361</v>
+        <v>892</v>
       </c>
       <c r="J19" s="0">
         <v>383.69600000000003</v>
@@ -3333,7 +4404,7 @@
         <v>63</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>362</v>
+        <v>893</v>
       </c>
       <c r="J20" s="0">
         <v>367.87400000000002</v>
@@ -3365,7 +4436,7 @@
         <v>64</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>363</v>
+        <v>894</v>
       </c>
       <c r="J21" s="0">
         <v>367.8381</v>
@@ -3397,7 +4468,7 @@
         <v>65</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>364</v>
+        <v>895</v>
       </c>
       <c r="J22" s="0">
         <v>290.31869999999998</v>
@@ -3429,7 +4500,7 @@
         <v>66</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>365</v>
+        <v>896</v>
       </c>
       <c r="J23" s="0">
         <v>253.11709999999999</v>
@@ -3461,7 +4532,7 @@
         <v>67</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>366</v>
+        <v>897</v>
       </c>
       <c r="J24" s="0">
         <v>4968.7178000000004</v>
@@ -3493,7 +4564,7 @@
         <v>68</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>367</v>
+        <v>898</v>
       </c>
       <c r="J25" s="0">
         <v>3314.2456000000002</v>
@@ -3525,7 +4596,7 @@
         <v>69</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>368</v>
+        <v>899</v>
       </c>
       <c r="J26" s="0">
         <v>720.75220000000002</v>
@@ -3557,7 +4628,7 @@
         <v>70</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>369</v>
+        <v>900</v>
       </c>
       <c r="J27" s="0">
         <v>584.66700000000003</v>
@@ -3589,7 +4660,7 @@
         <v>71</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>370</v>
+        <v>901</v>
       </c>
       <c r="J28" s="0">
         <v>414.71820000000002</v>
@@ -3621,7 +4692,7 @@
         <v>72</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>371</v>
+        <v>902</v>
       </c>
       <c r="J29" s="0">
         <v>406.6533</v>
@@ -3653,7 +4724,7 @@
         <v>73</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>372</v>
+        <v>903</v>
       </c>
       <c r="J30" s="0">
         <v>371.4246</v>
@@ -3685,7 +4756,7 @@
         <v>74</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>373</v>
+        <v>904</v>
       </c>
       <c r="J31" s="0">
         <v>347.6481</v>
@@ -3717,7 +4788,7 @@
         <v>75</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>374</v>
+        <v>905</v>
       </c>
       <c r="J32" s="0">
         <v>340.82400000000001</v>
@@ -3749,7 +4820,7 @@
         <v>76</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>375</v>
+        <v>906</v>
       </c>
       <c r="J33" s="0">
         <v>308.06799999999998</v>
@@ -3781,7 +4852,7 @@
         <v>77</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>376</v>
+        <v>907</v>
       </c>
       <c r="J34" s="0">
         <v>252.10589999999999</v>
@@ -3813,7 +4884,7 @@
         <v>78</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>377</v>
+        <v>908</v>
       </c>
       <c r="J35" s="0">
         <v>213.29320000000001</v>
@@ -3845,7 +4916,7 @@
         <v>80</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>379</v>
+        <v>909</v>
       </c>
       <c r="J36" s="0">
         <v>2818.2202000000002</v>
@@ -3877,7 +4948,7 @@
         <v>81</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>380</v>
+        <v>910</v>
       </c>
       <c r="J37" s="0">
         <v>578.16610000000003</v>
@@ -3909,7 +4980,7 @@
         <v>83</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>382</v>
+        <v>911</v>
       </c>
       <c r="J38" s="0">
         <v>448.01760000000002</v>
@@ -3941,7 +5012,7 @@
         <v>84</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>383</v>
+        <v>912</v>
       </c>
       <c r="J39" s="0">
         <v>429.6198</v>
@@ -3973,7 +5044,7 @@
         <v>85</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>384</v>
+        <v>913</v>
       </c>
       <c r="J40" s="0">
         <v>406.0299</v>
@@ -4005,7 +5076,7 @@
         <v>86</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>385</v>
+        <v>914</v>
       </c>
       <c r="J41" s="0">
         <v>405.92529999999999</v>
@@ -4037,7 +5108,7 @@
         <v>87</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>386</v>
+        <v>915</v>
       </c>
       <c r="J42" s="0">
         <v>403.39850000000001</v>
@@ -4069,7 +5140,7 @@
         <v>88</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>387</v>
+        <v>916</v>
       </c>
       <c r="J43" s="0">
         <v>381.14350000000002</v>
@@ -4101,7 +5172,7 @@
         <v>89</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>388</v>
+        <v>917</v>
       </c>
       <c r="J44" s="0">
         <v>254.68129999999999</v>
@@ -4133,7 +5204,7 @@
         <v>90</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>389</v>
+        <v>918</v>
       </c>
       <c r="J45" s="0">
         <v>166.26730000000001</v>
@@ -4165,7 +5236,7 @@
         <v>659</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>840</v>
+        <v>919</v>
       </c>
       <c r="J46" s="0">
         <v>5173.3311000000003</v>
@@ -4197,7 +5268,7 @@
         <v>660</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>841</v>
+        <v>920</v>
       </c>
       <c r="J47" s="0">
         <v>3079.3002999999999</v>
@@ -4229,7 +5300,7 @@
         <v>663</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>843</v>
+        <v>921</v>
       </c>
       <c r="J48" s="0">
         <v>424.15600000000001</v>
@@ -4261,7 +5332,7 @@
         <v>664</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>844</v>
+        <v>922</v>
       </c>
       <c r="J49" s="0">
         <v>387.75049999999999</v>
@@ -4293,7 +5364,7 @@
         <v>665</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>845</v>
+        <v>923</v>
       </c>
       <c r="J50" s="0">
         <v>348.00529999999998</v>
@@ -4325,7 +5396,7 @@
         <v>666</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>846</v>
+        <v>924</v>
       </c>
       <c r="J51" s="0">
         <v>332.44470000000001</v>
@@ -4357,7 +5428,7 @@
         <v>667</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>847</v>
+        <v>925</v>
       </c>
       <c r="J52" s="0">
         <v>320.80650000000003</v>
@@ -4389,7 +5460,7 @@
         <v>668</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>848</v>
+        <v>926</v>
       </c>
       <c r="J53" s="0">
         <v>310.77530000000002</v>
@@ -4421,7 +5492,7 @@
         <v>669</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>849</v>
+        <v>927</v>
       </c>
       <c r="J54" s="0">
         <v>255.58779999999999</v>
@@ -4453,7 +5524,7 @@
         <v>670</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>850</v>
+        <v>928</v>
       </c>
       <c r="J55" s="0">
         <v>224.2235</v>
@@ -4485,7 +5556,7 @@
         <v>671</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>851</v>
+        <v>929</v>
       </c>
       <c r="J56" s="0">
         <v>6088.3633</v>
@@ -4517,7 +5588,7 @@
         <v>672</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>852</v>
+        <v>930</v>
       </c>
       <c r="J57" s="0">
         <v>5077.0581000000002</v>
@@ -4549,7 +5620,7 @@
         <v>673</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>853</v>
+        <v>931</v>
       </c>
       <c r="J58" s="0">
         <v>728.97640000000001</v>
@@ -4581,7 +5652,7 @@
         <v>674</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>854</v>
+        <v>932</v>
       </c>
       <c r="J59" s="0">
         <v>681.9529</v>
@@ -4613,7 +5684,7 @@
         <v>675</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>855</v>
+        <v>933</v>
       </c>
       <c r="J60" s="0">
         <v>460.65499999999997</v>
@@ -4645,7 +5716,7 @@
         <v>676</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>856</v>
+        <v>934</v>
       </c>
       <c r="J61" s="0">
         <v>406.1062</v>
@@ -4677,7 +5748,7 @@
         <v>677</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>857</v>
+        <v>935</v>
       </c>
       <c r="J62" s="0">
         <v>382.6694</v>
@@ -4709,7 +5780,7 @@
         <v>678</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>858</v>
+        <v>936</v>
       </c>
       <c r="J63" s="0">
         <v>369.21839999999998</v>
@@ -4741,7 +5812,7 @@
         <v>679</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>859</v>
+        <v>937</v>
       </c>
       <c r="J64" s="0">
         <v>341.30959999999999</v>
@@ -4773,7 +5844,7 @@
         <v>680</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>860</v>
+        <v>938</v>
       </c>
       <c r="J65" s="0">
         <v>319.78870000000001</v>
@@ -4805,7 +5876,7 @@
         <v>681</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>861</v>
+        <v>939</v>
       </c>
       <c r="J66" s="0">
         <v>289.6028</v>
@@ -4837,7 +5908,7 @@
         <v>682</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>862</v>
+        <v>940</v>
       </c>
       <c r="J67" s="0">
         <v>284.9262</v>
@@ -4869,7 +5940,7 @@
         <v>683</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>863</v>
+        <v>941</v>
       </c>
       <c r="J68" s="0">
         <v>5367.4771000000001</v>
@@ -4901,7 +5972,7 @@
         <v>684</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>864</v>
+        <v>942</v>
       </c>
       <c r="J69" s="0">
         <v>3219.1161999999999</v>
@@ -4933,7 +6004,7 @@
         <v>307</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>865</v>
+        <v>943</v>
       </c>
       <c r="J70" s="0">
         <v>999.82090000000005</v>
@@ -4965,7 +6036,7 @@
         <v>308</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>866</v>
+        <v>944</v>
       </c>
       <c r="J71" s="0">
         <v>829.32470000000001</v>
@@ -4997,7 +6068,7 @@
         <v>685</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>867</v>
+        <v>945</v>
       </c>
       <c r="J72" s="0">
         <v>434.72210000000001</v>
@@ -5029,7 +6100,7 @@
         <v>686</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>868</v>
+        <v>946</v>
       </c>
       <c r="J73" s="0">
         <v>420.51510000000002</v>
@@ -5061,7 +6132,7 @@
         <v>687</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>869</v>
+        <v>947</v>
       </c>
       <c r="J74" s="0">
         <v>416.28559999999999</v>
@@ -5093,7 +6164,7 @@
         <v>688</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>870</v>
+        <v>948</v>
       </c>
       <c r="J75" s="0">
         <v>400.9085</v>
@@ -5125,7 +6196,7 @@
         <v>689</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>871</v>
+        <v>949</v>
       </c>
       <c r="J76" s="0">
         <v>360.4205</v>
@@ -5157,7 +6228,7 @@
         <v>690</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>872</v>
+        <v>950</v>
       </c>
       <c r="J77" s="0">
         <v>305.30689999999999</v>
@@ -5189,7 +6260,7 @@
         <v>691</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>873</v>
+        <v>951</v>
       </c>
       <c r="J78" s="0">
         <v>293.2808</v>
@@ -5221,7 +6292,7 @@
         <v>692</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>874</v>
+        <v>952</v>
       </c>
       <c r="J79" s="0">
         <v>247.7748</v>
@@ -5253,7 +6324,7 @@
         <v>91</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>390</v>
+        <v>953</v>
       </c>
       <c r="J80" s="0">
         <v>5813.3739999999998</v>
@@ -5285,7 +6356,7 @@
         <v>92</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>391</v>
+        <v>954</v>
       </c>
       <c r="J81" s="0">
         <v>3499.9191999999998</v>
@@ -5317,7 +6388,7 @@
         <v>93</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>392</v>
+        <v>955</v>
       </c>
       <c r="J82" s="0">
         <v>643.7663</v>
@@ -5349,7 +6420,7 @@
         <v>94</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>393</v>
+        <v>956</v>
       </c>
       <c r="J83" s="0">
         <v>507.9119</v>
@@ -5381,7 +6452,7 @@
         <v>95</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>394</v>
+        <v>957</v>
       </c>
       <c r="J84" s="0">
         <v>413.24200000000002</v>
@@ -5413,7 +6484,7 @@
         <v>96</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>395</v>
+        <v>958</v>
       </c>
       <c r="J85" s="0">
         <v>412.743</v>
@@ -5445,7 +6516,7 @@
         <v>97</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>396</v>
+        <v>959</v>
       </c>
       <c r="J86" s="0">
         <v>365.9803</v>
@@ -5477,7 +6548,7 @@
         <v>98</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>397</v>
+        <v>960</v>
       </c>
       <c r="J87" s="0">
         <v>362.68889999999999</v>
@@ -5509,7 +6580,7 @@
         <v>99</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>398</v>
+        <v>961</v>
       </c>
       <c r="J88" s="0">
         <v>337.94470000000001</v>
@@ -5541,7 +6612,7 @@
         <v>100</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>399</v>
+        <v>962</v>
       </c>
       <c r="J89" s="0">
         <v>275.04509999999999</v>
@@ -5573,7 +6644,7 @@
         <v>101</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>400</v>
+        <v>963</v>
       </c>
       <c r="J90" s="0">
         <v>253.987</v>
@@ -5605,7 +6676,7 @@
         <v>102</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>401</v>
+        <v>964</v>
       </c>
       <c r="J91" s="0">
         <v>197.0513</v>
@@ -5637,7 +6708,7 @@
         <v>103</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>402</v>
+        <v>965</v>
       </c>
       <c r="J92" s="0">
         <v>6411.3008</v>
@@ -5669,7 +6740,7 @@
         <v>104</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>403</v>
+        <v>966</v>
       </c>
       <c r="J93" s="0">
         <v>5363.7114000000001</v>
@@ -5701,7 +6772,7 @@
         <v>107</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>406</v>
+        <v>967</v>
       </c>
       <c r="J94" s="0">
         <v>465.0847</v>
@@ -5733,7 +6804,7 @@
         <v>108</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>407</v>
+        <v>968</v>
       </c>
       <c r="J95" s="0">
         <v>432.71969999999999</v>
@@ -5765,7 +6836,7 @@
         <v>109</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>408</v>
+        <v>969</v>
       </c>
       <c r="J96" s="0">
         <v>403.6884</v>
@@ -5797,7 +6868,7 @@
         <v>110</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>409</v>
+        <v>970</v>
       </c>
       <c r="J97" s="0">
         <v>393.85660000000001</v>
@@ -5829,7 +6900,7 @@
         <v>111</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>410</v>
+        <v>971</v>
       </c>
       <c r="J98" s="0">
         <v>328.83640000000003</v>
@@ -5861,7 +6932,7 @@
         <v>112</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>411</v>
+        <v>972</v>
       </c>
       <c r="J99" s="0">
         <v>289.99919999999997</v>
@@ -5893,7 +6964,7 @@
         <v>113</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>412</v>
+        <v>973</v>
       </c>
       <c r="J100" s="0">
         <v>253.50819999999999</v>
@@ -5925,7 +6996,7 @@
         <v>114</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>413</v>
+        <v>974</v>
       </c>
       <c r="J101" s="0">
         <v>156.39179999999999</v>
@@ -5957,7 +7028,7 @@
         <v>115</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>414</v>
+        <v>975</v>
       </c>
       <c r="J102" s="0">
         <v>5347.2299999999996</v>
@@ -5989,7 +7060,7 @@
         <v>117</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>416</v>
+        <v>976</v>
       </c>
       <c r="J103" s="0">
         <v>832.64940000000001</v>
@@ -6021,7 +7092,7 @@
         <v>118</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>417</v>
+        <v>977</v>
       </c>
       <c r="J104" s="0">
         <v>670.97080000000005</v>
@@ -6053,7 +7124,7 @@
         <v>119</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>418</v>
+        <v>978</v>
       </c>
       <c r="J105" s="0">
         <v>452.6379</v>
@@ -6085,7 +7156,7 @@
         <v>120</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>419</v>
+        <v>979</v>
       </c>
       <c r="J106" s="0">
         <v>432.76639999999998</v>
@@ -6117,7 +7188,7 @@
         <v>121</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>420</v>
+        <v>980</v>
       </c>
       <c r="J107" s="0">
         <v>430.21100000000001</v>
@@ -6149,7 +7220,7 @@
         <v>122</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>421</v>
+        <v>981</v>
       </c>
       <c r="J108" s="0">
         <v>426.60840000000002</v>
@@ -6181,7 +7252,7 @@
         <v>123</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>422</v>
+        <v>982</v>
       </c>
       <c r="J109" s="0">
         <v>408.17599999999999</v>
@@ -6213,7 +7284,7 @@
         <v>124</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>423</v>
+        <v>983</v>
       </c>
       <c r="J110" s="0">
         <v>393.9744</v>
@@ -6245,7 +7316,7 @@
         <v>125</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>424</v>
+        <v>984</v>
       </c>
       <c r="J111" s="0">
         <v>369.06290000000001</v>
@@ -6277,7 +7348,7 @@
         <v>126</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>425</v>
+        <v>985</v>
       </c>
       <c r="J112" s="0">
         <v>363.61939999999999</v>
@@ -6309,7 +7380,7 @@
         <v>127</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>426</v>
+        <v>986</v>
       </c>
       <c r="J113" s="0">
         <v>5889.4614000000001</v>
@@ -6341,7 +7412,7 @@
         <v>128</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>427</v>
+        <v>987</v>
       </c>
       <c r="J114" s="0">
         <v>2742.3312999999998</v>
@@ -6373,7 +7444,7 @@
         <v>129</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>428</v>
+        <v>988</v>
       </c>
       <c r="J115" s="0">
         <v>673.23270000000002</v>
@@ -6405,7 +7476,7 @@
         <v>130</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>429</v>
+        <v>989</v>
       </c>
       <c r="J116" s="0">
         <v>548.54560000000004</v>
@@ -6437,7 +7508,7 @@
         <v>131</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>430</v>
+        <v>990</v>
       </c>
       <c r="J117" s="0">
         <v>406.4975</v>
@@ -6469,7 +7540,7 @@
         <v>132</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>431</v>
+        <v>991</v>
       </c>
       <c r="J118" s="0">
         <v>370.59609999999998</v>
@@ -6501,7 +7572,7 @@
         <v>133</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>432</v>
+        <v>992</v>
       </c>
       <c r="J119" s="0">
         <v>295.41489999999999</v>
@@ -6533,7 +7604,7 @@
         <v>134</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>433</v>
+        <v>993</v>
       </c>
       <c r="J120" s="0">
         <v>294.39229999999998</v>
@@ -6565,7 +7636,7 @@
         <v>135</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>434</v>
+        <v>994</v>
       </c>
       <c r="J121" s="0">
         <v>290.21879999999999</v>
@@ -6597,7 +7668,7 @@
         <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>436</v>
+        <v>995</v>
       </c>
       <c r="J122" s="0">
         <v>241.96080000000001</v>
@@ -6629,7 +7700,7 @@
         <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>437</v>
+        <v>996</v>
       </c>
       <c r="J123" s="0">
         <v>208.0266</v>
@@ -6661,7 +7732,7 @@
         <v>140</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>439</v>
+        <v>997</v>
       </c>
       <c r="J124" s="0">
         <v>2255.5239000000001</v>
@@ -6693,7 +7764,7 @@
         <v>141</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>440</v>
+        <v>998</v>
       </c>
       <c r="J125" s="0">
         <v>784.23540000000003</v>
@@ -6725,7 +7796,7 @@
         <v>142</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>441</v>
+        <v>999</v>
       </c>
       <c r="J126" s="0">
         <v>590.41420000000005</v>
@@ -6757,7 +7828,7 @@
         <v>143</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>442</v>
+        <v>1000</v>
       </c>
       <c r="J127" s="0">
         <v>431.26760000000002</v>
@@ -6789,7 +7860,7 @@
         <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>443</v>
+        <v>1001</v>
       </c>
       <c r="J128" s="0">
         <v>372.27710000000002</v>
@@ -6821,7 +7892,7 @@
         <v>145</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>444</v>
+        <v>1002</v>
       </c>
       <c r="J129" s="0">
         <v>370.83260000000001</v>
@@ -6853,7 +7924,7 @@
         <v>146</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>445</v>
+        <v>1003</v>
       </c>
       <c r="J130" s="0">
         <v>368.27210000000002</v>
@@ -6885,7 +7956,7 @@
         <v>147</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>446</v>
+        <v>1004</v>
       </c>
       <c r="J131" s="0">
         <v>345.15750000000003</v>
@@ -6917,7 +7988,7 @@
         <v>148</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>447</v>
+        <v>1005</v>
       </c>
       <c r="J132" s="0">
         <v>335.8723</v>
@@ -6949,7 +8020,7 @@
         <v>149</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>448</v>
+        <v>1006</v>
       </c>
       <c r="J133" s="0">
         <v>309.04379999999998</v>
@@ -6981,7 +8052,7 @@
         <v>150</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>449</v>
+        <v>1007</v>
       </c>
       <c r="J134" s="0">
         <v>280.34730000000002</v>
@@ -7013,7 +8084,7 @@
         <v>151</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>450</v>
+        <v>1008</v>
       </c>
       <c r="J135" s="0">
         <v>6089.4750999999997</v>
@@ -7045,7 +8116,7 @@
         <v>152</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>451</v>
+        <v>1009</v>
       </c>
       <c r="J136" s="0">
         <v>4801.2959000000001</v>
@@ -7077,7 +8148,7 @@
         <v>153</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>452</v>
+        <v>1010</v>
       </c>
       <c r="J137" s="0">
         <v>729.38409999999999</v>
@@ -7109,7 +8180,7 @@
         <v>155</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>454</v>
+        <v>1011</v>
       </c>
       <c r="J138" s="0">
         <v>414.8329</v>
@@ -7141,7 +8212,7 @@
         <v>156</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>455</v>
+        <v>1012</v>
       </c>
       <c r="J139" s="0">
         <v>407.11009999999999</v>
@@ -7173,7 +8244,7 @@
         <v>157</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>456</v>
+        <v>1013</v>
       </c>
       <c r="J140" s="0">
         <v>390.21910000000003</v>
@@ -7205,7 +8276,7 @@
         <v>158</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>457</v>
+        <v>1014</v>
       </c>
       <c r="J141" s="0">
         <v>362.1839</v>
@@ -7237,7 +8308,7 @@
         <v>159</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>458</v>
+        <v>1015</v>
       </c>
       <c r="J142" s="0">
         <v>349.2903</v>
@@ -7269,7 +8340,7 @@
         <v>160</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>459</v>
+        <v>1016</v>
       </c>
       <c r="J143" s="0">
         <v>339.61919999999998</v>
@@ -7301,7 +8372,7 @@
         <v>161</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>460</v>
+        <v>1017</v>
       </c>
       <c r="J144" s="0">
         <v>321.077</v>
@@ -7333,7 +8404,7 @@
         <v>162</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>461</v>
+        <v>1018</v>
       </c>
       <c r="J145" s="0">
         <v>320.34030000000001</v>
@@ -7365,7 +8436,7 @@
         <v>163</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>462</v>
+        <v>1019</v>
       </c>
       <c r="J146" s="0">
         <v>4900.8388999999997</v>
@@ -7397,7 +8468,7 @@
         <v>164</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>463</v>
+        <v>1020</v>
       </c>
       <c r="J147" s="0">
         <v>2991.1887000000002</v>
@@ -7429,7 +8500,7 @@
         <v>165</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>464</v>
+        <v>1021</v>
       </c>
       <c r="J148" s="0">
         <v>694.42499999999996</v>
@@ -7461,7 +8532,7 @@
         <v>166</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>465</v>
+        <v>1022</v>
       </c>
       <c r="J149" s="0">
         <v>590.76210000000003</v>
@@ -7493,7 +8564,7 @@
         <v>167</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>466</v>
+        <v>1023</v>
       </c>
       <c r="J150" s="0">
         <v>434.02370000000002</v>
@@ -7525,7 +8596,7 @@
         <v>168</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>467</v>
+        <v>1024</v>
       </c>
       <c r="J151" s="0">
         <v>417.05189999999999</v>
@@ -7557,7 +8628,7 @@
         <v>169</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>468</v>
+        <v>1025</v>
       </c>
       <c r="J152" s="0">
         <v>407.86430000000001</v>
@@ -7589,7 +8660,7 @@
         <v>170</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>469</v>
+        <v>1026</v>
       </c>
       <c r="J153" s="0">
         <v>406.37779999999998</v>
@@ -7621,7 +8692,7 @@
         <v>171</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>470</v>
+        <v>1027</v>
       </c>
       <c r="J154" s="0">
         <v>379.51209999999998</v>
@@ -7653,7 +8724,7 @@
         <v>172</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>471</v>
+        <v>1028</v>
       </c>
       <c r="J155" s="0">
         <v>361.57029999999998</v>
@@ -7685,7 +8756,7 @@
         <v>173</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>472</v>
+        <v>1029</v>
       </c>
       <c r="J156" s="0">
         <v>324.36189999999999</v>
@@ -7717,7 +8788,7 @@
         <v>176</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>475</v>
+        <v>1030</v>
       </c>
       <c r="J157" s="0">
         <v>2639.6545000000001</v>
@@ -7749,7 +8820,7 @@
         <v>177</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>476</v>
+        <v>1031</v>
       </c>
       <c r="J158" s="0">
         <v>538.57830000000001</v>
@@ -7781,7 +8852,7 @@
         <v>178</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>477</v>
+        <v>1032</v>
       </c>
       <c r="J159" s="0">
         <v>439.68729999999999</v>
@@ -7813,7 +8884,7 @@
         <v>180</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>479</v>
+        <v>1033</v>
       </c>
       <c r="J160" s="0">
         <v>348.95269999999999</v>
@@ -7845,7 +8916,7 @@
         <v>181</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>480</v>
+        <v>1034</v>
       </c>
       <c r="J161" s="0">
         <v>320.45060000000001</v>
@@ -7877,7 +8948,7 @@
         <v>182</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>481</v>
+        <v>1035</v>
       </c>
       <c r="J162" s="0">
         <v>306.95499999999999</v>
@@ -7909,7 +8980,7 @@
         <v>183</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>482</v>
+        <v>1036</v>
       </c>
       <c r="J163" s="0">
         <v>286.13639999999998</v>
@@ -7941,7 +9012,7 @@
         <v>184</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>483</v>
+        <v>1037</v>
       </c>
       <c r="J164" s="0">
         <v>270.46800000000002</v>
@@ -7973,7 +9044,7 @@
         <v>185</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>484</v>
+        <v>1038</v>
       </c>
       <c r="J165" s="0">
         <v>266.42959999999999</v>
@@ -8005,7 +9076,7 @@
         <v>186</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>485</v>
+        <v>1039</v>
       </c>
       <c r="J166" s="0">
         <v>198.7653</v>
@@ -8037,7 +9108,7 @@
         <v>187</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>486</v>
+        <v>1040</v>
       </c>
       <c r="J167" s="0">
         <v>6949.5127000000002</v>
@@ -8069,7 +9140,7 @@
         <v>188</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>487</v>
+        <v>1041</v>
       </c>
       <c r="J168" s="0">
         <v>1918.3168000000001</v>
@@ -8101,7 +9172,7 @@
         <v>189</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>488</v>
+        <v>1042</v>
       </c>
       <c r="J169" s="0">
         <v>842.53420000000006</v>
@@ -8133,7 +9204,7 @@
         <v>190</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>489</v>
+        <v>1043</v>
       </c>
       <c r="J170" s="0">
         <v>625.51949999999999</v>
@@ -8165,7 +9236,7 @@
         <v>191</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>490</v>
+        <v>1044</v>
       </c>
       <c r="J171" s="0">
         <v>403.39569999999998</v>
@@ -8197,7 +9268,7 @@
         <v>192</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>491</v>
+        <v>1045</v>
       </c>
       <c r="J172" s="0">
         <v>401.83440000000002</v>
@@ -8229,7 +9300,7 @@
         <v>193</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>492</v>
+        <v>1046</v>
       </c>
       <c r="J173" s="0">
         <v>401.53390000000002</v>
@@ -8261,7 +9332,7 @@
         <v>194</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>493</v>
+        <v>1047</v>
       </c>
       <c r="J174" s="0">
         <v>325.73790000000002</v>
@@ -8293,7 +9364,7 @@
         <v>195</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>494</v>
+        <v>1048</v>
       </c>
       <c r="J175" s="0">
         <v>306.47129999999999</v>
@@ -8325,7 +9396,7 @@
         <v>196</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>495</v>
+        <v>1049</v>
       </c>
       <c r="J176" s="0">
         <v>297.54129999999998</v>
@@ -8357,7 +9428,7 @@
         <v>197</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>496</v>
+        <v>1050</v>
       </c>
       <c r="J177" s="0">
         <v>251.23050000000001</v>
@@ -8389,7 +9460,7 @@
         <v>198</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>497</v>
+        <v>1051</v>
       </c>
       <c r="J178" s="0">
         <v>104.34829999999999</v>
@@ -8421,7 +9492,7 @@
         <v>199</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>498</v>
+        <v>1052</v>
       </c>
       <c r="J179" s="0">
         <v>5196.1244999999999</v>
@@ -8453,7 +9524,7 @@
         <v>201</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>500</v>
+        <v>1053</v>
       </c>
       <c r="J180" s="0">
         <v>554.0693</v>
@@ -8485,7 +9556,7 @@
         <v>202</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>501</v>
+        <v>1054</v>
       </c>
       <c r="J181" s="0">
         <v>97.465900000000005</v>
@@ -8517,7 +9588,7 @@
         <v>203</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>502</v>
+        <v>1055</v>
       </c>
       <c r="J182" s="0">
         <v>413.24349999999998</v>
@@ -8549,7 +9620,7 @@
         <v>204</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>503</v>
+        <v>1056</v>
       </c>
       <c r="J183" s="0">
         <v>390.69720000000001</v>
@@ -8581,7 +9652,7 @@
         <v>205</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>504</v>
+        <v>1057</v>
       </c>
       <c r="J184" s="0">
         <v>384.44110000000001</v>
@@ -8613,7 +9684,7 @@
         <v>206</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>505</v>
+        <v>1058</v>
       </c>
       <c r="J185" s="0">
         <v>369.39760000000001</v>
@@ -8645,7 +9716,7 @@
         <v>207</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>506</v>
+        <v>1059</v>
       </c>
       <c r="J186" s="0">
         <v>355.85449999999997</v>
@@ -8677,7 +9748,7 @@
         <v>208</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>507</v>
+        <v>1060</v>
       </c>
       <c r="J187" s="0">
         <v>332.20139999999998</v>
@@ -8709,7 +9780,7 @@
         <v>209</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>508</v>
+        <v>1061</v>
       </c>
       <c r="J188" s="0">
         <v>304.4751</v>
@@ -8741,7 +9812,7 @@
         <v>210</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>509</v>
+        <v>1062</v>
       </c>
       <c r="J189" s="0">
         <v>263.24160000000001</v>
@@ -8773,7 +9844,7 @@
         <v>211</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>510</v>
+        <v>1063</v>
       </c>
       <c r="J190" s="0">
         <v>5598.6216000000004</v>
@@ -8805,7 +9876,7 @@
         <v>212</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>511</v>
+        <v>1064</v>
       </c>
       <c r="J191" s="0">
         <v>4298.6826000000001</v>
@@ -8837,7 +9908,7 @@
         <v>213</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>512</v>
+        <v>1065</v>
       </c>
       <c r="J192" s="0">
         <v>831.18269999999996</v>
@@ -8869,7 +9940,7 @@
         <v>214</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>513</v>
+        <v>1066</v>
       </c>
       <c r="J193" s="0">
         <v>746.42259999999999</v>
@@ -8901,7 +9972,7 @@
         <v>215</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>514</v>
+        <v>1067</v>
       </c>
       <c r="J194" s="0">
         <v>477.65440000000001</v>
@@ -8933,7 +10004,7 @@
         <v>216</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>515</v>
+        <v>1068</v>
       </c>
       <c r="J195" s="0">
         <v>455.09550000000002</v>
@@ -8965,7 +10036,7 @@
         <v>217</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>516</v>
+        <v>1069</v>
       </c>
       <c r="J196" s="0">
         <v>442.9828</v>
@@ -8997,7 +10068,7 @@
         <v>218</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>517</v>
+        <v>1070</v>
       </c>
       <c r="J197" s="0">
         <v>403.95710000000003</v>
@@ -9029,7 +10100,7 @@
         <v>219</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>518</v>
+        <v>1071</v>
       </c>
       <c r="J198" s="0">
         <v>353.99869999999999</v>
@@ -9061,7 +10132,7 @@
         <v>220</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>519</v>
+        <v>1072</v>
       </c>
       <c r="J199" s="0">
         <v>282.62110000000001</v>
@@ -9093,7 +10164,7 @@
         <v>221</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>520</v>
+        <v>1073</v>
       </c>
       <c r="J200" s="0">
         <v>251.0352</v>
@@ -9125,7 +10196,7 @@
         <v>222</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>521</v>
+        <v>1074</v>
       </c>
       <c r="J201" s="0">
         <v>226.5855</v>
@@ -9157,7 +10228,7 @@
         <v>223</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>522</v>
+        <v>1075</v>
       </c>
       <c r="J202" s="0">
         <v>3073.4854</v>
@@ -9189,7 +10260,7 @@
         <v>224</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>523</v>
+        <v>1076</v>
       </c>
       <c r="J203" s="0">
         <v>1817.3022000000001</v>
@@ -9221,7 +10292,7 @@
         <v>213</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>524</v>
+        <v>1077</v>
       </c>
       <c r="J204" s="0">
         <v>831.18269999999996</v>
@@ -9253,7 +10324,7 @@
         <v>225</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>526</v>
+        <v>1078</v>
       </c>
       <c r="J205" s="0">
         <v>444.28719999999999</v>
@@ -9285,7 +10356,7 @@
         <v>226</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>527</v>
+        <v>1079</v>
       </c>
       <c r="J206" s="0">
         <v>406.01569999999998</v>
@@ -9317,7 +10388,7 @@
         <v>227</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>528</v>
+        <v>1080</v>
       </c>
       <c r="J207" s="0">
         <v>377.0512</v>
@@ -9349,7 +10420,7 @@
         <v>228</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>529</v>
+        <v>1081</v>
       </c>
       <c r="J208" s="0">
         <v>370.54059999999998</v>
@@ -9381,7 +10452,7 @@
         <v>229</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>530</v>
+        <v>1082</v>
       </c>
       <c r="J209" s="0">
         <v>364.45699999999999</v>
@@ -9413,7 +10484,7 @@
         <v>230</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>531</v>
+        <v>1083</v>
       </c>
       <c r="J210" s="0">
         <v>357.5231</v>
@@ -9445,7 +10516,7 @@
         <v>231</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>532</v>
+        <v>1084</v>
       </c>
       <c r="J211" s="0">
         <v>289.80360000000002</v>
@@ -9477,7 +10548,7 @@
         <v>232</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>533</v>
+        <v>1085</v>
       </c>
       <c r="J212" s="0">
         <v>205.23990000000001</v>
@@ -9509,7 +10580,7 @@
         <v>233</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>534</v>
+        <v>1086</v>
       </c>
       <c r="J213" s="0">
         <v>5904.6377000000002</v>
@@ -9541,7 +10612,7 @@
         <v>234</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>535</v>
+        <v>1087</v>
       </c>
       <c r="J214" s="0">
         <v>4907.7012000000004</v>
@@ -9573,7 +10644,7 @@
         <v>235</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>536</v>
+        <v>1088</v>
       </c>
       <c r="J215" s="0">
         <v>202.81960000000001</v>
@@ -9605,7 +10676,7 @@
         <v>237</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>538</v>
+        <v>1089</v>
       </c>
       <c r="J216" s="0">
         <v>383.23849999999999</v>
@@ -9637,7 +10708,7 @@
         <v>238</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>539</v>
+        <v>1090</v>
       </c>
       <c r="J217" s="0">
         <v>363.8911</v>
@@ -9669,7 +10740,7 @@
         <v>239</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>540</v>
+        <v>1091</v>
       </c>
       <c r="J218" s="0">
         <v>355.88670000000002</v>
@@ -9701,7 +10772,7 @@
         <v>240</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>541</v>
+        <v>1092</v>
       </c>
       <c r="J219" s="0">
         <v>351.3347</v>
@@ -9733,7 +10804,7 @@
         <v>241</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>542</v>
+        <v>1093</v>
       </c>
       <c r="J220" s="0">
         <v>333.8578</v>
@@ -9765,7 +10836,7 @@
         <v>242</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>543</v>
+        <v>1094</v>
       </c>
       <c r="J221" s="0">
         <v>313.44380000000001</v>
@@ -9797,7 +10868,7 @@
         <v>243</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>544</v>
+        <v>1095</v>
       </c>
       <c r="J222" s="0">
         <v>238.27189999999999</v>
@@ -9829,7 +10900,7 @@
         <v>244</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>545</v>
+        <v>1096</v>
       </c>
       <c r="J223" s="0">
         <v>141.53020000000001</v>
@@ -9861,7 +10932,7 @@
         <v>245</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>546</v>
+        <v>1097</v>
       </c>
       <c r="J224" s="0">
         <v>6671.5464000000002</v>
@@ -9893,7 +10964,7 @@
         <v>246</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>547</v>
+        <v>1098</v>
       </c>
       <c r="J225" s="0">
         <v>2604.8850000000002</v>
@@ -9925,7 +10996,7 @@
         <v>248</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>549</v>
+        <v>1099</v>
       </c>
       <c r="J226" s="0">
         <v>539.66269999999997</v>
@@ -9957,7 +11028,7 @@
         <v>250</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>551</v>
+        <v>1100</v>
       </c>
       <c r="J227" s="0">
         <v>429.82010000000002</v>
@@ -9989,7 +11060,7 @@
         <v>251</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>552</v>
+        <v>1101</v>
       </c>
       <c r="J228" s="0">
         <v>421.38249999999999</v>
@@ -10021,7 +11092,7 @@
         <v>252</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>553</v>
+        <v>1102</v>
       </c>
       <c r="J229" s="0">
         <v>417.74880000000002</v>
@@ -10053,7 +11124,7 @@
         <v>253</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>554</v>
+        <v>1103</v>
       </c>
       <c r="J230" s="0">
         <v>393.11059999999998</v>
@@ -10085,7 +11156,7 @@
         <v>254</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>555</v>
+        <v>1104</v>
       </c>
       <c r="J231" s="0">
         <v>392.10489999999999</v>
@@ -10117,7 +11188,7 @@
         <v>255</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>556</v>
+        <v>1105</v>
       </c>
       <c r="J232" s="0">
         <v>387.5043</v>
@@ -10149,7 +11220,7 @@
         <v>256</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>557</v>
+        <v>1106</v>
       </c>
       <c r="J233" s="0">
         <v>215.23259999999999</v>
@@ -10181,7 +11252,7 @@
         <v>693</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>804</v>
+        <v>1107</v>
       </c>
       <c r="J234" s="0">
         <v>6179.7012000000004</v>
@@ -10213,7 +11284,7 @@
         <v>694</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>805</v>
+        <v>1108</v>
       </c>
       <c r="J235" s="0">
         <v>2590.0304999999999</v>
@@ -10245,7 +11316,7 @@
         <v>695</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>806</v>
+        <v>1109</v>
       </c>
       <c r="J236" s="0">
         <v>1052.7577000000001</v>
@@ -10277,7 +11348,7 @@
         <v>696</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>807</v>
+        <v>1110</v>
       </c>
       <c r="J237" s="0">
         <v>663.33749999999998</v>
@@ -10309,7 +11380,7 @@
         <v>697</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>808</v>
+        <v>1111</v>
       </c>
       <c r="J238" s="0">
         <v>506.81569999999999</v>
@@ -10341,7 +11412,7 @@
         <v>698</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>809</v>
+        <v>1112</v>
       </c>
       <c r="J239" s="0">
         <v>408.8279</v>
@@ -10373,7 +11444,7 @@
         <v>699</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>810</v>
+        <v>1113</v>
       </c>
       <c r="J240" s="0">
         <v>402.4606</v>
@@ -10405,7 +11476,7 @@
         <v>700</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>811</v>
+        <v>1114</v>
       </c>
       <c r="J241" s="0">
         <v>395.95499999999999</v>
@@ -10437,7 +11508,7 @@
         <v>701</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>812</v>
+        <v>1115</v>
       </c>
       <c r="J242" s="0">
         <v>384.18630000000002</v>
@@ -10469,7 +11540,7 @@
         <v>702</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>813</v>
+        <v>1116</v>
       </c>
       <c r="J243" s="0">
         <v>337.53550000000001</v>
@@ -10501,7 +11572,7 @@
         <v>703</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>814</v>
+        <v>1117</v>
       </c>
       <c r="J244" s="0">
         <v>304.91230000000002</v>
@@ -10533,7 +11604,7 @@
         <v>704</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>815</v>
+        <v>1118</v>
       </c>
       <c r="J245" s="0">
         <v>125.54000000000001</v>
@@ -10565,7 +11636,7 @@
         <v>705</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>816</v>
+        <v>1119</v>
       </c>
       <c r="J246" s="0">
         <v>5385.1138000000001</v>
@@ -10597,7 +11668,7 @@
         <v>706</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>817</v>
+        <v>1120</v>
       </c>
       <c r="J247" s="0">
         <v>2843.9126000000001</v>
@@ -10629,7 +11700,7 @@
         <v>707</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>818</v>
+        <v>1121</v>
       </c>
       <c r="J248" s="0">
         <v>710.74549999999999</v>
@@ -10661,7 +11732,7 @@
         <v>708</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>819</v>
+        <v>1122</v>
       </c>
       <c r="J249" s="0">
         <v>550.2423</v>
@@ -10693,7 +11764,7 @@
         <v>709</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>820</v>
+        <v>1123</v>
       </c>
       <c r="J250" s="0">
         <v>438.92590000000001</v>
@@ -10725,7 +11796,7 @@
         <v>710</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>821</v>
+        <v>1124</v>
       </c>
       <c r="J251" s="0">
         <v>423.42290000000003</v>
@@ -10757,7 +11828,7 @@
         <v>711</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>822</v>
+        <v>1125</v>
       </c>
       <c r="J252" s="0">
         <v>403.89089999999999</v>
@@ -10789,7 +11860,7 @@
         <v>712</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>823</v>
+        <v>1126</v>
       </c>
       <c r="J253" s="0">
         <v>391.21699999999999</v>
@@ -10821,7 +11892,7 @@
         <v>713</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>824</v>
+        <v>1127</v>
       </c>
       <c r="J254" s="0">
         <v>383.9436</v>
@@ -10853,7 +11924,7 @@
         <v>714</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>825</v>
+        <v>1128</v>
       </c>
       <c r="J255" s="0">
         <v>312.447</v>
@@ -10885,7 +11956,7 @@
         <v>715</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>826</v>
+        <v>1129</v>
       </c>
       <c r="J256" s="0">
         <v>309.3852</v>
@@ -10917,7 +11988,7 @@
         <v>716</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>827</v>
+        <v>1130</v>
       </c>
       <c r="J257" s="0">
         <v>235.6891</v>
@@ -10949,7 +12020,7 @@
         <v>717</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>828</v>
+        <v>1131</v>
       </c>
       <c r="J258" s="0">
         <v>6293.9867999999997</v>
@@ -10981,7 +12052,7 @@
         <v>718</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>829</v>
+        <v>1132</v>
       </c>
       <c r="J259" s="0">
         <v>5358.5902999999999</v>
@@ -11013,7 +12084,7 @@
         <v>719</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>830</v>
+        <v>1133</v>
       </c>
       <c r="J260" s="0">
         <v>577.04179999999997</v>
@@ -11045,7 +12116,7 @@
         <v>720</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>831</v>
+        <v>1134</v>
       </c>
       <c r="J261" s="0">
         <v>518.29719999999998</v>
@@ -11077,7 +12148,7 @@
         <v>721</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>832</v>
+        <v>1135</v>
       </c>
       <c r="J262" s="0">
         <v>427.73379999999997</v>
@@ -11109,7 +12180,7 @@
         <v>722</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>833</v>
+        <v>1136</v>
       </c>
       <c r="J263" s="0">
         <v>404.26459999999997</v>
@@ -11141,7 +12212,7 @@
         <v>723</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>834</v>
+        <v>1137</v>
       </c>
       <c r="J264" s="0">
         <v>398.51589999999999</v>
@@ -11173,7 +12244,7 @@
         <v>724</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>835</v>
+        <v>1138</v>
       </c>
       <c r="J265" s="0">
         <v>392.9486</v>
@@ -11205,7 +12276,7 @@
         <v>725</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>836</v>
+        <v>1139</v>
       </c>
       <c r="J266" s="0">
         <v>382.86340000000001</v>
@@ -11237,7 +12308,7 @@
         <v>726</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>837</v>
+        <v>1140</v>
       </c>
       <c r="J267" s="0">
         <v>368.97640000000001</v>
@@ -11269,7 +12340,7 @@
         <v>727</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>838</v>
+        <v>1141</v>
       </c>
       <c r="J268" s="0">
         <v>347.17689999999999</v>
@@ -11301,7 +12372,7 @@
         <v>728</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>839</v>
+        <v>1142</v>
       </c>
       <c r="J269" s="0">
         <v>328.54599999999999</v>
@@ -11333,7 +12404,7 @@
         <v>257</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>558</v>
+        <v>1143</v>
       </c>
       <c r="J270" s="0">
         <v>5568.125</v>
@@ -11365,7 +12436,7 @@
         <v>258</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>559</v>
+        <v>1144</v>
       </c>
       <c r="J271" s="0">
         <v>2316.6012999999998</v>
@@ -11397,7 +12468,7 @@
         <v>259</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>560</v>
+        <v>1145</v>
       </c>
       <c r="J272" s="0">
         <v>504.78460000000001</v>
@@ -11429,7 +12500,7 @@
         <v>260</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>561</v>
+        <v>1146</v>
       </c>
       <c r="J273" s="0">
         <v>445.50999999999999</v>
@@ -11461,7 +12532,7 @@
         <v>261</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>562</v>
+        <v>1147</v>
       </c>
       <c r="J274" s="0">
         <v>401.56920000000002</v>
@@ -11493,7 +12564,7 @@
         <v>262</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>563</v>
+        <v>1148</v>
       </c>
       <c r="J275" s="0">
         <v>392.42399999999998</v>
@@ -11525,7 +12596,7 @@
         <v>263</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>564</v>
+        <v>1149</v>
       </c>
       <c r="J276" s="0">
         <v>368.18880000000001</v>
@@ -11557,7 +12628,7 @@
         <v>264</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>565</v>
+        <v>1150</v>
       </c>
       <c r="J277" s="0">
         <v>366.78320000000002</v>
@@ -11589,7 +12660,7 @@
         <v>265</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>566</v>
+        <v>1151</v>
       </c>
       <c r="J278" s="0">
         <v>361.8997</v>
@@ -11621,7 +12692,7 @@
         <v>266</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>567</v>
+        <v>1152</v>
       </c>
       <c r="J279" s="0">
         <v>322.42989999999998</v>
@@ -11653,7 +12724,7 @@
         <v>267</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>568</v>
+        <v>1153</v>
       </c>
       <c r="J280" s="0">
         <v>308.6019</v>
@@ -11685,7 +12756,7 @@
         <v>268</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>569</v>
+        <v>1154</v>
       </c>
       <c r="J281" s="0">
         <v>260.48289999999997</v>
@@ -11717,7 +12788,7 @@
         <v>103</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>570</v>
+        <v>1155</v>
       </c>
       <c r="J282" s="0">
         <v>6411.3008</v>
@@ -11749,7 +12820,7 @@
         <v>104</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>571</v>
+        <v>1156</v>
       </c>
       <c r="J283" s="0">
         <v>5363.7114000000001</v>
@@ -11781,7 +12852,7 @@
         <v>107</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>574</v>
+        <v>1157</v>
       </c>
       <c r="J284" s="0">
         <v>465.0847</v>
@@ -11813,7 +12884,7 @@
         <v>108</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>575</v>
+        <v>1158</v>
       </c>
       <c r="J285" s="0">
         <v>432.71969999999999</v>
@@ -11845,7 +12916,7 @@
         <v>109</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>576</v>
+        <v>1159</v>
       </c>
       <c r="J286" s="0">
         <v>403.6884</v>
@@ -11877,7 +12948,7 @@
         <v>110</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>577</v>
+        <v>1160</v>
       </c>
       <c r="J287" s="0">
         <v>393.85660000000001</v>
@@ -11909,7 +12980,7 @@
         <v>111</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>578</v>
+        <v>1161</v>
       </c>
       <c r="J288" s="0">
         <v>328.83640000000003</v>
@@ -11941,7 +13012,7 @@
         <v>112</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>579</v>
+        <v>1162</v>
       </c>
       <c r="J289" s="0">
         <v>289.99919999999997</v>
@@ -11973,7 +13044,7 @@
         <v>113</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>580</v>
+        <v>1163</v>
       </c>
       <c r="J290" s="0">
         <v>253.50819999999999</v>
@@ -12005,7 +13076,7 @@
         <v>114</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>581</v>
+        <v>1164</v>
       </c>
       <c r="J291" s="0">
         <v>156.39179999999999</v>
@@ -12037,7 +13108,7 @@
         <v>269</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>582</v>
+        <v>1165</v>
       </c>
       <c r="J292" s="0">
         <v>5610.5132000000003</v>
@@ -12069,7 +13140,7 @@
         <v>270</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>583</v>
+        <v>1166</v>
       </c>
       <c r="J293" s="0">
         <v>2526.6718999999998</v>
@@ -12101,7 +13172,7 @@
         <v>271</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>584</v>
+        <v>1167</v>
       </c>
       <c r="J294" s="0">
         <v>663.2672</v>
@@ -12133,7 +13204,7 @@
         <v>272</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>585</v>
+        <v>1168</v>
       </c>
       <c r="J295" s="0">
         <v>553.69179999999994</v>
@@ -12165,7 +13236,7 @@
         <v>273</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>586</v>
+        <v>1169</v>
       </c>
       <c r="J296" s="0">
         <v>436.38159999999999</v>
@@ -12197,7 +13268,7 @@
         <v>274</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>587</v>
+        <v>1170</v>
       </c>
       <c r="J297" s="0">
         <v>411.78269999999998</v>
@@ -12229,7 +13300,7 @@
         <v>275</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>588</v>
+        <v>1171</v>
       </c>
       <c r="J298" s="0">
         <v>407.44670000000002</v>
@@ -12261,7 +13332,7 @@
         <v>276</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>589</v>
+        <v>1172</v>
       </c>
       <c r="J299" s="0">
         <v>390.17970000000003</v>
@@ -12293,7 +13364,7 @@
         <v>277</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>590</v>
+        <v>1173</v>
       </c>
       <c r="J300" s="0">
         <v>379.34300000000002</v>
@@ -12325,7 +13396,7 @@
         <v>278</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>591</v>
+        <v>1174</v>
       </c>
       <c r="J301" s="0">
         <v>378.32549999999998</v>
@@ -12357,7 +13428,7 @@
         <v>279</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>592</v>
+        <v>1175</v>
       </c>
       <c r="J302" s="0">
         <v>248.1077</v>
@@ -12389,7 +13460,7 @@
         <v>280</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>593</v>
+        <v>1176</v>
       </c>
       <c r="J303" s="0">
         <v>155.72280000000001</v>
@@ -12421,7 +13492,7 @@
         <v>281</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>594</v>
+        <v>1177</v>
       </c>
       <c r="J304" s="0">
         <v>6378.5679</v>
@@ -12453,7 +13524,7 @@
         <v>282</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>595</v>
+        <v>1178</v>
       </c>
       <c r="J305" s="0">
         <v>3677.8054000000002</v>
@@ -12485,7 +13556,7 @@
         <v>283</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>596</v>
+        <v>1179</v>
       </c>
       <c r="J306" s="0">
         <v>990.75639999999999</v>
@@ -12517,7 +13588,7 @@
         <v>284</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>597</v>
+        <v>1180</v>
       </c>
       <c r="J307" s="0">
         <v>912.61609999999996</v>
@@ -12549,7 +13620,7 @@
         <v>285</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>598</v>
+        <v>1181</v>
       </c>
       <c r="J308" s="0">
         <v>448.30200000000002</v>
@@ -12581,7 +13652,7 @@
         <v>286</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>599</v>
+        <v>1182</v>
       </c>
       <c r="J309" s="0">
         <v>415.84109999999998</v>
@@ -12613,7 +13684,7 @@
         <v>287</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>600</v>
+        <v>1183</v>
       </c>
       <c r="J310" s="0">
         <v>380.94420000000002</v>
@@ -12645,7 +13716,7 @@
         <v>288</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>601</v>
+        <v>1184</v>
       </c>
       <c r="J311" s="0">
         <v>359.60860000000002</v>
@@ -12677,7 +13748,7 @@
         <v>289</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>602</v>
+        <v>1185</v>
       </c>
       <c r="J312" s="0">
         <v>338.8168</v>
@@ -12709,7 +13780,7 @@
         <v>290</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>603</v>
+        <v>1186</v>
       </c>
       <c r="J313" s="0">
         <v>320.63470000000001</v>
@@ -12741,7 +13812,7 @@
         <v>291</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>604</v>
+        <v>1187</v>
       </c>
       <c r="J314" s="0">
         <v>287.04489999999999</v>
@@ -12773,7 +13844,7 @@
         <v>292</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>605</v>
+        <v>1188</v>
       </c>
       <c r="J315" s="0">
         <v>107.8788</v>
@@ -12805,7 +13876,7 @@
         <v>293</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>606</v>
+        <v>1189</v>
       </c>
       <c r="J316" s="0">
         <v>5099.2568000000001</v>
@@ -12837,7 +13908,7 @@
         <v>294</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>607</v>
+        <v>1190</v>
       </c>
       <c r="J317" s="0">
         <v>2383.1239999999998</v>
@@ -12869,7 +13940,7 @@
         <v>295</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>608</v>
+        <v>1191</v>
       </c>
       <c r="J318" s="0">
         <v>670.93709999999999</v>
@@ -12901,7 +13972,7 @@
         <v>296</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>609</v>
+        <v>1192</v>
       </c>
       <c r="J319" s="0">
         <v>459.24430000000001</v>
@@ -12933,7 +14004,7 @@
         <v>297</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>610</v>
+        <v>1193</v>
       </c>
       <c r="J320" s="0">
         <v>415.84710000000001</v>
@@ -12965,7 +14036,7 @@
         <v>298</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>611</v>
+        <v>1194</v>
       </c>
       <c r="J321" s="0">
         <v>404.09039999999999</v>
@@ -12997,7 +14068,7 @@
         <v>299</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>612</v>
+        <v>1195</v>
       </c>
       <c r="J322" s="0">
         <v>370.1207</v>
@@ -13029,7 +14100,7 @@
         <v>300</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>613</v>
+        <v>1196</v>
       </c>
       <c r="J323" s="0">
         <v>369.87549999999999</v>
@@ -13061,7 +14132,7 @@
         <v>301</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>614</v>
+        <v>1197</v>
       </c>
       <c r="J324" s="0">
         <v>332.15789999999998</v>
@@ -13093,7 +14164,7 @@
         <v>302</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>615</v>
+        <v>1198</v>
       </c>
       <c r="J325" s="0">
         <v>310.02600000000001</v>
@@ -13125,7 +14196,7 @@
         <v>303</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>616</v>
+        <v>1199</v>
       </c>
       <c r="J326" s="0">
         <v>137.19120000000001</v>
@@ -13157,7 +14228,7 @@
         <v>305</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>618</v>
+        <v>1200</v>
       </c>
       <c r="J327" s="0">
         <v>6147.9931999999999</v>
@@ -13189,7 +14260,7 @@
         <v>306</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>619</v>
+        <v>1201</v>
       </c>
       <c r="J328" s="0">
         <v>4509.7578000000003</v>
@@ -13221,7 +14292,7 @@
         <v>307</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>620</v>
+        <v>1202</v>
       </c>
       <c r="J329" s="0">
         <v>999.82090000000005</v>
@@ -13253,7 +14324,7 @@
         <v>308</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>621</v>
+        <v>1203</v>
       </c>
       <c r="J330" s="0">
         <v>829.32470000000001</v>
@@ -13285,7 +14356,7 @@
         <v>309</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>622</v>
+        <v>1204</v>
       </c>
       <c r="J331" s="0">
         <v>460.868</v>
@@ -13317,7 +14388,7 @@
         <v>310</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>623</v>
+        <v>1205</v>
       </c>
       <c r="J332" s="0">
         <v>418.91930000000002</v>
@@ -13349,7 +14420,7 @@
         <v>311</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>624</v>
+        <v>1206</v>
       </c>
       <c r="J333" s="0">
         <v>377.29809999999998</v>
@@ -13381,7 +14452,7 @@
         <v>312</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>625</v>
+        <v>1207</v>
       </c>
       <c r="J334" s="0">
         <v>376.07799999999998</v>
@@ -13413,7 +14484,7 @@
         <v>313</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>626</v>
+        <v>1208</v>
       </c>
       <c r="J335" s="0">
         <v>345.4522</v>
@@ -13445,7 +14516,7 @@
         <v>314</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>627</v>
+        <v>1209</v>
       </c>
       <c r="J336" s="0">
         <v>333.1805</v>
@@ -13477,7 +14548,7 @@
         <v>315</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>628</v>
+        <v>1210</v>
       </c>
       <c r="J337" s="0">
         <v>297.38940000000002</v>
@@ -13509,7 +14580,7 @@
         <v>316</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>629</v>
+        <v>1211</v>
       </c>
       <c r="J338" s="0">
         <v>196.88849999999999</v>
@@ -13541,7 +14612,7 @@
         <v>317</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>630</v>
+        <v>1212</v>
       </c>
       <c r="J339" s="0">
         <v>5372.8154000000004</v>
@@ -13573,7 +14644,7 @@
         <v>318</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>631</v>
+        <v>1213</v>
       </c>
       <c r="J340" s="0">
         <v>5089.0283</v>
@@ -13605,7 +14676,7 @@
         <v>321</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>634</v>
+        <v>1214</v>
       </c>
       <c r="J341" s="0">
         <v>414.66230000000002</v>
@@ -13637,7 +14708,7 @@
         <v>322</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>635</v>
+        <v>1215</v>
       </c>
       <c r="J342" s="0">
         <v>403.9067</v>
@@ -13669,7 +14740,7 @@
         <v>323</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>636</v>
+        <v>1216</v>
       </c>
       <c r="J343" s="0">
         <v>374.75290000000001</v>
@@ -13701,7 +14772,7 @@
         <v>324</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>637</v>
+        <v>1217</v>
       </c>
       <c r="J344" s="0">
         <v>372.04629999999997</v>
@@ -13733,7 +14804,7 @@
         <v>325</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>638</v>
+        <v>1218</v>
       </c>
       <c r="J345" s="0">
         <v>372.0009</v>
@@ -13765,7 +14836,7 @@
         <v>326</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>639</v>
+        <v>1219</v>
       </c>
       <c r="J346" s="0">
         <v>318.33179999999999</v>
@@ -13797,7 +14868,7 @@
         <v>327</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>640</v>
+        <v>1220</v>
       </c>
       <c r="J347" s="0">
         <v>295.59719999999999</v>
@@ -13829,7 +14900,7 @@
         <v>328</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>641</v>
+        <v>1221</v>
       </c>
       <c r="J348" s="0">
         <v>137.02930000000001</v>
@@ -13861,7 +14932,7 @@
         <v>329</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>642</v>
+        <v>1222</v>
       </c>
       <c r="J349" s="0">
         <v>4746.6201000000001</v>
@@ -13893,7 +14964,7 @@
         <v>330</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>643</v>
+        <v>1223</v>
       </c>
       <c r="J350" s="0">
         <v>4426.7367999999997</v>
@@ -13925,7 +14996,7 @@
         <v>331</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>644</v>
+        <v>1224</v>
       </c>
       <c r="J351" s="0">
         <v>502.13749999999999</v>
@@ -13957,7 +15028,7 @@
         <v>334</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>647</v>
+        <v>1225</v>
       </c>
       <c r="J352" s="0">
         <v>439.52850000000001</v>
@@ -13989,7 +15060,7 @@
         <v>335</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>648</v>
+        <v>1226</v>
       </c>
       <c r="J353" s="0">
         <v>423.6062</v>
@@ -14021,7 +15092,7 @@
         <v>336</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>649</v>
+        <v>1227</v>
       </c>
       <c r="J354" s="0">
         <v>388.16570000000002</v>
@@ -14053,7 +15124,7 @@
         <v>337</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>650</v>
+        <v>1228</v>
       </c>
       <c r="J355" s="0">
         <v>361.62639999999999</v>
@@ -14085,7 +15156,7 @@
         <v>338</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>651</v>
+        <v>1229</v>
       </c>
       <c r="J356" s="0">
         <v>319.28989999999999</v>
@@ -14117,7 +15188,7 @@
         <v>339</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>652</v>
+        <v>1230</v>
       </c>
       <c r="J357" s="0">
         <v>283.29320000000001</v>
@@ -14149,7 +15220,7 @@
         <v>340</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>653</v>
+        <v>1231</v>
       </c>
       <c r="J358" s="0">
         <v>254.66130000000001</v>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="81754" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="194559" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="194559" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="201005" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>
@@ -3758,16 +3758,16 @@
   <dimension ref="A1:J385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="true"/>
-    <col min="2" max="2" width="7" customWidth="true"/>
-    <col min="3" max="3" width="11.28515625" customWidth="true"/>
-    <col min="4" max="4" width="17.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13" customWidth="true"/>
-    <col min="7" max="7" width="8.5703125" customWidth="true"/>
-    <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="147" customWidth="true"/>
-    <col min="10" max="10" width="9.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14.08984375" customWidth="true"/>
+    <col min="2" max="2" width="6.54296875" customWidth="true"/>
+    <col min="3" max="3" width="10.36328125" customWidth="true"/>
+    <col min="4" max="4" width="16.36328125" customWidth="true"/>
+    <col min="5" max="5" width="11.81640625" customWidth="true"/>
+    <col min="6" max="6" width="11.90625" customWidth="true"/>
+    <col min="7" max="7" width="7.90625" customWidth="true"/>
+    <col min="8" max="8" width="36.26953125" customWidth="true"/>
+    <col min="9" max="9" width="167.54296875" customWidth="true"/>
+    <col min="10" max="10" width="9.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3828,7 +3828,7 @@
         <v>43</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>875</v>
+        <v>342</v>
       </c>
       <c r="J2" s="0">
         <v>5104.9130999999998</v>
@@ -3860,7 +3860,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>876</v>
+        <v>343</v>
       </c>
       <c r="J3" s="0">
         <v>3263.4158000000002</v>
@@ -3892,7 +3892,7 @@
         <v>47</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>877</v>
+        <v>346</v>
       </c>
       <c r="J4" s="0">
         <v>443.3879</v>
@@ -3924,7 +3924,7 @@
         <v>48</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>878</v>
+        <v>347</v>
       </c>
       <c r="J5" s="0">
         <v>410.7122</v>
@@ -3956,7 +3956,7 @@
         <v>49</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>879</v>
+        <v>348</v>
       </c>
       <c r="J6" s="0">
         <v>393.60379999999998</v>
@@ -3988,7 +3988,7 @@
         <v>50</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>880</v>
+        <v>349</v>
       </c>
       <c r="J7" s="0">
         <v>378.97039999999998</v>
@@ -4020,7 +4020,7 @@
         <v>51</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>881</v>
+        <v>350</v>
       </c>
       <c r="J8" s="0">
         <v>353.012</v>
@@ -4052,7 +4052,7 @@
         <v>52</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>882</v>
+        <v>351</v>
       </c>
       <c r="J9" s="0">
         <v>323.56819999999999</v>
@@ -4084,7 +4084,7 @@
         <v>53</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>883</v>
+        <v>352</v>
       </c>
       <c r="J10" s="0">
         <v>292.92790000000002</v>
@@ -4116,7 +4116,7 @@
         <v>54</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>884</v>
+        <v>353</v>
       </c>
       <c r="J11" s="0">
         <v>218.8537</v>
@@ -4148,7 +4148,7 @@
         <v>55</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>885</v>
+        <v>354</v>
       </c>
       <c r="J12" s="0">
         <v>5212.9053000000004</v>
@@ -4180,7 +4180,7 @@
         <v>56</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>886</v>
+        <v>355</v>
       </c>
       <c r="J13" s="0">
         <v>1797.9413</v>
@@ -4212,7 +4212,7 @@
         <v>57</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>887</v>
+        <v>356</v>
       </c>
       <c r="J14" s="0">
         <v>942.65679999999998</v>
@@ -4244,7 +4244,7 @@
         <v>58</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>888</v>
+        <v>357</v>
       </c>
       <c r="J15" s="0">
         <v>813.27890000000002</v>
@@ -4276,7 +4276,7 @@
         <v>59</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>889</v>
+        <v>358</v>
       </c>
       <c r="J16" s="0">
         <v>394.9126</v>
@@ -4308,7 +4308,7 @@
         <v>60</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>890</v>
+        <v>359</v>
       </c>
       <c r="J17" s="0">
         <v>393.85860000000002</v>
@@ -4340,7 +4340,7 @@
         <v>61</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>891</v>
+        <v>360</v>
       </c>
       <c r="J18" s="0">
         <v>391.5865</v>
@@ -4372,7 +4372,7 @@
         <v>62</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>892</v>
+        <v>361</v>
       </c>
       <c r="J19" s="0">
         <v>383.69600000000003</v>
@@ -4404,7 +4404,7 @@
         <v>63</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>893</v>
+        <v>362</v>
       </c>
       <c r="J20" s="0">
         <v>367.87400000000002</v>
@@ -4436,7 +4436,7 @@
         <v>64</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>894</v>
+        <v>363</v>
       </c>
       <c r="J21" s="0">
         <v>367.8381</v>
@@ -4468,7 +4468,7 @@
         <v>65</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>895</v>
+        <v>364</v>
       </c>
       <c r="J22" s="0">
         <v>290.31869999999998</v>
@@ -4500,7 +4500,7 @@
         <v>66</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>896</v>
+        <v>365</v>
       </c>
       <c r="J23" s="0">
         <v>253.11709999999999</v>
@@ -4532,7 +4532,7 @@
         <v>67</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>897</v>
+        <v>366</v>
       </c>
       <c r="J24" s="0">
         <v>4968.7178000000004</v>
@@ -4564,7 +4564,7 @@
         <v>68</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>898</v>
+        <v>367</v>
       </c>
       <c r="J25" s="0">
         <v>3314.2456000000002</v>
@@ -4596,7 +4596,7 @@
         <v>69</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>899</v>
+        <v>368</v>
       </c>
       <c r="J26" s="0">
         <v>720.75220000000002</v>
@@ -4628,7 +4628,7 @@
         <v>70</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>900</v>
+        <v>369</v>
       </c>
       <c r="J27" s="0">
         <v>584.66700000000003</v>
@@ -4660,7 +4660,7 @@
         <v>71</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>901</v>
+        <v>370</v>
       </c>
       <c r="J28" s="0">
         <v>414.71820000000002</v>
@@ -4692,7 +4692,7 @@
         <v>72</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>902</v>
+        <v>371</v>
       </c>
       <c r="J29" s="0">
         <v>406.6533</v>
@@ -4724,7 +4724,7 @@
         <v>73</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>903</v>
+        <v>372</v>
       </c>
       <c r="J30" s="0">
         <v>371.4246</v>
@@ -4756,7 +4756,7 @@
         <v>74</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>904</v>
+        <v>373</v>
       </c>
       <c r="J31" s="0">
         <v>347.6481</v>
@@ -4788,7 +4788,7 @@
         <v>75</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>905</v>
+        <v>374</v>
       </c>
       <c r="J32" s="0">
         <v>340.82400000000001</v>
@@ -4820,7 +4820,7 @@
         <v>76</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>906</v>
+        <v>375</v>
       </c>
       <c r="J33" s="0">
         <v>308.06799999999998</v>
@@ -4852,7 +4852,7 @@
         <v>77</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>907</v>
+        <v>376</v>
       </c>
       <c r="J34" s="0">
         <v>252.10589999999999</v>
@@ -4884,7 +4884,7 @@
         <v>78</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>908</v>
+        <v>377</v>
       </c>
       <c r="J35" s="0">
         <v>213.29320000000001</v>
@@ -4916,7 +4916,7 @@
         <v>80</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>909</v>
+        <v>379</v>
       </c>
       <c r="J36" s="0">
         <v>2818.2202000000002</v>
@@ -4948,7 +4948,7 @@
         <v>81</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>910</v>
+        <v>380</v>
       </c>
       <c r="J37" s="0">
         <v>578.16610000000003</v>
@@ -4980,7 +4980,7 @@
         <v>83</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>911</v>
+        <v>382</v>
       </c>
       <c r="J38" s="0">
         <v>448.01760000000002</v>
@@ -5012,7 +5012,7 @@
         <v>84</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>912</v>
+        <v>383</v>
       </c>
       <c r="J39" s="0">
         <v>429.6198</v>
@@ -5044,7 +5044,7 @@
         <v>85</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>913</v>
+        <v>384</v>
       </c>
       <c r="J40" s="0">
         <v>406.0299</v>
@@ -5076,7 +5076,7 @@
         <v>86</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>914</v>
+        <v>385</v>
       </c>
       <c r="J41" s="0">
         <v>405.92529999999999</v>
@@ -5108,7 +5108,7 @@
         <v>87</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>915</v>
+        <v>386</v>
       </c>
       <c r="J42" s="0">
         <v>403.39850000000001</v>
@@ -5140,7 +5140,7 @@
         <v>88</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>916</v>
+        <v>387</v>
       </c>
       <c r="J43" s="0">
         <v>381.14350000000002</v>
@@ -5172,7 +5172,7 @@
         <v>89</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>917</v>
+        <v>388</v>
       </c>
       <c r="J44" s="0">
         <v>254.68129999999999</v>
@@ -5204,7 +5204,7 @@
         <v>90</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>918</v>
+        <v>389</v>
       </c>
       <c r="J45" s="0">
         <v>166.26730000000001</v>
@@ -5236,7 +5236,7 @@
         <v>659</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>919</v>
+        <v>840</v>
       </c>
       <c r="J46" s="0">
         <v>5173.3311000000003</v>
@@ -5268,7 +5268,7 @@
         <v>660</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>920</v>
+        <v>841</v>
       </c>
       <c r="J47" s="0">
         <v>3079.3002999999999</v>
@@ -5300,7 +5300,7 @@
         <v>663</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>921</v>
+        <v>843</v>
       </c>
       <c r="J48" s="0">
         <v>424.15600000000001</v>
@@ -5332,7 +5332,7 @@
         <v>664</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>922</v>
+        <v>844</v>
       </c>
       <c r="J49" s="0">
         <v>387.75049999999999</v>
@@ -5364,7 +5364,7 @@
         <v>665</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>923</v>
+        <v>845</v>
       </c>
       <c r="J50" s="0">
         <v>348.00529999999998</v>
@@ -5396,7 +5396,7 @@
         <v>666</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>924</v>
+        <v>846</v>
       </c>
       <c r="J51" s="0">
         <v>332.44470000000001</v>
@@ -5428,7 +5428,7 @@
         <v>667</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>925</v>
+        <v>847</v>
       </c>
       <c r="J52" s="0">
         <v>320.80650000000003</v>
@@ -5460,7 +5460,7 @@
         <v>668</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>926</v>
+        <v>848</v>
       </c>
       <c r="J53" s="0">
         <v>310.77530000000002</v>
@@ -5492,7 +5492,7 @@
         <v>669</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>927</v>
+        <v>849</v>
       </c>
       <c r="J54" s="0">
         <v>255.58779999999999</v>
@@ -5524,7 +5524,7 @@
         <v>670</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>928</v>
+        <v>850</v>
       </c>
       <c r="J55" s="0">
         <v>224.2235</v>
@@ -5556,7 +5556,7 @@
         <v>671</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>929</v>
+        <v>851</v>
       </c>
       <c r="J56" s="0">
         <v>6088.3633</v>
@@ -5588,7 +5588,7 @@
         <v>672</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>930</v>
+        <v>852</v>
       </c>
       <c r="J57" s="0">
         <v>5077.0581000000002</v>
@@ -5620,7 +5620,7 @@
         <v>673</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>931</v>
+        <v>853</v>
       </c>
       <c r="J58" s="0">
         <v>728.97640000000001</v>
@@ -5652,7 +5652,7 @@
         <v>674</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>932</v>
+        <v>854</v>
       </c>
       <c r="J59" s="0">
         <v>681.9529</v>
@@ -5684,7 +5684,7 @@
         <v>675</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>933</v>
+        <v>855</v>
       </c>
       <c r="J60" s="0">
         <v>460.65499999999997</v>
@@ -5716,7 +5716,7 @@
         <v>676</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>934</v>
+        <v>856</v>
       </c>
       <c r="J61" s="0">
         <v>406.1062</v>
@@ -5748,7 +5748,7 @@
         <v>677</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>935</v>
+        <v>857</v>
       </c>
       <c r="J62" s="0">
         <v>382.6694</v>
@@ -5780,7 +5780,7 @@
         <v>678</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>936</v>
+        <v>858</v>
       </c>
       <c r="J63" s="0">
         <v>369.21839999999998</v>
@@ -5812,7 +5812,7 @@
         <v>679</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>937</v>
+        <v>859</v>
       </c>
       <c r="J64" s="0">
         <v>341.30959999999999</v>
@@ -5844,7 +5844,7 @@
         <v>680</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>938</v>
+        <v>860</v>
       </c>
       <c r="J65" s="0">
         <v>319.78870000000001</v>
@@ -5876,7 +5876,7 @@
         <v>681</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>939</v>
+        <v>861</v>
       </c>
       <c r="J66" s="0">
         <v>289.6028</v>
@@ -5908,7 +5908,7 @@
         <v>682</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>940</v>
+        <v>862</v>
       </c>
       <c r="J67" s="0">
         <v>284.9262</v>
@@ -5940,7 +5940,7 @@
         <v>683</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>941</v>
+        <v>863</v>
       </c>
       <c r="J68" s="0">
         <v>5367.4771000000001</v>
@@ -5972,7 +5972,7 @@
         <v>684</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>942</v>
+        <v>864</v>
       </c>
       <c r="J69" s="0">
         <v>3219.1161999999999</v>
@@ -6004,7 +6004,7 @@
         <v>307</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>943</v>
+        <v>865</v>
       </c>
       <c r="J70" s="0">
         <v>999.82090000000005</v>
@@ -6036,7 +6036,7 @@
         <v>308</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>944</v>
+        <v>866</v>
       </c>
       <c r="J71" s="0">
         <v>829.32470000000001</v>
@@ -6068,7 +6068,7 @@
         <v>685</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>945</v>
+        <v>867</v>
       </c>
       <c r="J72" s="0">
         <v>434.72210000000001</v>
@@ -6100,7 +6100,7 @@
         <v>686</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>946</v>
+        <v>868</v>
       </c>
       <c r="J73" s="0">
         <v>420.51510000000002</v>
@@ -6132,7 +6132,7 @@
         <v>687</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>947</v>
+        <v>869</v>
       </c>
       <c r="J74" s="0">
         <v>416.28559999999999</v>
@@ -6164,7 +6164,7 @@
         <v>688</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>948</v>
+        <v>870</v>
       </c>
       <c r="J75" s="0">
         <v>400.9085</v>
@@ -6196,7 +6196,7 @@
         <v>689</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>949</v>
+        <v>871</v>
       </c>
       <c r="J76" s="0">
         <v>360.4205</v>
@@ -6228,7 +6228,7 @@
         <v>690</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>950</v>
+        <v>872</v>
       </c>
       <c r="J77" s="0">
         <v>305.30689999999999</v>
@@ -6260,7 +6260,7 @@
         <v>691</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>951</v>
+        <v>873</v>
       </c>
       <c r="J78" s="0">
         <v>293.2808</v>
@@ -6292,7 +6292,7 @@
         <v>692</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>952</v>
+        <v>874</v>
       </c>
       <c r="J79" s="0">
         <v>247.7748</v>
@@ -6324,7 +6324,7 @@
         <v>91</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>953</v>
+        <v>390</v>
       </c>
       <c r="J80" s="0">
         <v>5813.3739999999998</v>
@@ -6356,7 +6356,7 @@
         <v>92</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>954</v>
+        <v>391</v>
       </c>
       <c r="J81" s="0">
         <v>3499.9191999999998</v>
@@ -6388,7 +6388,7 @@
         <v>93</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>955</v>
+        <v>392</v>
       </c>
       <c r="J82" s="0">
         <v>643.7663</v>
@@ -6420,7 +6420,7 @@
         <v>94</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>956</v>
+        <v>393</v>
       </c>
       <c r="J83" s="0">
         <v>507.9119</v>
@@ -6452,7 +6452,7 @@
         <v>95</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>957</v>
+        <v>394</v>
       </c>
       <c r="J84" s="0">
         <v>413.24200000000002</v>
@@ -6484,7 +6484,7 @@
         <v>96</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>958</v>
+        <v>395</v>
       </c>
       <c r="J85" s="0">
         <v>412.743</v>
@@ -6516,7 +6516,7 @@
         <v>97</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>959</v>
+        <v>396</v>
       </c>
       <c r="J86" s="0">
         <v>365.9803</v>
@@ -6548,7 +6548,7 @@
         <v>98</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>960</v>
+        <v>397</v>
       </c>
       <c r="J87" s="0">
         <v>362.68889999999999</v>
@@ -6580,7 +6580,7 @@
         <v>99</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>961</v>
+        <v>398</v>
       </c>
       <c r="J88" s="0">
         <v>337.94470000000001</v>
@@ -6612,7 +6612,7 @@
         <v>100</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>962</v>
+        <v>399</v>
       </c>
       <c r="J89" s="0">
         <v>275.04509999999999</v>
@@ -6644,7 +6644,7 @@
         <v>101</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>963</v>
+        <v>400</v>
       </c>
       <c r="J90" s="0">
         <v>253.987</v>
@@ -6676,7 +6676,7 @@
         <v>102</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>964</v>
+        <v>401</v>
       </c>
       <c r="J91" s="0">
         <v>197.0513</v>
@@ -6708,7 +6708,7 @@
         <v>103</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>965</v>
+        <v>402</v>
       </c>
       <c r="J92" s="0">
         <v>6411.3008</v>
@@ -6740,7 +6740,7 @@
         <v>104</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>966</v>
+        <v>403</v>
       </c>
       <c r="J93" s="0">
         <v>5363.7114000000001</v>
@@ -6772,7 +6772,7 @@
         <v>107</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>967</v>
+        <v>406</v>
       </c>
       <c r="J94" s="0">
         <v>465.0847</v>
@@ -6804,7 +6804,7 @@
         <v>108</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>968</v>
+        <v>407</v>
       </c>
       <c r="J95" s="0">
         <v>432.71969999999999</v>
@@ -6836,7 +6836,7 @@
         <v>109</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>969</v>
+        <v>408</v>
       </c>
       <c r="J96" s="0">
         <v>403.6884</v>
@@ -6868,7 +6868,7 @@
         <v>110</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>970</v>
+        <v>409</v>
       </c>
       <c r="J97" s="0">
         <v>393.85660000000001</v>
@@ -6900,7 +6900,7 @@
         <v>111</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>971</v>
+        <v>410</v>
       </c>
       <c r="J98" s="0">
         <v>328.83640000000003</v>
@@ -6932,7 +6932,7 @@
         <v>112</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>972</v>
+        <v>411</v>
       </c>
       <c r="J99" s="0">
         <v>289.99919999999997</v>
@@ -6964,7 +6964,7 @@
         <v>113</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>973</v>
+        <v>412</v>
       </c>
       <c r="J100" s="0">
         <v>253.50819999999999</v>
@@ -6996,7 +6996,7 @@
         <v>114</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>974</v>
+        <v>413</v>
       </c>
       <c r="J101" s="0">
         <v>156.39179999999999</v>
@@ -7028,7 +7028,7 @@
         <v>115</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>975</v>
+        <v>414</v>
       </c>
       <c r="J102" s="0">
         <v>5347.2299999999996</v>
@@ -7060,7 +7060,7 @@
         <v>117</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>976</v>
+        <v>416</v>
       </c>
       <c r="J103" s="0">
         <v>832.64940000000001</v>
@@ -7092,7 +7092,7 @@
         <v>118</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>977</v>
+        <v>417</v>
       </c>
       <c r="J104" s="0">
         <v>670.97080000000005</v>
@@ -7124,7 +7124,7 @@
         <v>119</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>978</v>
+        <v>418</v>
       </c>
       <c r="J105" s="0">
         <v>452.6379</v>
@@ -7156,7 +7156,7 @@
         <v>120</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>979</v>
+        <v>419</v>
       </c>
       <c r="J106" s="0">
         <v>432.76639999999998</v>
@@ -7188,7 +7188,7 @@
         <v>121</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>980</v>
+        <v>420</v>
       </c>
       <c r="J107" s="0">
         <v>430.21100000000001</v>
@@ -7220,7 +7220,7 @@
         <v>122</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>981</v>
+        <v>421</v>
       </c>
       <c r="J108" s="0">
         <v>426.60840000000002</v>
@@ -7252,7 +7252,7 @@
         <v>123</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>982</v>
+        <v>422</v>
       </c>
       <c r="J109" s="0">
         <v>408.17599999999999</v>
@@ -7284,7 +7284,7 @@
         <v>124</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>983</v>
+        <v>423</v>
       </c>
       <c r="J110" s="0">
         <v>393.9744</v>
@@ -7316,7 +7316,7 @@
         <v>125</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>984</v>
+        <v>424</v>
       </c>
       <c r="J111" s="0">
         <v>369.06290000000001</v>
@@ -7348,7 +7348,7 @@
         <v>126</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>985</v>
+        <v>425</v>
       </c>
       <c r="J112" s="0">
         <v>363.61939999999999</v>
@@ -7380,7 +7380,7 @@
         <v>127</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>986</v>
+        <v>426</v>
       </c>
       <c r="J113" s="0">
         <v>5889.4614000000001</v>
@@ -7412,7 +7412,7 @@
         <v>128</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>987</v>
+        <v>427</v>
       </c>
       <c r="J114" s="0">
         <v>2742.3312999999998</v>
@@ -7444,7 +7444,7 @@
         <v>129</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>988</v>
+        <v>428</v>
       </c>
       <c r="J115" s="0">
         <v>673.23270000000002</v>
@@ -7476,7 +7476,7 @@
         <v>130</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>989</v>
+        <v>429</v>
       </c>
       <c r="J116" s="0">
         <v>548.54560000000004</v>
@@ -7508,7 +7508,7 @@
         <v>131</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>990</v>
+        <v>430</v>
       </c>
       <c r="J117" s="0">
         <v>406.4975</v>
@@ -7540,7 +7540,7 @@
         <v>132</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>991</v>
+        <v>431</v>
       </c>
       <c r="J118" s="0">
         <v>370.59609999999998</v>
@@ -7572,7 +7572,7 @@
         <v>133</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>992</v>
+        <v>432</v>
       </c>
       <c r="J119" s="0">
         <v>295.41489999999999</v>
@@ -7604,7 +7604,7 @@
         <v>134</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>993</v>
+        <v>433</v>
       </c>
       <c r="J120" s="0">
         <v>294.39229999999998</v>
@@ -7636,7 +7636,7 @@
         <v>135</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>994</v>
+        <v>434</v>
       </c>
       <c r="J121" s="0">
         <v>290.21879999999999</v>
@@ -7668,7 +7668,7 @@
         <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>995</v>
+        <v>436</v>
       </c>
       <c r="J122" s="0">
         <v>241.96080000000001</v>
@@ -7700,7 +7700,7 @@
         <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>996</v>
+        <v>437</v>
       </c>
       <c r="J123" s="0">
         <v>208.0266</v>
@@ -7732,7 +7732,7 @@
         <v>140</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>997</v>
+        <v>439</v>
       </c>
       <c r="J124" s="0">
         <v>2255.5239000000001</v>
@@ -7764,7 +7764,7 @@
         <v>141</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>998</v>
+        <v>440</v>
       </c>
       <c r="J125" s="0">
         <v>784.23540000000003</v>
@@ -7796,7 +7796,7 @@
         <v>142</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>999</v>
+        <v>441</v>
       </c>
       <c r="J126" s="0">
         <v>590.41420000000005</v>
@@ -7828,7 +7828,7 @@
         <v>143</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>1000</v>
+        <v>442</v>
       </c>
       <c r="J127" s="0">
         <v>431.26760000000002</v>
@@ -7860,7 +7860,7 @@
         <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>1001</v>
+        <v>443</v>
       </c>
       <c r="J128" s="0">
         <v>372.27710000000002</v>
@@ -7892,7 +7892,7 @@
         <v>145</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>1002</v>
+        <v>444</v>
       </c>
       <c r="J129" s="0">
         <v>370.83260000000001</v>
@@ -7924,7 +7924,7 @@
         <v>146</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>1003</v>
+        <v>445</v>
       </c>
       <c r="J130" s="0">
         <v>368.27210000000002</v>
@@ -7956,7 +7956,7 @@
         <v>147</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>1004</v>
+        <v>446</v>
       </c>
       <c r="J131" s="0">
         <v>345.15750000000003</v>
@@ -7988,7 +7988,7 @@
         <v>148</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>1005</v>
+        <v>447</v>
       </c>
       <c r="J132" s="0">
         <v>335.8723</v>
@@ -8020,7 +8020,7 @@
         <v>149</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>1006</v>
+        <v>448</v>
       </c>
       <c r="J133" s="0">
         <v>309.04379999999998</v>
@@ -8052,7 +8052,7 @@
         <v>150</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>1007</v>
+        <v>449</v>
       </c>
       <c r="J134" s="0">
         <v>280.34730000000002</v>
@@ -8084,7 +8084,7 @@
         <v>151</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>1008</v>
+        <v>450</v>
       </c>
       <c r="J135" s="0">
         <v>6089.4750999999997</v>
@@ -8116,7 +8116,7 @@
         <v>152</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>1009</v>
+        <v>451</v>
       </c>
       <c r="J136" s="0">
         <v>4801.2959000000001</v>
@@ -8148,7 +8148,7 @@
         <v>153</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>1010</v>
+        <v>452</v>
       </c>
       <c r="J137" s="0">
         <v>729.38409999999999</v>
@@ -8180,7 +8180,7 @@
         <v>155</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>1011</v>
+        <v>454</v>
       </c>
       <c r="J138" s="0">
         <v>414.8329</v>
@@ -8212,7 +8212,7 @@
         <v>156</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>1012</v>
+        <v>455</v>
       </c>
       <c r="J139" s="0">
         <v>407.11009999999999</v>
@@ -8244,7 +8244,7 @@
         <v>157</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>1013</v>
+        <v>456</v>
       </c>
       <c r="J140" s="0">
         <v>390.21910000000003</v>
@@ -8276,7 +8276,7 @@
         <v>158</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>1014</v>
+        <v>457</v>
       </c>
       <c r="J141" s="0">
         <v>362.1839</v>
@@ -8308,7 +8308,7 @@
         <v>159</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>1015</v>
+        <v>458</v>
       </c>
       <c r="J142" s="0">
         <v>349.2903</v>
@@ -8340,7 +8340,7 @@
         <v>160</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>1016</v>
+        <v>459</v>
       </c>
       <c r="J143" s="0">
         <v>339.61919999999998</v>
@@ -8372,7 +8372,7 @@
         <v>161</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>1017</v>
+        <v>460</v>
       </c>
       <c r="J144" s="0">
         <v>321.077</v>
@@ -8404,7 +8404,7 @@
         <v>162</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>1018</v>
+        <v>461</v>
       </c>
       <c r="J145" s="0">
         <v>320.34030000000001</v>
@@ -8436,7 +8436,7 @@
         <v>163</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>1019</v>
+        <v>462</v>
       </c>
       <c r="J146" s="0">
         <v>4900.8388999999997</v>
@@ -8468,7 +8468,7 @@
         <v>164</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>1020</v>
+        <v>463</v>
       </c>
       <c r="J147" s="0">
         <v>2991.1887000000002</v>
@@ -8500,7 +8500,7 @@
         <v>165</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>1021</v>
+        <v>464</v>
       </c>
       <c r="J148" s="0">
         <v>694.42499999999996</v>
@@ -8532,7 +8532,7 @@
         <v>166</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>1022</v>
+        <v>465</v>
       </c>
       <c r="J149" s="0">
         <v>590.76210000000003</v>
@@ -8564,7 +8564,7 @@
         <v>167</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>1023</v>
+        <v>466</v>
       </c>
       <c r="J150" s="0">
         <v>434.02370000000002</v>
@@ -8596,7 +8596,7 @@
         <v>168</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>1024</v>
+        <v>467</v>
       </c>
       <c r="J151" s="0">
         <v>417.05189999999999</v>
@@ -8628,7 +8628,7 @@
         <v>169</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>1025</v>
+        <v>468</v>
       </c>
       <c r="J152" s="0">
         <v>407.86430000000001</v>
@@ -8660,7 +8660,7 @@
         <v>170</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>1026</v>
+        <v>469</v>
       </c>
       <c r="J153" s="0">
         <v>406.37779999999998</v>
@@ -8692,7 +8692,7 @@
         <v>171</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>1027</v>
+        <v>470</v>
       </c>
       <c r="J154" s="0">
         <v>379.51209999999998</v>
@@ -8724,7 +8724,7 @@
         <v>172</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>1028</v>
+        <v>471</v>
       </c>
       <c r="J155" s="0">
         <v>361.57029999999998</v>
@@ -8756,7 +8756,7 @@
         <v>173</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>1029</v>
+        <v>472</v>
       </c>
       <c r="J156" s="0">
         <v>324.36189999999999</v>
@@ -8788,7 +8788,7 @@
         <v>176</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>1030</v>
+        <v>475</v>
       </c>
       <c r="J157" s="0">
         <v>2639.6545000000001</v>
@@ -8820,7 +8820,7 @@
         <v>177</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>1031</v>
+        <v>476</v>
       </c>
       <c r="J158" s="0">
         <v>538.57830000000001</v>
@@ -8852,7 +8852,7 @@
         <v>178</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>1032</v>
+        <v>477</v>
       </c>
       <c r="J159" s="0">
         <v>439.68729999999999</v>
@@ -8884,7 +8884,7 @@
         <v>180</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>1033</v>
+        <v>479</v>
       </c>
       <c r="J160" s="0">
         <v>348.95269999999999</v>
@@ -8916,7 +8916,7 @@
         <v>181</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>1034</v>
+        <v>480</v>
       </c>
       <c r="J161" s="0">
         <v>320.45060000000001</v>
@@ -8948,7 +8948,7 @@
         <v>182</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>1035</v>
+        <v>481</v>
       </c>
       <c r="J162" s="0">
         <v>306.95499999999999</v>
@@ -8980,7 +8980,7 @@
         <v>183</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>1036</v>
+        <v>482</v>
       </c>
       <c r="J163" s="0">
         <v>286.13639999999998</v>
@@ -9012,7 +9012,7 @@
         <v>184</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>1037</v>
+        <v>483</v>
       </c>
       <c r="J164" s="0">
         <v>270.46800000000002</v>
@@ -9044,7 +9044,7 @@
         <v>185</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>1038</v>
+        <v>484</v>
       </c>
       <c r="J165" s="0">
         <v>266.42959999999999</v>
@@ -9076,7 +9076,7 @@
         <v>186</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>1039</v>
+        <v>485</v>
       </c>
       <c r="J166" s="0">
         <v>198.7653</v>
@@ -9108,7 +9108,7 @@
         <v>187</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>1040</v>
+        <v>486</v>
       </c>
       <c r="J167" s="0">
         <v>6949.5127000000002</v>
@@ -9140,7 +9140,7 @@
         <v>188</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>1041</v>
+        <v>487</v>
       </c>
       <c r="J168" s="0">
         <v>1918.3168000000001</v>
@@ -9172,7 +9172,7 @@
         <v>189</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>1042</v>
+        <v>488</v>
       </c>
       <c r="J169" s="0">
         <v>842.53420000000006</v>
@@ -9204,7 +9204,7 @@
         <v>190</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>1043</v>
+        <v>489</v>
       </c>
       <c r="J170" s="0">
         <v>625.51949999999999</v>
@@ -9236,7 +9236,7 @@
         <v>191</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>1044</v>
+        <v>490</v>
       </c>
       <c r="J171" s="0">
         <v>403.39569999999998</v>
@@ -9268,7 +9268,7 @@
         <v>192</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>1045</v>
+        <v>491</v>
       </c>
       <c r="J172" s="0">
         <v>401.83440000000002</v>
@@ -9300,7 +9300,7 @@
         <v>193</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>1046</v>
+        <v>492</v>
       </c>
       <c r="J173" s="0">
         <v>401.53390000000002</v>
@@ -9332,7 +9332,7 @@
         <v>194</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>1047</v>
+        <v>493</v>
       </c>
       <c r="J174" s="0">
         <v>325.73790000000002</v>
@@ -9364,7 +9364,7 @@
         <v>195</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>1048</v>
+        <v>494</v>
       </c>
       <c r="J175" s="0">
         <v>306.47129999999999</v>
@@ -9396,7 +9396,7 @@
         <v>196</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>1049</v>
+        <v>495</v>
       </c>
       <c r="J176" s="0">
         <v>297.54129999999998</v>
@@ -9428,7 +9428,7 @@
         <v>197</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>1050</v>
+        <v>496</v>
       </c>
       <c r="J177" s="0">
         <v>251.23050000000001</v>
@@ -9460,7 +9460,7 @@
         <v>198</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>1051</v>
+        <v>497</v>
       </c>
       <c r="J178" s="0">
         <v>104.34829999999999</v>
@@ -9492,7 +9492,7 @@
         <v>199</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>1052</v>
+        <v>498</v>
       </c>
       <c r="J179" s="0">
         <v>5196.1244999999999</v>
@@ -9524,7 +9524,7 @@
         <v>201</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>1053</v>
+        <v>500</v>
       </c>
       <c r="J180" s="0">
         <v>554.0693</v>
@@ -9556,7 +9556,7 @@
         <v>202</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>1054</v>
+        <v>501</v>
       </c>
       <c r="J181" s="0">
         <v>97.465900000000005</v>
@@ -9588,7 +9588,7 @@
         <v>203</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>1055</v>
+        <v>502</v>
       </c>
       <c r="J182" s="0">
         <v>413.24349999999998</v>
@@ -9620,7 +9620,7 @@
         <v>204</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>1056</v>
+        <v>503</v>
       </c>
       <c r="J183" s="0">
         <v>390.69720000000001</v>
@@ -9652,7 +9652,7 @@
         <v>205</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>1057</v>
+        <v>504</v>
       </c>
       <c r="J184" s="0">
         <v>384.44110000000001</v>
@@ -9684,7 +9684,7 @@
         <v>206</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>1058</v>
+        <v>505</v>
       </c>
       <c r="J185" s="0">
         <v>369.39760000000001</v>
@@ -9716,7 +9716,7 @@
         <v>207</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>1059</v>
+        <v>506</v>
       </c>
       <c r="J186" s="0">
         <v>355.85449999999997</v>
@@ -9748,7 +9748,7 @@
         <v>208</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>1060</v>
+        <v>507</v>
       </c>
       <c r="J187" s="0">
         <v>332.20139999999998</v>
@@ -9780,7 +9780,7 @@
         <v>209</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>1061</v>
+        <v>508</v>
       </c>
       <c r="J188" s="0">
         <v>304.4751</v>
@@ -9812,7 +9812,7 @@
         <v>210</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>1062</v>
+        <v>509</v>
       </c>
       <c r="J189" s="0">
         <v>263.24160000000001</v>
@@ -9844,7 +9844,7 @@
         <v>211</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>1063</v>
+        <v>510</v>
       </c>
       <c r="J190" s="0">
         <v>5598.6216000000004</v>
@@ -9876,7 +9876,7 @@
         <v>212</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>1064</v>
+        <v>511</v>
       </c>
       <c r="J191" s="0">
         <v>4298.6826000000001</v>
@@ -9908,7 +9908,7 @@
         <v>213</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>1065</v>
+        <v>512</v>
       </c>
       <c r="J192" s="0">
         <v>831.18269999999996</v>
@@ -9940,7 +9940,7 @@
         <v>214</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>1066</v>
+        <v>513</v>
       </c>
       <c r="J193" s="0">
         <v>746.42259999999999</v>
@@ -9972,7 +9972,7 @@
         <v>215</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>1067</v>
+        <v>514</v>
       </c>
       <c r="J194" s="0">
         <v>477.65440000000001</v>
@@ -10004,7 +10004,7 @@
         <v>216</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>1068</v>
+        <v>515</v>
       </c>
       <c r="J195" s="0">
         <v>455.09550000000002</v>
@@ -10036,7 +10036,7 @@
         <v>217</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>1069</v>
+        <v>516</v>
       </c>
       <c r="J196" s="0">
         <v>442.9828</v>
@@ -10068,7 +10068,7 @@
         <v>218</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>1070</v>
+        <v>517</v>
       </c>
       <c r="J197" s="0">
         <v>403.95710000000003</v>
@@ -10100,7 +10100,7 @@
         <v>219</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>1071</v>
+        <v>518</v>
       </c>
       <c r="J198" s="0">
         <v>353.99869999999999</v>
@@ -10132,7 +10132,7 @@
         <v>220</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>1072</v>
+        <v>519</v>
       </c>
       <c r="J199" s="0">
         <v>282.62110000000001</v>
@@ -10164,7 +10164,7 @@
         <v>221</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>1073</v>
+        <v>520</v>
       </c>
       <c r="J200" s="0">
         <v>251.0352</v>
@@ -10196,7 +10196,7 @@
         <v>222</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>1074</v>
+        <v>521</v>
       </c>
       <c r="J201" s="0">
         <v>226.5855</v>
@@ -10228,7 +10228,7 @@
         <v>223</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>1075</v>
+        <v>522</v>
       </c>
       <c r="J202" s="0">
         <v>3073.4854</v>
@@ -10260,7 +10260,7 @@
         <v>224</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>1076</v>
+        <v>523</v>
       </c>
       <c r="J203" s="0">
         <v>1817.3022000000001</v>
@@ -10292,7 +10292,7 @@
         <v>213</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>1077</v>
+        <v>524</v>
       </c>
       <c r="J204" s="0">
         <v>831.18269999999996</v>
@@ -10324,7 +10324,7 @@
         <v>225</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>1078</v>
+        <v>526</v>
       </c>
       <c r="J205" s="0">
         <v>444.28719999999999</v>
@@ -10356,7 +10356,7 @@
         <v>226</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>1079</v>
+        <v>527</v>
       </c>
       <c r="J206" s="0">
         <v>406.01569999999998</v>
@@ -10388,7 +10388,7 @@
         <v>227</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>1080</v>
+        <v>528</v>
       </c>
       <c r="J207" s="0">
         <v>377.0512</v>
@@ -10420,7 +10420,7 @@
         <v>228</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>1081</v>
+        <v>529</v>
       </c>
       <c r="J208" s="0">
         <v>370.54059999999998</v>
@@ -10452,7 +10452,7 @@
         <v>229</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>1082</v>
+        <v>530</v>
       </c>
       <c r="J209" s="0">
         <v>364.45699999999999</v>
@@ -10484,7 +10484,7 @@
         <v>230</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>1083</v>
+        <v>531</v>
       </c>
       <c r="J210" s="0">
         <v>357.5231</v>
@@ -10516,7 +10516,7 @@
         <v>231</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>1084</v>
+        <v>532</v>
       </c>
       <c r="J211" s="0">
         <v>289.80360000000002</v>
@@ -10548,7 +10548,7 @@
         <v>232</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>1085</v>
+        <v>533</v>
       </c>
       <c r="J212" s="0">
         <v>205.23990000000001</v>
@@ -10580,7 +10580,7 @@
         <v>233</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>1086</v>
+        <v>534</v>
       </c>
       <c r="J213" s="0">
         <v>5904.6377000000002</v>
@@ -10612,7 +10612,7 @@
         <v>234</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>1087</v>
+        <v>535</v>
       </c>
       <c r="J214" s="0">
         <v>4907.7012000000004</v>
@@ -10644,7 +10644,7 @@
         <v>235</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>1088</v>
+        <v>536</v>
       </c>
       <c r="J215" s="0">
         <v>202.81960000000001</v>
@@ -10676,7 +10676,7 @@
         <v>237</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>1089</v>
+        <v>538</v>
       </c>
       <c r="J216" s="0">
         <v>383.23849999999999</v>
@@ -10708,7 +10708,7 @@
         <v>238</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>1090</v>
+        <v>539</v>
       </c>
       <c r="J217" s="0">
         <v>363.8911</v>
@@ -10740,7 +10740,7 @@
         <v>239</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>1091</v>
+        <v>540</v>
       </c>
       <c r="J218" s="0">
         <v>355.88670000000002</v>
@@ -10772,7 +10772,7 @@
         <v>240</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>1092</v>
+        <v>541</v>
       </c>
       <c r="J219" s="0">
         <v>351.3347</v>
@@ -10804,7 +10804,7 @@
         <v>241</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>1093</v>
+        <v>542</v>
       </c>
       <c r="J220" s="0">
         <v>333.8578</v>
@@ -10836,7 +10836,7 @@
         <v>242</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>1094</v>
+        <v>543</v>
       </c>
       <c r="J221" s="0">
         <v>313.44380000000001</v>
@@ -10868,7 +10868,7 @@
         <v>243</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>1095</v>
+        <v>544</v>
       </c>
       <c r="J222" s="0">
         <v>238.27189999999999</v>
@@ -10900,7 +10900,7 @@
         <v>244</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>1096</v>
+        <v>545</v>
       </c>
       <c r="J223" s="0">
         <v>141.53020000000001</v>
@@ -10932,7 +10932,7 @@
         <v>245</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>1097</v>
+        <v>546</v>
       </c>
       <c r="J224" s="0">
         <v>6671.5464000000002</v>
@@ -10964,7 +10964,7 @@
         <v>246</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>1098</v>
+        <v>547</v>
       </c>
       <c r="J225" s="0">
         <v>2604.8850000000002</v>
@@ -10996,7 +10996,7 @@
         <v>248</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>1099</v>
+        <v>549</v>
       </c>
       <c r="J226" s="0">
         <v>539.66269999999997</v>
@@ -11028,7 +11028,7 @@
         <v>250</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>1100</v>
+        <v>551</v>
       </c>
       <c r="J227" s="0">
         <v>429.82010000000002</v>
@@ -11060,7 +11060,7 @@
         <v>251</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>1101</v>
+        <v>552</v>
       </c>
       <c r="J228" s="0">
         <v>421.38249999999999</v>
@@ -11092,7 +11092,7 @@
         <v>252</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>1102</v>
+        <v>553</v>
       </c>
       <c r="J229" s="0">
         <v>417.74880000000002</v>
@@ -11124,7 +11124,7 @@
         <v>253</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>1103</v>
+        <v>554</v>
       </c>
       <c r="J230" s="0">
         <v>393.11059999999998</v>
@@ -11156,7 +11156,7 @@
         <v>254</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>1104</v>
+        <v>555</v>
       </c>
       <c r="J231" s="0">
         <v>392.10489999999999</v>
@@ -11188,7 +11188,7 @@
         <v>255</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>1105</v>
+        <v>556</v>
       </c>
       <c r="J232" s="0">
         <v>387.5043</v>
@@ -11220,7 +11220,7 @@
         <v>256</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>1106</v>
+        <v>557</v>
       </c>
       <c r="J233" s="0">
         <v>215.23259999999999</v>
@@ -11252,7 +11252,7 @@
         <v>693</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>1107</v>
+        <v>804</v>
       </c>
       <c r="J234" s="0">
         <v>6179.7012000000004</v>
@@ -11284,7 +11284,7 @@
         <v>694</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>1108</v>
+        <v>805</v>
       </c>
       <c r="J235" s="0">
         <v>2590.0304999999999</v>
@@ -11316,7 +11316,7 @@
         <v>695</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>1109</v>
+        <v>806</v>
       </c>
       <c r="J236" s="0">
         <v>1052.7577000000001</v>
@@ -11348,7 +11348,7 @@
         <v>696</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>1110</v>
+        <v>807</v>
       </c>
       <c r="J237" s="0">
         <v>663.33749999999998</v>
@@ -11380,7 +11380,7 @@
         <v>697</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>1111</v>
+        <v>808</v>
       </c>
       <c r="J238" s="0">
         <v>506.81569999999999</v>
@@ -11412,7 +11412,7 @@
         <v>698</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>1112</v>
+        <v>809</v>
       </c>
       <c r="J239" s="0">
         <v>408.8279</v>
@@ -11444,7 +11444,7 @@
         <v>699</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>1113</v>
+        <v>810</v>
       </c>
       <c r="J240" s="0">
         <v>402.4606</v>
@@ -11476,7 +11476,7 @@
         <v>700</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>1114</v>
+        <v>811</v>
       </c>
       <c r="J241" s="0">
         <v>395.95499999999999</v>
@@ -11508,7 +11508,7 @@
         <v>701</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>1115</v>
+        <v>812</v>
       </c>
       <c r="J242" s="0">
         <v>384.18630000000002</v>
@@ -11540,7 +11540,7 @@
         <v>702</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>1116</v>
+        <v>813</v>
       </c>
       <c r="J243" s="0">
         <v>337.53550000000001</v>
@@ -11572,7 +11572,7 @@
         <v>703</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>1117</v>
+        <v>814</v>
       </c>
       <c r="J244" s="0">
         <v>304.91230000000002</v>
@@ -11604,7 +11604,7 @@
         <v>704</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>1118</v>
+        <v>815</v>
       </c>
       <c r="J245" s="0">
         <v>125.54000000000001</v>
@@ -11636,7 +11636,7 @@
         <v>705</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>1119</v>
+        <v>816</v>
       </c>
       <c r="J246" s="0">
         <v>5385.1138000000001</v>
@@ -11668,7 +11668,7 @@
         <v>706</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>1120</v>
+        <v>817</v>
       </c>
       <c r="J247" s="0">
         <v>2843.9126000000001</v>
@@ -11700,7 +11700,7 @@
         <v>707</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>1121</v>
+        <v>818</v>
       </c>
       <c r="J248" s="0">
         <v>710.74549999999999</v>
@@ -11732,7 +11732,7 @@
         <v>708</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>1122</v>
+        <v>819</v>
       </c>
       <c r="J249" s="0">
         <v>550.2423</v>
@@ -11764,7 +11764,7 @@
         <v>709</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>1123</v>
+        <v>820</v>
       </c>
       <c r="J250" s="0">
         <v>438.92590000000001</v>
@@ -11796,7 +11796,7 @@
         <v>710</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>1124</v>
+        <v>821</v>
       </c>
       <c r="J251" s="0">
         <v>423.42290000000003</v>
@@ -11828,7 +11828,7 @@
         <v>711</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>1125</v>
+        <v>822</v>
       </c>
       <c r="J252" s="0">
         <v>403.89089999999999</v>
@@ -11860,7 +11860,7 @@
         <v>712</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>1126</v>
+        <v>823</v>
       </c>
       <c r="J253" s="0">
         <v>391.21699999999999</v>
@@ -11892,7 +11892,7 @@
         <v>713</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>1127</v>
+        <v>824</v>
       </c>
       <c r="J254" s="0">
         <v>383.9436</v>
@@ -11924,7 +11924,7 @@
         <v>714</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>1128</v>
+        <v>825</v>
       </c>
       <c r="J255" s="0">
         <v>312.447</v>
@@ -11956,7 +11956,7 @@
         <v>715</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>1129</v>
+        <v>826</v>
       </c>
       <c r="J256" s="0">
         <v>309.3852</v>
@@ -11988,7 +11988,7 @@
         <v>716</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>1130</v>
+        <v>827</v>
       </c>
       <c r="J257" s="0">
         <v>235.6891</v>
@@ -12020,7 +12020,7 @@
         <v>717</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>1131</v>
+        <v>828</v>
       </c>
       <c r="J258" s="0">
         <v>6293.9867999999997</v>
@@ -12052,7 +12052,7 @@
         <v>718</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>1132</v>
+        <v>829</v>
       </c>
       <c r="J259" s="0">
         <v>5358.5902999999999</v>
@@ -12084,7 +12084,7 @@
         <v>719</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>1133</v>
+        <v>830</v>
       </c>
       <c r="J260" s="0">
         <v>577.04179999999997</v>
@@ -12116,7 +12116,7 @@
         <v>720</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>1134</v>
+        <v>831</v>
       </c>
       <c r="J261" s="0">
         <v>518.29719999999998</v>
@@ -12148,7 +12148,7 @@
         <v>721</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>1135</v>
+        <v>832</v>
       </c>
       <c r="J262" s="0">
         <v>427.73379999999997</v>
@@ -12180,7 +12180,7 @@
         <v>722</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>1136</v>
+        <v>833</v>
       </c>
       <c r="J263" s="0">
         <v>404.26459999999997</v>
@@ -12212,7 +12212,7 @@
         <v>723</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>1137</v>
+        <v>834</v>
       </c>
       <c r="J264" s="0">
         <v>398.51589999999999</v>
@@ -12244,7 +12244,7 @@
         <v>724</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>1138</v>
+        <v>835</v>
       </c>
       <c r="J265" s="0">
         <v>392.9486</v>
@@ -12276,7 +12276,7 @@
         <v>725</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>1139</v>
+        <v>836</v>
       </c>
       <c r="J266" s="0">
         <v>382.86340000000001</v>
@@ -12308,7 +12308,7 @@
         <v>726</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>1140</v>
+        <v>837</v>
       </c>
       <c r="J267" s="0">
         <v>368.97640000000001</v>
@@ -12340,7 +12340,7 @@
         <v>727</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>1141</v>
+        <v>838</v>
       </c>
       <c r="J268" s="0">
         <v>347.17689999999999</v>
@@ -12372,7 +12372,7 @@
         <v>728</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>1142</v>
+        <v>839</v>
       </c>
       <c r="J269" s="0">
         <v>328.54599999999999</v>
@@ -12404,7 +12404,7 @@
         <v>257</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>1143</v>
+        <v>558</v>
       </c>
       <c r="J270" s="0">
         <v>5568.125</v>
@@ -12436,7 +12436,7 @@
         <v>258</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>1144</v>
+        <v>559</v>
       </c>
       <c r="J271" s="0">
         <v>2316.6012999999998</v>
@@ -12468,7 +12468,7 @@
         <v>259</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>1145</v>
+        <v>560</v>
       </c>
       <c r="J272" s="0">
         <v>504.78460000000001</v>
@@ -12500,7 +12500,7 @@
         <v>260</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>1146</v>
+        <v>561</v>
       </c>
       <c r="J273" s="0">
         <v>445.50999999999999</v>
@@ -12532,7 +12532,7 @@
         <v>261</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>1147</v>
+        <v>562</v>
       </c>
       <c r="J274" s="0">
         <v>401.56920000000002</v>
@@ -12564,7 +12564,7 @@
         <v>262</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>1148</v>
+        <v>563</v>
       </c>
       <c r="J275" s="0">
         <v>392.42399999999998</v>
@@ -12596,7 +12596,7 @@
         <v>263</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>1149</v>
+        <v>564</v>
       </c>
       <c r="J276" s="0">
         <v>368.18880000000001</v>
@@ -12628,7 +12628,7 @@
         <v>264</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>1150</v>
+        <v>565</v>
       </c>
       <c r="J277" s="0">
         <v>366.78320000000002</v>
@@ -12660,7 +12660,7 @@
         <v>265</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>1151</v>
+        <v>566</v>
       </c>
       <c r="J278" s="0">
         <v>361.8997</v>
@@ -12692,7 +12692,7 @@
         <v>266</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>1152</v>
+        <v>567</v>
       </c>
       <c r="J279" s="0">
         <v>322.42989999999998</v>
@@ -12724,7 +12724,7 @@
         <v>267</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>1153</v>
+        <v>568</v>
       </c>
       <c r="J280" s="0">
         <v>308.6019</v>
@@ -12756,7 +12756,7 @@
         <v>268</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>1154</v>
+        <v>569</v>
       </c>
       <c r="J281" s="0">
         <v>260.48289999999997</v>
@@ -12788,7 +12788,7 @@
         <v>103</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>1155</v>
+        <v>570</v>
       </c>
       <c r="J282" s="0">
         <v>6411.3008</v>
@@ -12820,7 +12820,7 @@
         <v>104</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>1156</v>
+        <v>571</v>
       </c>
       <c r="J283" s="0">
         <v>5363.7114000000001</v>
@@ -12852,7 +12852,7 @@
         <v>107</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>1157</v>
+        <v>574</v>
       </c>
       <c r="J284" s="0">
         <v>465.0847</v>
@@ -12884,7 +12884,7 @@
         <v>108</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>1158</v>
+        <v>575</v>
       </c>
       <c r="J285" s="0">
         <v>432.71969999999999</v>
@@ -12916,7 +12916,7 @@
         <v>109</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>1159</v>
+        <v>576</v>
       </c>
       <c r="J286" s="0">
         <v>403.6884</v>
@@ -12948,7 +12948,7 @@
         <v>110</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>1160</v>
+        <v>577</v>
       </c>
       <c r="J287" s="0">
         <v>393.85660000000001</v>
@@ -12980,7 +12980,7 @@
         <v>111</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>1161</v>
+        <v>578</v>
       </c>
       <c r="J288" s="0">
         <v>328.83640000000003</v>
@@ -13012,7 +13012,7 @@
         <v>112</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>1162</v>
+        <v>579</v>
       </c>
       <c r="J289" s="0">
         <v>289.99919999999997</v>
@@ -13044,7 +13044,7 @@
         <v>113</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>1163</v>
+        <v>580</v>
       </c>
       <c r="J290" s="0">
         <v>253.50819999999999</v>
@@ -13076,7 +13076,7 @@
         <v>114</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>1164</v>
+        <v>581</v>
       </c>
       <c r="J291" s="0">
         <v>156.39179999999999</v>
@@ -13108,7 +13108,7 @@
         <v>269</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>1165</v>
+        <v>582</v>
       </c>
       <c r="J292" s="0">
         <v>5610.5132000000003</v>
@@ -13140,7 +13140,7 @@
         <v>270</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>1166</v>
+        <v>583</v>
       </c>
       <c r="J293" s="0">
         <v>2526.6718999999998</v>
@@ -13172,7 +13172,7 @@
         <v>271</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>1167</v>
+        <v>584</v>
       </c>
       <c r="J294" s="0">
         <v>663.2672</v>
@@ -13204,7 +13204,7 @@
         <v>272</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>1168</v>
+        <v>585</v>
       </c>
       <c r="J295" s="0">
         <v>553.69179999999994</v>
@@ -13236,7 +13236,7 @@
         <v>273</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>1169</v>
+        <v>586</v>
       </c>
       <c r="J296" s="0">
         <v>436.38159999999999</v>
@@ -13268,7 +13268,7 @@
         <v>274</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>1170</v>
+        <v>587</v>
       </c>
       <c r="J297" s="0">
         <v>411.78269999999998</v>
@@ -13300,7 +13300,7 @@
         <v>275</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>1171</v>
+        <v>588</v>
       </c>
       <c r="J298" s="0">
         <v>407.44670000000002</v>
@@ -13332,7 +13332,7 @@
         <v>276</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>1172</v>
+        <v>589</v>
       </c>
       <c r="J299" s="0">
         <v>390.17970000000003</v>
@@ -13364,7 +13364,7 @@
         <v>277</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>1173</v>
+        <v>590</v>
       </c>
       <c r="J300" s="0">
         <v>379.34300000000002</v>
@@ -13396,7 +13396,7 @@
         <v>278</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>1174</v>
+        <v>591</v>
       </c>
       <c r="J301" s="0">
         <v>378.32549999999998</v>
@@ -13428,7 +13428,7 @@
         <v>279</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>1175</v>
+        <v>592</v>
       </c>
       <c r="J302" s="0">
         <v>248.1077</v>
@@ -13460,7 +13460,7 @@
         <v>280</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>1176</v>
+        <v>593</v>
       </c>
       <c r="J303" s="0">
         <v>155.72280000000001</v>
@@ -13492,7 +13492,7 @@
         <v>281</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>1177</v>
+        <v>594</v>
       </c>
       <c r="J304" s="0">
         <v>6378.5679</v>
@@ -13524,7 +13524,7 @@
         <v>282</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>1178</v>
+        <v>595</v>
       </c>
       <c r="J305" s="0">
         <v>3677.8054000000002</v>
@@ -13556,7 +13556,7 @@
         <v>283</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>1179</v>
+        <v>596</v>
       </c>
       <c r="J306" s="0">
         <v>990.75639999999999</v>
@@ -13588,7 +13588,7 @@
         <v>284</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>1180</v>
+        <v>597</v>
       </c>
       <c r="J307" s="0">
         <v>912.61609999999996</v>
@@ -13620,7 +13620,7 @@
         <v>285</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>1181</v>
+        <v>598</v>
       </c>
       <c r="J308" s="0">
         <v>448.30200000000002</v>
@@ -13652,7 +13652,7 @@
         <v>286</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>1182</v>
+        <v>599</v>
       </c>
       <c r="J309" s="0">
         <v>415.84109999999998</v>
@@ -13684,7 +13684,7 @@
         <v>287</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>1183</v>
+        <v>600</v>
       </c>
       <c r="J310" s="0">
         <v>380.94420000000002</v>
@@ -13716,7 +13716,7 @@
         <v>288</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>1184</v>
+        <v>601</v>
       </c>
       <c r="J311" s="0">
         <v>359.60860000000002</v>
@@ -13748,7 +13748,7 @@
         <v>289</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>1185</v>
+        <v>602</v>
       </c>
       <c r="J312" s="0">
         <v>338.8168</v>
@@ -13780,7 +13780,7 @@
         <v>290</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>1186</v>
+        <v>603</v>
       </c>
       <c r="J313" s="0">
         <v>320.63470000000001</v>
@@ -13812,7 +13812,7 @@
         <v>291</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>1187</v>
+        <v>604</v>
       </c>
       <c r="J314" s="0">
         <v>287.04489999999999</v>
@@ -13844,7 +13844,7 @@
         <v>292</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>1188</v>
+        <v>605</v>
       </c>
       <c r="J315" s="0">
         <v>107.8788</v>
@@ -13876,7 +13876,7 @@
         <v>293</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>1189</v>
+        <v>606</v>
       </c>
       <c r="J316" s="0">
         <v>5099.2568000000001</v>
@@ -13908,7 +13908,7 @@
         <v>294</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>1190</v>
+        <v>607</v>
       </c>
       <c r="J317" s="0">
         <v>2383.1239999999998</v>
@@ -13940,7 +13940,7 @@
         <v>295</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>1191</v>
+        <v>608</v>
       </c>
       <c r="J318" s="0">
         <v>670.93709999999999</v>
@@ -13972,7 +13972,7 @@
         <v>296</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>1192</v>
+        <v>609</v>
       </c>
       <c r="J319" s="0">
         <v>459.24430000000001</v>
@@ -14004,7 +14004,7 @@
         <v>297</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>1193</v>
+        <v>610</v>
       </c>
       <c r="J320" s="0">
         <v>415.84710000000001</v>
@@ -14036,7 +14036,7 @@
         <v>298</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>1194</v>
+        <v>611</v>
       </c>
       <c r="J321" s="0">
         <v>404.09039999999999</v>
@@ -14068,7 +14068,7 @@
         <v>299</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>1195</v>
+        <v>612</v>
       </c>
       <c r="J322" s="0">
         <v>370.1207</v>
@@ -14100,7 +14100,7 @@
         <v>300</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>1196</v>
+        <v>613</v>
       </c>
       <c r="J323" s="0">
         <v>369.87549999999999</v>
@@ -14132,7 +14132,7 @@
         <v>301</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>1197</v>
+        <v>614</v>
       </c>
       <c r="J324" s="0">
         <v>332.15789999999998</v>
@@ -14164,7 +14164,7 @@
         <v>302</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>1198</v>
+        <v>615</v>
       </c>
       <c r="J325" s="0">
         <v>310.02600000000001</v>
@@ -14196,7 +14196,7 @@
         <v>303</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>1199</v>
+        <v>616</v>
       </c>
       <c r="J326" s="0">
         <v>137.19120000000001</v>
@@ -14228,7 +14228,7 @@
         <v>305</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>1200</v>
+        <v>618</v>
       </c>
       <c r="J327" s="0">
         <v>6147.9931999999999</v>
@@ -14260,7 +14260,7 @@
         <v>306</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>1201</v>
+        <v>619</v>
       </c>
       <c r="J328" s="0">
         <v>4509.7578000000003</v>
@@ -14292,7 +14292,7 @@
         <v>307</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>1202</v>
+        <v>620</v>
       </c>
       <c r="J329" s="0">
         <v>999.82090000000005</v>
@@ -14324,7 +14324,7 @@
         <v>308</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>1203</v>
+        <v>621</v>
       </c>
       <c r="J330" s="0">
         <v>829.32470000000001</v>
@@ -14356,7 +14356,7 @@
         <v>309</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>1204</v>
+        <v>622</v>
       </c>
       <c r="J331" s="0">
         <v>460.868</v>
@@ -14388,7 +14388,7 @@
         <v>310</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>1205</v>
+        <v>623</v>
       </c>
       <c r="J332" s="0">
         <v>418.91930000000002</v>
@@ -14420,7 +14420,7 @@
         <v>311</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>1206</v>
+        <v>624</v>
       </c>
       <c r="J333" s="0">
         <v>377.29809999999998</v>
@@ -14452,7 +14452,7 @@
         <v>312</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>1207</v>
+        <v>625</v>
       </c>
       <c r="J334" s="0">
         <v>376.07799999999998</v>
@@ -14484,7 +14484,7 @@
         <v>313</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>1208</v>
+        <v>626</v>
       </c>
       <c r="J335" s="0">
         <v>345.4522</v>
@@ -14516,7 +14516,7 @@
         <v>314</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>1209</v>
+        <v>627</v>
       </c>
       <c r="J336" s="0">
         <v>333.1805</v>
@@ -14548,7 +14548,7 @@
         <v>315</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>1210</v>
+        <v>628</v>
       </c>
       <c r="J337" s="0">
         <v>297.38940000000002</v>
@@ -14580,7 +14580,7 @@
         <v>316</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>1211</v>
+        <v>629</v>
       </c>
       <c r="J338" s="0">
         <v>196.88849999999999</v>
@@ -14612,7 +14612,7 @@
         <v>317</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>1212</v>
+        <v>630</v>
       </c>
       <c r="J339" s="0">
         <v>5372.8154000000004</v>
@@ -14644,7 +14644,7 @@
         <v>318</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>1213</v>
+        <v>631</v>
       </c>
       <c r="J340" s="0">
         <v>5089.0283</v>
@@ -14676,7 +14676,7 @@
         <v>321</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>1214</v>
+        <v>634</v>
       </c>
       <c r="J341" s="0">
         <v>414.66230000000002</v>
@@ -14708,7 +14708,7 @@
         <v>322</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>1215</v>
+        <v>635</v>
       </c>
       <c r="J342" s="0">
         <v>403.9067</v>
@@ -14740,7 +14740,7 @@
         <v>323</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>1216</v>
+        <v>636</v>
       </c>
       <c r="J343" s="0">
         <v>374.75290000000001</v>
@@ -14772,7 +14772,7 @@
         <v>324</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>1217</v>
+        <v>637</v>
       </c>
       <c r="J344" s="0">
         <v>372.04629999999997</v>
@@ -14804,7 +14804,7 @@
         <v>325</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>1218</v>
+        <v>638</v>
       </c>
       <c r="J345" s="0">
         <v>372.0009</v>
@@ -14836,7 +14836,7 @@
         <v>326</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>1219</v>
+        <v>639</v>
       </c>
       <c r="J346" s="0">
         <v>318.33179999999999</v>
@@ -14868,7 +14868,7 @@
         <v>327</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>1220</v>
+        <v>640</v>
       </c>
       <c r="J347" s="0">
         <v>295.59719999999999</v>
@@ -14900,7 +14900,7 @@
         <v>328</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>1221</v>
+        <v>641</v>
       </c>
       <c r="J348" s="0">
         <v>137.02930000000001</v>
@@ -14932,7 +14932,7 @@
         <v>329</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>1222</v>
+        <v>642</v>
       </c>
       <c r="J349" s="0">
         <v>4746.6201000000001</v>
@@ -14964,7 +14964,7 @@
         <v>330</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>1223</v>
+        <v>643</v>
       </c>
       <c r="J350" s="0">
         <v>4426.7367999999997</v>
@@ -14996,7 +14996,7 @@
         <v>331</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>1224</v>
+        <v>644</v>
       </c>
       <c r="J351" s="0">
         <v>502.13749999999999</v>
@@ -15028,7 +15028,7 @@
         <v>334</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>1225</v>
+        <v>647</v>
       </c>
       <c r="J352" s="0">
         <v>439.52850000000001</v>
@@ -15060,7 +15060,7 @@
         <v>335</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>1226</v>
+        <v>648</v>
       </c>
       <c r="J353" s="0">
         <v>423.6062</v>
@@ -15092,7 +15092,7 @@
         <v>336</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>1227</v>
+        <v>649</v>
       </c>
       <c r="J354" s="0">
         <v>388.16570000000002</v>
@@ -15124,7 +15124,7 @@
         <v>337</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>1228</v>
+        <v>650</v>
       </c>
       <c r="J355" s="0">
         <v>361.62639999999999</v>
@@ -15156,7 +15156,7 @@
         <v>338</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>1229</v>
+        <v>651</v>
       </c>
       <c r="J356" s="0">
         <v>319.28989999999999</v>
@@ -15188,7 +15188,7 @@
         <v>339</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>1230</v>
+        <v>652</v>
       </c>
       <c r="J357" s="0">
         <v>283.29320000000001</v>
@@ -15220,7 +15220,7 @@
         <v>340</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>1231</v>
+        <v>653</v>
       </c>
       <c r="J358" s="0">
         <v>254.66130000000001</v>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="201005" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="210674" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="210674" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="213897" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="213897" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="217120" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="217120" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="220343" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="220343" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="226789" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="226789" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="255796" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>
@@ -3758,16 +3758,16 @@
   <dimension ref="A1:J385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="16.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="167.54296875" customWidth="true"/>
-    <col min="10" max="10" width="9.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="17.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="175.42578125" customWidth="true"/>
+    <col min="10" max="10" width="9.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="255796" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="268688" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>
@@ -3766,7 +3766,7 @@
     <col min="6" max="6" width="13" customWidth="true"/>
     <col min="7" max="7" width="8.5703125" customWidth="true"/>
     <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="175.42578125" customWidth="true"/>
+    <col min="9" max="9" width="147" customWidth="true"/>
     <col min="10" max="10" width="9.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3828,7 +3828,7 @@
         <v>43</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>342</v>
+        <v>875</v>
       </c>
       <c r="J2" s="0">
         <v>5104.9130999999998</v>
@@ -3860,7 +3860,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>343</v>
+        <v>876</v>
       </c>
       <c r="J3" s="0">
         <v>3263.4158000000002</v>
@@ -3892,7 +3892,7 @@
         <v>47</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>346</v>
+        <v>877</v>
       </c>
       <c r="J4" s="0">
         <v>443.3879</v>
@@ -3924,7 +3924,7 @@
         <v>48</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>347</v>
+        <v>878</v>
       </c>
       <c r="J5" s="0">
         <v>410.7122</v>
@@ -3956,7 +3956,7 @@
         <v>49</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>348</v>
+        <v>879</v>
       </c>
       <c r="J6" s="0">
         <v>393.60379999999998</v>
@@ -3988,7 +3988,7 @@
         <v>50</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>349</v>
+        <v>880</v>
       </c>
       <c r="J7" s="0">
         <v>378.97039999999998</v>
@@ -4020,7 +4020,7 @@
         <v>51</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>350</v>
+        <v>881</v>
       </c>
       <c r="J8" s="0">
         <v>353.012</v>
@@ -4052,7 +4052,7 @@
         <v>52</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>351</v>
+        <v>882</v>
       </c>
       <c r="J9" s="0">
         <v>323.56819999999999</v>
@@ -4084,7 +4084,7 @@
         <v>53</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>352</v>
+        <v>883</v>
       </c>
       <c r="J10" s="0">
         <v>292.92790000000002</v>
@@ -4116,7 +4116,7 @@
         <v>54</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>353</v>
+        <v>884</v>
       </c>
       <c r="J11" s="0">
         <v>218.8537</v>
@@ -4148,7 +4148,7 @@
         <v>55</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>354</v>
+        <v>885</v>
       </c>
       <c r="J12" s="0">
         <v>5212.9053000000004</v>
@@ -4180,7 +4180,7 @@
         <v>56</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>355</v>
+        <v>886</v>
       </c>
       <c r="J13" s="0">
         <v>1797.9413</v>
@@ -4212,7 +4212,7 @@
         <v>57</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>356</v>
+        <v>887</v>
       </c>
       <c r="J14" s="0">
         <v>942.65679999999998</v>
@@ -4244,7 +4244,7 @@
         <v>58</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>357</v>
+        <v>888</v>
       </c>
       <c r="J15" s="0">
         <v>813.27890000000002</v>
@@ -4276,7 +4276,7 @@
         <v>59</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>358</v>
+        <v>889</v>
       </c>
       <c r="J16" s="0">
         <v>394.9126</v>
@@ -4308,7 +4308,7 @@
         <v>60</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>359</v>
+        <v>890</v>
       </c>
       <c r="J17" s="0">
         <v>393.85860000000002</v>
@@ -4340,7 +4340,7 @@
         <v>61</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>360</v>
+        <v>891</v>
       </c>
       <c r="J18" s="0">
         <v>391.5865</v>
@@ -4372,7 +4372,7 @@
         <v>62</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>361</v>
+        <v>892</v>
       </c>
       <c r="J19" s="0">
         <v>383.69600000000003</v>
@@ -4404,7 +4404,7 @@
         <v>63</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>362</v>
+        <v>893</v>
       </c>
       <c r="J20" s="0">
         <v>367.87400000000002</v>
@@ -4436,7 +4436,7 @@
         <v>64</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>363</v>
+        <v>894</v>
       </c>
       <c r="J21" s="0">
         <v>367.8381</v>
@@ -4468,7 +4468,7 @@
         <v>65</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>364</v>
+        <v>895</v>
       </c>
       <c r="J22" s="0">
         <v>290.31869999999998</v>
@@ -4500,7 +4500,7 @@
         <v>66</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>365</v>
+        <v>896</v>
       </c>
       <c r="J23" s="0">
         <v>253.11709999999999</v>
@@ -4532,7 +4532,7 @@
         <v>67</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>366</v>
+        <v>897</v>
       </c>
       <c r="J24" s="0">
         <v>4968.7178000000004</v>
@@ -4564,7 +4564,7 @@
         <v>68</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>367</v>
+        <v>898</v>
       </c>
       <c r="J25" s="0">
         <v>3314.2456000000002</v>
@@ -4596,7 +4596,7 @@
         <v>69</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>368</v>
+        <v>899</v>
       </c>
       <c r="J26" s="0">
         <v>720.75220000000002</v>
@@ -4628,7 +4628,7 @@
         <v>70</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>369</v>
+        <v>900</v>
       </c>
       <c r="J27" s="0">
         <v>584.66700000000003</v>
@@ -4660,7 +4660,7 @@
         <v>71</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>370</v>
+        <v>901</v>
       </c>
       <c r="J28" s="0">
         <v>414.71820000000002</v>
@@ -4692,7 +4692,7 @@
         <v>72</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>371</v>
+        <v>902</v>
       </c>
       <c r="J29" s="0">
         <v>406.6533</v>
@@ -4724,7 +4724,7 @@
         <v>73</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>372</v>
+        <v>903</v>
       </c>
       <c r="J30" s="0">
         <v>371.4246</v>
@@ -4756,7 +4756,7 @@
         <v>74</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>373</v>
+        <v>904</v>
       </c>
       <c r="J31" s="0">
         <v>347.6481</v>
@@ -4788,7 +4788,7 @@
         <v>75</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>374</v>
+        <v>905</v>
       </c>
       <c r="J32" s="0">
         <v>340.82400000000001</v>
@@ -4820,7 +4820,7 @@
         <v>76</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>375</v>
+        <v>906</v>
       </c>
       <c r="J33" s="0">
         <v>308.06799999999998</v>
@@ -4852,7 +4852,7 @@
         <v>77</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>376</v>
+        <v>907</v>
       </c>
       <c r="J34" s="0">
         <v>252.10589999999999</v>
@@ -4884,7 +4884,7 @@
         <v>78</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>377</v>
+        <v>908</v>
       </c>
       <c r="J35" s="0">
         <v>213.29320000000001</v>
@@ -4916,7 +4916,7 @@
         <v>80</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>379</v>
+        <v>909</v>
       </c>
       <c r="J36" s="0">
         <v>2818.2202000000002</v>
@@ -4948,7 +4948,7 @@
         <v>81</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>380</v>
+        <v>910</v>
       </c>
       <c r="J37" s="0">
         <v>578.16610000000003</v>
@@ -4980,7 +4980,7 @@
         <v>83</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>382</v>
+        <v>911</v>
       </c>
       <c r="J38" s="0">
         <v>448.01760000000002</v>
@@ -5012,7 +5012,7 @@
         <v>84</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>383</v>
+        <v>912</v>
       </c>
       <c r="J39" s="0">
         <v>429.6198</v>
@@ -5044,7 +5044,7 @@
         <v>85</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>384</v>
+        <v>913</v>
       </c>
       <c r="J40" s="0">
         <v>406.0299</v>
@@ -5076,7 +5076,7 @@
         <v>86</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>385</v>
+        <v>914</v>
       </c>
       <c r="J41" s="0">
         <v>405.92529999999999</v>
@@ -5108,7 +5108,7 @@
         <v>87</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>386</v>
+        <v>915</v>
       </c>
       <c r="J42" s="0">
         <v>403.39850000000001</v>
@@ -5140,7 +5140,7 @@
         <v>88</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>387</v>
+        <v>916</v>
       </c>
       <c r="J43" s="0">
         <v>381.14350000000002</v>
@@ -5172,7 +5172,7 @@
         <v>89</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>388</v>
+        <v>917</v>
       </c>
       <c r="J44" s="0">
         <v>254.68129999999999</v>
@@ -5204,7 +5204,7 @@
         <v>90</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>389</v>
+        <v>918</v>
       </c>
       <c r="J45" s="0">
         <v>166.26730000000001</v>
@@ -5236,7 +5236,7 @@
         <v>659</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>840</v>
+        <v>919</v>
       </c>
       <c r="J46" s="0">
         <v>5173.3311000000003</v>
@@ -5268,7 +5268,7 @@
         <v>660</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>841</v>
+        <v>920</v>
       </c>
       <c r="J47" s="0">
         <v>3079.3002999999999</v>
@@ -5300,7 +5300,7 @@
         <v>663</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>843</v>
+        <v>921</v>
       </c>
       <c r="J48" s="0">
         <v>424.15600000000001</v>
@@ -5332,7 +5332,7 @@
         <v>664</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>844</v>
+        <v>922</v>
       </c>
       <c r="J49" s="0">
         <v>387.75049999999999</v>
@@ -5364,7 +5364,7 @@
         <v>665</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>845</v>
+        <v>923</v>
       </c>
       <c r="J50" s="0">
         <v>348.00529999999998</v>
@@ -5396,7 +5396,7 @@
         <v>666</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>846</v>
+        <v>924</v>
       </c>
       <c r="J51" s="0">
         <v>332.44470000000001</v>
@@ -5428,7 +5428,7 @@
         <v>667</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>847</v>
+        <v>925</v>
       </c>
       <c r="J52" s="0">
         <v>320.80650000000003</v>
@@ -5460,7 +5460,7 @@
         <v>668</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>848</v>
+        <v>926</v>
       </c>
       <c r="J53" s="0">
         <v>310.77530000000002</v>
@@ -5492,7 +5492,7 @@
         <v>669</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>849</v>
+        <v>927</v>
       </c>
       <c r="J54" s="0">
         <v>255.58779999999999</v>
@@ -5524,7 +5524,7 @@
         <v>670</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>850</v>
+        <v>928</v>
       </c>
       <c r="J55" s="0">
         <v>224.2235</v>
@@ -5556,7 +5556,7 @@
         <v>671</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>851</v>
+        <v>929</v>
       </c>
       <c r="J56" s="0">
         <v>6088.3633</v>
@@ -5588,7 +5588,7 @@
         <v>672</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>852</v>
+        <v>930</v>
       </c>
       <c r="J57" s="0">
         <v>5077.0581000000002</v>
@@ -5620,7 +5620,7 @@
         <v>673</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>853</v>
+        <v>931</v>
       </c>
       <c r="J58" s="0">
         <v>728.97640000000001</v>
@@ -5652,7 +5652,7 @@
         <v>674</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>854</v>
+        <v>932</v>
       </c>
       <c r="J59" s="0">
         <v>681.9529</v>
@@ -5684,7 +5684,7 @@
         <v>675</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>855</v>
+        <v>933</v>
       </c>
       <c r="J60" s="0">
         <v>460.65499999999997</v>
@@ -5716,7 +5716,7 @@
         <v>676</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>856</v>
+        <v>934</v>
       </c>
       <c r="J61" s="0">
         <v>406.1062</v>
@@ -5748,7 +5748,7 @@
         <v>677</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>857</v>
+        <v>935</v>
       </c>
       <c r="J62" s="0">
         <v>382.6694</v>
@@ -5780,7 +5780,7 @@
         <v>678</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>858</v>
+        <v>936</v>
       </c>
       <c r="J63" s="0">
         <v>369.21839999999998</v>
@@ -5812,7 +5812,7 @@
         <v>679</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>859</v>
+        <v>937</v>
       </c>
       <c r="J64" s="0">
         <v>341.30959999999999</v>
@@ -5844,7 +5844,7 @@
         <v>680</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>860</v>
+        <v>938</v>
       </c>
       <c r="J65" s="0">
         <v>319.78870000000001</v>
@@ -5876,7 +5876,7 @@
         <v>681</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>861</v>
+        <v>939</v>
       </c>
       <c r="J66" s="0">
         <v>289.6028</v>
@@ -5908,7 +5908,7 @@
         <v>682</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>862</v>
+        <v>940</v>
       </c>
       <c r="J67" s="0">
         <v>284.9262</v>
@@ -5940,7 +5940,7 @@
         <v>683</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>863</v>
+        <v>941</v>
       </c>
       <c r="J68" s="0">
         <v>5367.4771000000001</v>
@@ -5972,7 +5972,7 @@
         <v>684</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>864</v>
+        <v>942</v>
       </c>
       <c r="J69" s="0">
         <v>3219.1161999999999</v>
@@ -6004,7 +6004,7 @@
         <v>307</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>865</v>
+        <v>943</v>
       </c>
       <c r="J70" s="0">
         <v>999.82090000000005</v>
@@ -6036,7 +6036,7 @@
         <v>308</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>866</v>
+        <v>944</v>
       </c>
       <c r="J71" s="0">
         <v>829.32470000000001</v>
@@ -6068,7 +6068,7 @@
         <v>685</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>867</v>
+        <v>945</v>
       </c>
       <c r="J72" s="0">
         <v>434.72210000000001</v>
@@ -6100,7 +6100,7 @@
         <v>686</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>868</v>
+        <v>946</v>
       </c>
       <c r="J73" s="0">
         <v>420.51510000000002</v>
@@ -6132,7 +6132,7 @@
         <v>687</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>869</v>
+        <v>947</v>
       </c>
       <c r="J74" s="0">
         <v>416.28559999999999</v>
@@ -6164,7 +6164,7 @@
         <v>688</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>870</v>
+        <v>948</v>
       </c>
       <c r="J75" s="0">
         <v>400.9085</v>
@@ -6196,7 +6196,7 @@
         <v>689</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>871</v>
+        <v>949</v>
       </c>
       <c r="J76" s="0">
         <v>360.4205</v>
@@ -6228,7 +6228,7 @@
         <v>690</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>872</v>
+        <v>950</v>
       </c>
       <c r="J77" s="0">
         <v>305.30689999999999</v>
@@ -6260,7 +6260,7 @@
         <v>691</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>873</v>
+        <v>951</v>
       </c>
       <c r="J78" s="0">
         <v>293.2808</v>
@@ -6292,7 +6292,7 @@
         <v>692</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>874</v>
+        <v>952</v>
       </c>
       <c r="J79" s="0">
         <v>247.7748</v>
@@ -6324,7 +6324,7 @@
         <v>91</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>390</v>
+        <v>953</v>
       </c>
       <c r="J80" s="0">
         <v>5813.3739999999998</v>
@@ -6356,7 +6356,7 @@
         <v>92</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>391</v>
+        <v>954</v>
       </c>
       <c r="J81" s="0">
         <v>3499.9191999999998</v>
@@ -6388,7 +6388,7 @@
         <v>93</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>392</v>
+        <v>955</v>
       </c>
       <c r="J82" s="0">
         <v>643.7663</v>
@@ -6420,7 +6420,7 @@
         <v>94</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>393</v>
+        <v>956</v>
       </c>
       <c r="J83" s="0">
         <v>507.9119</v>
@@ -6452,7 +6452,7 @@
         <v>95</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>394</v>
+        <v>957</v>
       </c>
       <c r="J84" s="0">
         <v>413.24200000000002</v>
@@ -6484,7 +6484,7 @@
         <v>96</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>395</v>
+        <v>958</v>
       </c>
       <c r="J85" s="0">
         <v>412.743</v>
@@ -6516,7 +6516,7 @@
         <v>97</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>396</v>
+        <v>959</v>
       </c>
       <c r="J86" s="0">
         <v>365.9803</v>
@@ -6548,7 +6548,7 @@
         <v>98</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>397</v>
+        <v>960</v>
       </c>
       <c r="J87" s="0">
         <v>362.68889999999999</v>
@@ -6580,7 +6580,7 @@
         <v>99</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>398</v>
+        <v>961</v>
       </c>
       <c r="J88" s="0">
         <v>337.94470000000001</v>
@@ -6612,7 +6612,7 @@
         <v>100</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>399</v>
+        <v>962</v>
       </c>
       <c r="J89" s="0">
         <v>275.04509999999999</v>
@@ -6644,7 +6644,7 @@
         <v>101</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>400</v>
+        <v>963</v>
       </c>
       <c r="J90" s="0">
         <v>253.987</v>
@@ -6676,7 +6676,7 @@
         <v>102</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>401</v>
+        <v>964</v>
       </c>
       <c r="J91" s="0">
         <v>197.0513</v>
@@ -6708,7 +6708,7 @@
         <v>103</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>402</v>
+        <v>965</v>
       </c>
       <c r="J92" s="0">
         <v>6411.3008</v>
@@ -6740,7 +6740,7 @@
         <v>104</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>403</v>
+        <v>966</v>
       </c>
       <c r="J93" s="0">
         <v>5363.7114000000001</v>
@@ -6772,7 +6772,7 @@
         <v>107</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>406</v>
+        <v>967</v>
       </c>
       <c r="J94" s="0">
         <v>465.0847</v>
@@ -6804,7 +6804,7 @@
         <v>108</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>407</v>
+        <v>968</v>
       </c>
       <c r="J95" s="0">
         <v>432.71969999999999</v>
@@ -6836,7 +6836,7 @@
         <v>109</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>408</v>
+        <v>969</v>
       </c>
       <c r="J96" s="0">
         <v>403.6884</v>
@@ -6868,7 +6868,7 @@
         <v>110</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>409</v>
+        <v>970</v>
       </c>
       <c r="J97" s="0">
         <v>393.85660000000001</v>
@@ -6900,7 +6900,7 @@
         <v>111</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>410</v>
+        <v>971</v>
       </c>
       <c r="J98" s="0">
         <v>328.83640000000003</v>
@@ -6932,7 +6932,7 @@
         <v>112</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>411</v>
+        <v>972</v>
       </c>
       <c r="J99" s="0">
         <v>289.99919999999997</v>
@@ -6964,7 +6964,7 @@
         <v>113</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>412</v>
+        <v>973</v>
       </c>
       <c r="J100" s="0">
         <v>253.50819999999999</v>
@@ -6996,7 +6996,7 @@
         <v>114</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>413</v>
+        <v>974</v>
       </c>
       <c r="J101" s="0">
         <v>156.39179999999999</v>
@@ -7028,7 +7028,7 @@
         <v>115</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>414</v>
+        <v>975</v>
       </c>
       <c r="J102" s="0">
         <v>5347.2299999999996</v>
@@ -7060,7 +7060,7 @@
         <v>117</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>416</v>
+        <v>976</v>
       </c>
       <c r="J103" s="0">
         <v>832.64940000000001</v>
@@ -7092,7 +7092,7 @@
         <v>118</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>417</v>
+        <v>977</v>
       </c>
       <c r="J104" s="0">
         <v>670.97080000000005</v>
@@ -7124,7 +7124,7 @@
         <v>119</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>418</v>
+        <v>978</v>
       </c>
       <c r="J105" s="0">
         <v>452.6379</v>
@@ -7156,7 +7156,7 @@
         <v>120</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>419</v>
+        <v>979</v>
       </c>
       <c r="J106" s="0">
         <v>432.76639999999998</v>
@@ -7188,7 +7188,7 @@
         <v>121</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>420</v>
+        <v>980</v>
       </c>
       <c r="J107" s="0">
         <v>430.21100000000001</v>
@@ -7220,7 +7220,7 @@
         <v>122</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>421</v>
+        <v>981</v>
       </c>
       <c r="J108" s="0">
         <v>426.60840000000002</v>
@@ -7252,7 +7252,7 @@
         <v>123</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>422</v>
+        <v>982</v>
       </c>
       <c r="J109" s="0">
         <v>408.17599999999999</v>
@@ -7284,7 +7284,7 @@
         <v>124</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>423</v>
+        <v>983</v>
       </c>
       <c r="J110" s="0">
         <v>393.9744</v>
@@ -7316,7 +7316,7 @@
         <v>125</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>424</v>
+        <v>984</v>
       </c>
       <c r="J111" s="0">
         <v>369.06290000000001</v>
@@ -7348,7 +7348,7 @@
         <v>126</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>425</v>
+        <v>985</v>
       </c>
       <c r="J112" s="0">
         <v>363.61939999999999</v>
@@ -7380,7 +7380,7 @@
         <v>127</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>426</v>
+        <v>986</v>
       </c>
       <c r="J113" s="0">
         <v>5889.4614000000001</v>
@@ -7412,7 +7412,7 @@
         <v>128</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>427</v>
+        <v>987</v>
       </c>
       <c r="J114" s="0">
         <v>2742.3312999999998</v>
@@ -7444,7 +7444,7 @@
         <v>129</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>428</v>
+        <v>988</v>
       </c>
       <c r="J115" s="0">
         <v>673.23270000000002</v>
@@ -7476,7 +7476,7 @@
         <v>130</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>429</v>
+        <v>989</v>
       </c>
       <c r="J116" s="0">
         <v>548.54560000000004</v>
@@ -7508,7 +7508,7 @@
         <v>131</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>430</v>
+        <v>990</v>
       </c>
       <c r="J117" s="0">
         <v>406.4975</v>
@@ -7540,7 +7540,7 @@
         <v>132</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>431</v>
+        <v>991</v>
       </c>
       <c r="J118" s="0">
         <v>370.59609999999998</v>
@@ -7572,7 +7572,7 @@
         <v>133</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>432</v>
+        <v>992</v>
       </c>
       <c r="J119" s="0">
         <v>295.41489999999999</v>
@@ -7604,7 +7604,7 @@
         <v>134</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>433</v>
+        <v>993</v>
       </c>
       <c r="J120" s="0">
         <v>294.39229999999998</v>
@@ -7636,7 +7636,7 @@
         <v>135</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>434</v>
+        <v>994</v>
       </c>
       <c r="J121" s="0">
         <v>290.21879999999999</v>
@@ -7668,7 +7668,7 @@
         <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>436</v>
+        <v>995</v>
       </c>
       <c r="J122" s="0">
         <v>241.96080000000001</v>
@@ -7700,7 +7700,7 @@
         <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>437</v>
+        <v>996</v>
       </c>
       <c r="J123" s="0">
         <v>208.0266</v>
@@ -7732,7 +7732,7 @@
         <v>140</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>439</v>
+        <v>997</v>
       </c>
       <c r="J124" s="0">
         <v>2255.5239000000001</v>
@@ -7764,7 +7764,7 @@
         <v>141</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>440</v>
+        <v>998</v>
       </c>
       <c r="J125" s="0">
         <v>784.23540000000003</v>
@@ -7796,7 +7796,7 @@
         <v>142</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>441</v>
+        <v>999</v>
       </c>
       <c r="J126" s="0">
         <v>590.41420000000005</v>
@@ -7828,7 +7828,7 @@
         <v>143</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>442</v>
+        <v>1000</v>
       </c>
       <c r="J127" s="0">
         <v>431.26760000000002</v>
@@ -7860,7 +7860,7 @@
         <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>443</v>
+        <v>1001</v>
       </c>
       <c r="J128" s="0">
         <v>372.27710000000002</v>
@@ -7892,7 +7892,7 @@
         <v>145</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>444</v>
+        <v>1002</v>
       </c>
       <c r="J129" s="0">
         <v>370.83260000000001</v>
@@ -7924,7 +7924,7 @@
         <v>146</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>445</v>
+        <v>1003</v>
       </c>
       <c r="J130" s="0">
         <v>368.27210000000002</v>
@@ -7956,7 +7956,7 @@
         <v>147</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>446</v>
+        <v>1004</v>
       </c>
       <c r="J131" s="0">
         <v>345.15750000000003</v>
@@ -7988,7 +7988,7 @@
         <v>148</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>447</v>
+        <v>1005</v>
       </c>
       <c r="J132" s="0">
         <v>335.8723</v>
@@ -8020,7 +8020,7 @@
         <v>149</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>448</v>
+        <v>1006</v>
       </c>
       <c r="J133" s="0">
         <v>309.04379999999998</v>
@@ -8052,7 +8052,7 @@
         <v>150</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>449</v>
+        <v>1007</v>
       </c>
       <c r="J134" s="0">
         <v>280.34730000000002</v>
@@ -8084,7 +8084,7 @@
         <v>151</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>450</v>
+        <v>1008</v>
       </c>
       <c r="J135" s="0">
         <v>6089.4750999999997</v>
@@ -8116,7 +8116,7 @@
         <v>152</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>451</v>
+        <v>1009</v>
       </c>
       <c r="J136" s="0">
         <v>4801.2959000000001</v>
@@ -8148,7 +8148,7 @@
         <v>153</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>452</v>
+        <v>1010</v>
       </c>
       <c r="J137" s="0">
         <v>729.38409999999999</v>
@@ -8180,7 +8180,7 @@
         <v>155</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>454</v>
+        <v>1011</v>
       </c>
       <c r="J138" s="0">
         <v>414.8329</v>
@@ -8212,7 +8212,7 @@
         <v>156</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>455</v>
+        <v>1012</v>
       </c>
       <c r="J139" s="0">
         <v>407.11009999999999</v>
@@ -8244,7 +8244,7 @@
         <v>157</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>456</v>
+        <v>1013</v>
       </c>
       <c r="J140" s="0">
         <v>390.21910000000003</v>
@@ -8276,7 +8276,7 @@
         <v>158</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>457</v>
+        <v>1014</v>
       </c>
       <c r="J141" s="0">
         <v>362.1839</v>
@@ -8308,7 +8308,7 @@
         <v>159</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>458</v>
+        <v>1015</v>
       </c>
       <c r="J142" s="0">
         <v>349.2903</v>
@@ -8340,7 +8340,7 @@
         <v>160</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>459</v>
+        <v>1016</v>
       </c>
       <c r="J143" s="0">
         <v>339.61919999999998</v>
@@ -8372,7 +8372,7 @@
         <v>161</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>460</v>
+        <v>1017</v>
       </c>
       <c r="J144" s="0">
         <v>321.077</v>
@@ -8404,7 +8404,7 @@
         <v>162</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>461</v>
+        <v>1018</v>
       </c>
       <c r="J145" s="0">
         <v>320.34030000000001</v>
@@ -8436,7 +8436,7 @@
         <v>163</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>462</v>
+        <v>1019</v>
       </c>
       <c r="J146" s="0">
         <v>4900.8388999999997</v>
@@ -8468,7 +8468,7 @@
         <v>164</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>463</v>
+        <v>1020</v>
       </c>
       <c r="J147" s="0">
         <v>2991.1887000000002</v>
@@ -8500,7 +8500,7 @@
         <v>165</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>464</v>
+        <v>1021</v>
       </c>
       <c r="J148" s="0">
         <v>694.42499999999996</v>
@@ -8532,7 +8532,7 @@
         <v>166</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>465</v>
+        <v>1022</v>
       </c>
       <c r="J149" s="0">
         <v>590.76210000000003</v>
@@ -8564,7 +8564,7 @@
         <v>167</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>466</v>
+        <v>1023</v>
       </c>
       <c r="J150" s="0">
         <v>434.02370000000002</v>
@@ -8596,7 +8596,7 @@
         <v>168</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>467</v>
+        <v>1024</v>
       </c>
       <c r="J151" s="0">
         <v>417.05189999999999</v>
@@ -8628,7 +8628,7 @@
         <v>169</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>468</v>
+        <v>1025</v>
       </c>
       <c r="J152" s="0">
         <v>407.86430000000001</v>
@@ -8660,7 +8660,7 @@
         <v>170</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>469</v>
+        <v>1026</v>
       </c>
       <c r="J153" s="0">
         <v>406.37779999999998</v>
@@ -8692,7 +8692,7 @@
         <v>171</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>470</v>
+        <v>1027</v>
       </c>
       <c r="J154" s="0">
         <v>379.51209999999998</v>
@@ -8724,7 +8724,7 @@
         <v>172</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>471</v>
+        <v>1028</v>
       </c>
       <c r="J155" s="0">
         <v>361.57029999999998</v>
@@ -8756,7 +8756,7 @@
         <v>173</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>472</v>
+        <v>1029</v>
       </c>
       <c r="J156" s="0">
         <v>324.36189999999999</v>
@@ -8788,7 +8788,7 @@
         <v>176</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>475</v>
+        <v>1030</v>
       </c>
       <c r="J157" s="0">
         <v>2639.6545000000001</v>
@@ -8820,7 +8820,7 @@
         <v>177</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>476</v>
+        <v>1031</v>
       </c>
       <c r="J158" s="0">
         <v>538.57830000000001</v>
@@ -8852,7 +8852,7 @@
         <v>178</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>477</v>
+        <v>1032</v>
       </c>
       <c r="J159" s="0">
         <v>439.68729999999999</v>
@@ -8884,7 +8884,7 @@
         <v>180</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>479</v>
+        <v>1033</v>
       </c>
       <c r="J160" s="0">
         <v>348.95269999999999</v>
@@ -8916,7 +8916,7 @@
         <v>181</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>480</v>
+        <v>1034</v>
       </c>
       <c r="J161" s="0">
         <v>320.45060000000001</v>
@@ -8948,7 +8948,7 @@
         <v>182</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>481</v>
+        <v>1035</v>
       </c>
       <c r="J162" s="0">
         <v>306.95499999999999</v>
@@ -8980,7 +8980,7 @@
         <v>183</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>482</v>
+        <v>1036</v>
       </c>
       <c r="J163" s="0">
         <v>286.13639999999998</v>
@@ -9012,7 +9012,7 @@
         <v>184</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>483</v>
+        <v>1037</v>
       </c>
       <c r="J164" s="0">
         <v>270.46800000000002</v>
@@ -9044,7 +9044,7 @@
         <v>185</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>484</v>
+        <v>1038</v>
       </c>
       <c r="J165" s="0">
         <v>266.42959999999999</v>
@@ -9076,7 +9076,7 @@
         <v>186</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>485</v>
+        <v>1039</v>
       </c>
       <c r="J166" s="0">
         <v>198.7653</v>
@@ -9108,7 +9108,7 @@
         <v>187</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>486</v>
+        <v>1040</v>
       </c>
       <c r="J167" s="0">
         <v>6949.5127000000002</v>
@@ -9140,7 +9140,7 @@
         <v>188</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>487</v>
+        <v>1041</v>
       </c>
       <c r="J168" s="0">
         <v>1918.3168000000001</v>
@@ -9172,7 +9172,7 @@
         <v>189</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>488</v>
+        <v>1042</v>
       </c>
       <c r="J169" s="0">
         <v>842.53420000000006</v>
@@ -9204,7 +9204,7 @@
         <v>190</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>489</v>
+        <v>1043</v>
       </c>
       <c r="J170" s="0">
         <v>625.51949999999999</v>
@@ -9236,7 +9236,7 @@
         <v>191</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>490</v>
+        <v>1044</v>
       </c>
       <c r="J171" s="0">
         <v>403.39569999999998</v>
@@ -9268,7 +9268,7 @@
         <v>192</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>491</v>
+        <v>1045</v>
       </c>
       <c r="J172" s="0">
         <v>401.83440000000002</v>
@@ -9300,7 +9300,7 @@
         <v>193</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>492</v>
+        <v>1046</v>
       </c>
       <c r="J173" s="0">
         <v>401.53390000000002</v>
@@ -9332,7 +9332,7 @@
         <v>194</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>493</v>
+        <v>1047</v>
       </c>
       <c r="J174" s="0">
         <v>325.73790000000002</v>
@@ -9364,7 +9364,7 @@
         <v>195</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>494</v>
+        <v>1048</v>
       </c>
       <c r="J175" s="0">
         <v>306.47129999999999</v>
@@ -9396,7 +9396,7 @@
         <v>196</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>495</v>
+        <v>1049</v>
       </c>
       <c r="J176" s="0">
         <v>297.54129999999998</v>
@@ -9428,7 +9428,7 @@
         <v>197</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>496</v>
+        <v>1050</v>
       </c>
       <c r="J177" s="0">
         <v>251.23050000000001</v>
@@ -9460,7 +9460,7 @@
         <v>198</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>497</v>
+        <v>1051</v>
       </c>
       <c r="J178" s="0">
         <v>104.34829999999999</v>
@@ -9492,7 +9492,7 @@
         <v>199</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>498</v>
+        <v>1052</v>
       </c>
       <c r="J179" s="0">
         <v>5196.1244999999999</v>
@@ -9524,7 +9524,7 @@
         <v>201</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>500</v>
+        <v>1053</v>
       </c>
       <c r="J180" s="0">
         <v>554.0693</v>
@@ -9556,7 +9556,7 @@
         <v>202</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>501</v>
+        <v>1054</v>
       </c>
       <c r="J181" s="0">
         <v>97.465900000000005</v>
@@ -9588,7 +9588,7 @@
         <v>203</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>502</v>
+        <v>1055</v>
       </c>
       <c r="J182" s="0">
         <v>413.24349999999998</v>
@@ -9620,7 +9620,7 @@
         <v>204</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>503</v>
+        <v>1056</v>
       </c>
       <c r="J183" s="0">
         <v>390.69720000000001</v>
@@ -9652,7 +9652,7 @@
         <v>205</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>504</v>
+        <v>1057</v>
       </c>
       <c r="J184" s="0">
         <v>384.44110000000001</v>
@@ -9684,7 +9684,7 @@
         <v>206</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>505</v>
+        <v>1058</v>
       </c>
       <c r="J185" s="0">
         <v>369.39760000000001</v>
@@ -9716,7 +9716,7 @@
         <v>207</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>506</v>
+        <v>1059</v>
       </c>
       <c r="J186" s="0">
         <v>355.85449999999997</v>
@@ -9748,7 +9748,7 @@
         <v>208</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>507</v>
+        <v>1060</v>
       </c>
       <c r="J187" s="0">
         <v>332.20139999999998</v>
@@ -9780,7 +9780,7 @@
         <v>209</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>508</v>
+        <v>1061</v>
       </c>
       <c r="J188" s="0">
         <v>304.4751</v>
@@ -9812,7 +9812,7 @@
         <v>210</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>509</v>
+        <v>1062</v>
       </c>
       <c r="J189" s="0">
         <v>263.24160000000001</v>
@@ -9844,7 +9844,7 @@
         <v>211</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>510</v>
+        <v>1063</v>
       </c>
       <c r="J190" s="0">
         <v>5598.6216000000004</v>
@@ -9876,7 +9876,7 @@
         <v>212</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>511</v>
+        <v>1064</v>
       </c>
       <c r="J191" s="0">
         <v>4298.6826000000001</v>
@@ -9908,7 +9908,7 @@
         <v>213</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>512</v>
+        <v>1065</v>
       </c>
       <c r="J192" s="0">
         <v>831.18269999999996</v>
@@ -9940,7 +9940,7 @@
         <v>214</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>513</v>
+        <v>1066</v>
       </c>
       <c r="J193" s="0">
         <v>746.42259999999999</v>
@@ -9972,7 +9972,7 @@
         <v>215</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>514</v>
+        <v>1067</v>
       </c>
       <c r="J194" s="0">
         <v>477.65440000000001</v>
@@ -10004,7 +10004,7 @@
         <v>216</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>515</v>
+        <v>1068</v>
       </c>
       <c r="J195" s="0">
         <v>455.09550000000002</v>
@@ -10036,7 +10036,7 @@
         <v>217</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>516</v>
+        <v>1069</v>
       </c>
       <c r="J196" s="0">
         <v>442.9828</v>
@@ -10068,7 +10068,7 @@
         <v>218</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>517</v>
+        <v>1070</v>
       </c>
       <c r="J197" s="0">
         <v>403.95710000000003</v>
@@ -10100,7 +10100,7 @@
         <v>219</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>518</v>
+        <v>1071</v>
       </c>
       <c r="J198" s="0">
         <v>353.99869999999999</v>
@@ -10132,7 +10132,7 @@
         <v>220</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>519</v>
+        <v>1072</v>
       </c>
       <c r="J199" s="0">
         <v>282.62110000000001</v>
@@ -10164,7 +10164,7 @@
         <v>221</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>520</v>
+        <v>1073</v>
       </c>
       <c r="J200" s="0">
         <v>251.0352</v>
@@ -10196,7 +10196,7 @@
         <v>222</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>521</v>
+        <v>1074</v>
       </c>
       <c r="J201" s="0">
         <v>226.5855</v>
@@ -10228,7 +10228,7 @@
         <v>223</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>522</v>
+        <v>1075</v>
       </c>
       <c r="J202" s="0">
         <v>3073.4854</v>
@@ -10260,7 +10260,7 @@
         <v>224</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>523</v>
+        <v>1076</v>
       </c>
       <c r="J203" s="0">
         <v>1817.3022000000001</v>
@@ -10292,7 +10292,7 @@
         <v>213</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>524</v>
+        <v>1077</v>
       </c>
       <c r="J204" s="0">
         <v>831.18269999999996</v>
@@ -10324,7 +10324,7 @@
         <v>225</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>526</v>
+        <v>1078</v>
       </c>
       <c r="J205" s="0">
         <v>444.28719999999999</v>
@@ -10356,7 +10356,7 @@
         <v>226</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>527</v>
+        <v>1079</v>
       </c>
       <c r="J206" s="0">
         <v>406.01569999999998</v>
@@ -10388,7 +10388,7 @@
         <v>227</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>528</v>
+        <v>1080</v>
       </c>
       <c r="J207" s="0">
         <v>377.0512</v>
@@ -10420,7 +10420,7 @@
         <v>228</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>529</v>
+        <v>1081</v>
       </c>
       <c r="J208" s="0">
         <v>370.54059999999998</v>
@@ -10452,7 +10452,7 @@
         <v>229</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>530</v>
+        <v>1082</v>
       </c>
       <c r="J209" s="0">
         <v>364.45699999999999</v>
@@ -10484,7 +10484,7 @@
         <v>230</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>531</v>
+        <v>1083</v>
       </c>
       <c r="J210" s="0">
         <v>357.5231</v>
@@ -10516,7 +10516,7 @@
         <v>231</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>532</v>
+        <v>1084</v>
       </c>
       <c r="J211" s="0">
         <v>289.80360000000002</v>
@@ -10548,7 +10548,7 @@
         <v>232</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>533</v>
+        <v>1085</v>
       </c>
       <c r="J212" s="0">
         <v>205.23990000000001</v>
@@ -10580,7 +10580,7 @@
         <v>233</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>534</v>
+        <v>1086</v>
       </c>
       <c r="J213" s="0">
         <v>5904.6377000000002</v>
@@ -10612,7 +10612,7 @@
         <v>234</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>535</v>
+        <v>1087</v>
       </c>
       <c r="J214" s="0">
         <v>4907.7012000000004</v>
@@ -10644,7 +10644,7 @@
         <v>235</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>536</v>
+        <v>1088</v>
       </c>
       <c r="J215" s="0">
         <v>202.81960000000001</v>
@@ -10676,7 +10676,7 @@
         <v>237</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>538</v>
+        <v>1089</v>
       </c>
       <c r="J216" s="0">
         <v>383.23849999999999</v>
@@ -10708,7 +10708,7 @@
         <v>238</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>539</v>
+        <v>1090</v>
       </c>
       <c r="J217" s="0">
         <v>363.8911</v>
@@ -10740,7 +10740,7 @@
         <v>239</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>540</v>
+        <v>1091</v>
       </c>
       <c r="J218" s="0">
         <v>355.88670000000002</v>
@@ -10772,7 +10772,7 @@
         <v>240</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>541</v>
+        <v>1092</v>
       </c>
       <c r="J219" s="0">
         <v>351.3347</v>
@@ -10804,7 +10804,7 @@
         <v>241</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>542</v>
+        <v>1093</v>
       </c>
       <c r="J220" s="0">
         <v>333.8578</v>
@@ -10836,7 +10836,7 @@
         <v>242</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>543</v>
+        <v>1094</v>
       </c>
       <c r="J221" s="0">
         <v>313.44380000000001</v>
@@ -10868,7 +10868,7 @@
         <v>243</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>544</v>
+        <v>1095</v>
       </c>
       <c r="J222" s="0">
         <v>238.27189999999999</v>
@@ -10900,7 +10900,7 @@
         <v>244</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>545</v>
+        <v>1096</v>
       </c>
       <c r="J223" s="0">
         <v>141.53020000000001</v>
@@ -10932,7 +10932,7 @@
         <v>245</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>546</v>
+        <v>1097</v>
       </c>
       <c r="J224" s="0">
         <v>6671.5464000000002</v>
@@ -10964,7 +10964,7 @@
         <v>246</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>547</v>
+        <v>1098</v>
       </c>
       <c r="J225" s="0">
         <v>2604.8850000000002</v>
@@ -10996,7 +10996,7 @@
         <v>248</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>549</v>
+        <v>1099</v>
       </c>
       <c r="J226" s="0">
         <v>539.66269999999997</v>
@@ -11028,7 +11028,7 @@
         <v>250</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>551</v>
+        <v>1100</v>
       </c>
       <c r="J227" s="0">
         <v>429.82010000000002</v>
@@ -11060,7 +11060,7 @@
         <v>251</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>552</v>
+        <v>1101</v>
       </c>
       <c r="J228" s="0">
         <v>421.38249999999999</v>
@@ -11092,7 +11092,7 @@
         <v>252</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>553</v>
+        <v>1102</v>
       </c>
       <c r="J229" s="0">
         <v>417.74880000000002</v>
@@ -11124,7 +11124,7 @@
         <v>253</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>554</v>
+        <v>1103</v>
       </c>
       <c r="J230" s="0">
         <v>393.11059999999998</v>
@@ -11156,7 +11156,7 @@
         <v>254</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>555</v>
+        <v>1104</v>
       </c>
       <c r="J231" s="0">
         <v>392.10489999999999</v>
@@ -11188,7 +11188,7 @@
         <v>255</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>556</v>
+        <v>1105</v>
       </c>
       <c r="J232" s="0">
         <v>387.5043</v>
@@ -11220,7 +11220,7 @@
         <v>256</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>557</v>
+        <v>1106</v>
       </c>
       <c r="J233" s="0">
         <v>215.23259999999999</v>
@@ -11252,7 +11252,7 @@
         <v>693</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>804</v>
+        <v>1107</v>
       </c>
       <c r="J234" s="0">
         <v>6179.7012000000004</v>
@@ -11284,7 +11284,7 @@
         <v>694</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>805</v>
+        <v>1108</v>
       </c>
       <c r="J235" s="0">
         <v>2590.0304999999999</v>
@@ -11316,7 +11316,7 @@
         <v>695</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>806</v>
+        <v>1109</v>
       </c>
       <c r="J236" s="0">
         <v>1052.7577000000001</v>
@@ -11348,7 +11348,7 @@
         <v>696</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>807</v>
+        <v>1110</v>
       </c>
       <c r="J237" s="0">
         <v>663.33749999999998</v>
@@ -11380,7 +11380,7 @@
         <v>697</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>808</v>
+        <v>1111</v>
       </c>
       <c r="J238" s="0">
         <v>506.81569999999999</v>
@@ -11412,7 +11412,7 @@
         <v>698</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>809</v>
+        <v>1112</v>
       </c>
       <c r="J239" s="0">
         <v>408.8279</v>
@@ -11444,7 +11444,7 @@
         <v>699</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>810</v>
+        <v>1113</v>
       </c>
       <c r="J240" s="0">
         <v>402.4606</v>
@@ -11476,7 +11476,7 @@
         <v>700</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>811</v>
+        <v>1114</v>
       </c>
       <c r="J241" s="0">
         <v>395.95499999999999</v>
@@ -11508,7 +11508,7 @@
         <v>701</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>812</v>
+        <v>1115</v>
       </c>
       <c r="J242" s="0">
         <v>384.18630000000002</v>
@@ -11540,7 +11540,7 @@
         <v>702</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>813</v>
+        <v>1116</v>
       </c>
       <c r="J243" s="0">
         <v>337.53550000000001</v>
@@ -11572,7 +11572,7 @@
         <v>703</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>814</v>
+        <v>1117</v>
       </c>
       <c r="J244" s="0">
         <v>304.91230000000002</v>
@@ -11604,7 +11604,7 @@
         <v>704</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>815</v>
+        <v>1118</v>
       </c>
       <c r="J245" s="0">
         <v>125.54000000000001</v>
@@ -11636,7 +11636,7 @@
         <v>705</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>816</v>
+        <v>1119</v>
       </c>
       <c r="J246" s="0">
         <v>5385.1138000000001</v>
@@ -11668,7 +11668,7 @@
         <v>706</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>817</v>
+        <v>1120</v>
       </c>
       <c r="J247" s="0">
         <v>2843.9126000000001</v>
@@ -11700,7 +11700,7 @@
         <v>707</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>818</v>
+        <v>1121</v>
       </c>
       <c r="J248" s="0">
         <v>710.74549999999999</v>
@@ -11732,7 +11732,7 @@
         <v>708</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>819</v>
+        <v>1122</v>
       </c>
       <c r="J249" s="0">
         <v>550.2423</v>
@@ -11764,7 +11764,7 @@
         <v>709</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>820</v>
+        <v>1123</v>
       </c>
       <c r="J250" s="0">
         <v>438.92590000000001</v>
@@ -11796,7 +11796,7 @@
         <v>710</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>821</v>
+        <v>1124</v>
       </c>
       <c r="J251" s="0">
         <v>423.42290000000003</v>
@@ -11828,7 +11828,7 @@
         <v>711</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>822</v>
+        <v>1125</v>
       </c>
       <c r="J252" s="0">
         <v>403.89089999999999</v>
@@ -11860,7 +11860,7 @@
         <v>712</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>823</v>
+        <v>1126</v>
       </c>
       <c r="J253" s="0">
         <v>391.21699999999999</v>
@@ -11892,7 +11892,7 @@
         <v>713</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>824</v>
+        <v>1127</v>
       </c>
       <c r="J254" s="0">
         <v>383.9436</v>
@@ -11924,7 +11924,7 @@
         <v>714</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>825</v>
+        <v>1128</v>
       </c>
       <c r="J255" s="0">
         <v>312.447</v>
@@ -11956,7 +11956,7 @@
         <v>715</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>826</v>
+        <v>1129</v>
       </c>
       <c r="J256" s="0">
         <v>309.3852</v>
@@ -11988,7 +11988,7 @@
         <v>716</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>827</v>
+        <v>1130</v>
       </c>
       <c r="J257" s="0">
         <v>235.6891</v>
@@ -12020,7 +12020,7 @@
         <v>717</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>828</v>
+        <v>1131</v>
       </c>
       <c r="J258" s="0">
         <v>6293.9867999999997</v>
@@ -12052,7 +12052,7 @@
         <v>718</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>829</v>
+        <v>1132</v>
       </c>
       <c r="J259" s="0">
         <v>5358.5902999999999</v>
@@ -12084,7 +12084,7 @@
         <v>719</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>830</v>
+        <v>1133</v>
       </c>
       <c r="J260" s="0">
         <v>577.04179999999997</v>
@@ -12116,7 +12116,7 @@
         <v>720</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>831</v>
+        <v>1134</v>
       </c>
       <c r="J261" s="0">
         <v>518.29719999999998</v>
@@ -12148,7 +12148,7 @@
         <v>721</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>832</v>
+        <v>1135</v>
       </c>
       <c r="J262" s="0">
         <v>427.73379999999997</v>
@@ -12180,7 +12180,7 @@
         <v>722</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>833</v>
+        <v>1136</v>
       </c>
       <c r="J263" s="0">
         <v>404.26459999999997</v>
@@ -12212,7 +12212,7 @@
         <v>723</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>834</v>
+        <v>1137</v>
       </c>
       <c r="J264" s="0">
         <v>398.51589999999999</v>
@@ -12244,7 +12244,7 @@
         <v>724</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>835</v>
+        <v>1138</v>
       </c>
       <c r="J265" s="0">
         <v>392.9486</v>
@@ -12276,7 +12276,7 @@
         <v>725</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>836</v>
+        <v>1139</v>
       </c>
       <c r="J266" s="0">
         <v>382.86340000000001</v>
@@ -12308,7 +12308,7 @@
         <v>726</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>837</v>
+        <v>1140</v>
       </c>
       <c r="J267" s="0">
         <v>368.97640000000001</v>
@@ -12340,7 +12340,7 @@
         <v>727</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>838</v>
+        <v>1141</v>
       </c>
       <c r="J268" s="0">
         <v>347.17689999999999</v>
@@ -12372,7 +12372,7 @@
         <v>728</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>839</v>
+        <v>1142</v>
       </c>
       <c r="J269" s="0">
         <v>328.54599999999999</v>
@@ -12404,7 +12404,7 @@
         <v>257</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>558</v>
+        <v>1143</v>
       </c>
       <c r="J270" s="0">
         <v>5568.125</v>
@@ -12436,7 +12436,7 @@
         <v>258</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>559</v>
+        <v>1144</v>
       </c>
       <c r="J271" s="0">
         <v>2316.6012999999998</v>
@@ -12468,7 +12468,7 @@
         <v>259</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>560</v>
+        <v>1145</v>
       </c>
       <c r="J272" s="0">
         <v>504.78460000000001</v>
@@ -12500,7 +12500,7 @@
         <v>260</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>561</v>
+        <v>1146</v>
       </c>
       <c r="J273" s="0">
         <v>445.50999999999999</v>
@@ -12532,7 +12532,7 @@
         <v>261</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>562</v>
+        <v>1147</v>
       </c>
       <c r="J274" s="0">
         <v>401.56920000000002</v>
@@ -12564,7 +12564,7 @@
         <v>262</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>563</v>
+        <v>1148</v>
       </c>
       <c r="J275" s="0">
         <v>392.42399999999998</v>
@@ -12596,7 +12596,7 @@
         <v>263</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>564</v>
+        <v>1149</v>
       </c>
       <c r="J276" s="0">
         <v>368.18880000000001</v>
@@ -12628,7 +12628,7 @@
         <v>264</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>565</v>
+        <v>1150</v>
       </c>
       <c r="J277" s="0">
         <v>366.78320000000002</v>
@@ -12660,7 +12660,7 @@
         <v>265</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>566</v>
+        <v>1151</v>
       </c>
       <c r="J278" s="0">
         <v>361.8997</v>
@@ -12692,7 +12692,7 @@
         <v>266</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>567</v>
+        <v>1152</v>
       </c>
       <c r="J279" s="0">
         <v>322.42989999999998</v>
@@ -12724,7 +12724,7 @@
         <v>267</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>568</v>
+        <v>1153</v>
       </c>
       <c r="J280" s="0">
         <v>308.6019</v>
@@ -12756,7 +12756,7 @@
         <v>268</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>569</v>
+        <v>1154</v>
       </c>
       <c r="J281" s="0">
         <v>260.48289999999997</v>
@@ -12788,7 +12788,7 @@
         <v>103</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>570</v>
+        <v>1155</v>
       </c>
       <c r="J282" s="0">
         <v>6411.3008</v>
@@ -12820,7 +12820,7 @@
         <v>104</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>571</v>
+        <v>1156</v>
       </c>
       <c r="J283" s="0">
         <v>5363.7114000000001</v>
@@ -12852,7 +12852,7 @@
         <v>107</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>574</v>
+        <v>1157</v>
       </c>
       <c r="J284" s="0">
         <v>465.0847</v>
@@ -12884,7 +12884,7 @@
         <v>108</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>575</v>
+        <v>1158</v>
       </c>
       <c r="J285" s="0">
         <v>432.71969999999999</v>
@@ -12916,7 +12916,7 @@
         <v>109</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>576</v>
+        <v>1159</v>
       </c>
       <c r="J286" s="0">
         <v>403.6884</v>
@@ -12948,7 +12948,7 @@
         <v>110</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>577</v>
+        <v>1160</v>
       </c>
       <c r="J287" s="0">
         <v>393.85660000000001</v>
@@ -12980,7 +12980,7 @@
         <v>111</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>578</v>
+        <v>1161</v>
       </c>
       <c r="J288" s="0">
         <v>328.83640000000003</v>
@@ -13012,7 +13012,7 @@
         <v>112</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>579</v>
+        <v>1162</v>
       </c>
       <c r="J289" s="0">
         <v>289.99919999999997</v>
@@ -13044,7 +13044,7 @@
         <v>113</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>580</v>
+        <v>1163</v>
       </c>
       <c r="J290" s="0">
         <v>253.50819999999999</v>
@@ -13076,7 +13076,7 @@
         <v>114</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>581</v>
+        <v>1164</v>
       </c>
       <c r="J291" s="0">
         <v>156.39179999999999</v>
@@ -13108,7 +13108,7 @@
         <v>269</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>582</v>
+        <v>1165</v>
       </c>
       <c r="J292" s="0">
         <v>5610.5132000000003</v>
@@ -13140,7 +13140,7 @@
         <v>270</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>583</v>
+        <v>1166</v>
       </c>
       <c r="J293" s="0">
         <v>2526.6718999999998</v>
@@ -13172,7 +13172,7 @@
         <v>271</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>584</v>
+        <v>1167</v>
       </c>
       <c r="J294" s="0">
         <v>663.2672</v>
@@ -13204,7 +13204,7 @@
         <v>272</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>585</v>
+        <v>1168</v>
       </c>
       <c r="J295" s="0">
         <v>553.69179999999994</v>
@@ -13236,7 +13236,7 @@
         <v>273</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>586</v>
+        <v>1169</v>
       </c>
       <c r="J296" s="0">
         <v>436.38159999999999</v>
@@ -13268,7 +13268,7 @@
         <v>274</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>587</v>
+        <v>1170</v>
       </c>
       <c r="J297" s="0">
         <v>411.78269999999998</v>
@@ -13300,7 +13300,7 @@
         <v>275</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>588</v>
+        <v>1171</v>
       </c>
       <c r="J298" s="0">
         <v>407.44670000000002</v>
@@ -13332,7 +13332,7 @@
         <v>276</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>589</v>
+        <v>1172</v>
       </c>
       <c r="J299" s="0">
         <v>390.17970000000003</v>
@@ -13364,7 +13364,7 @@
         <v>277</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>590</v>
+        <v>1173</v>
       </c>
       <c r="J300" s="0">
         <v>379.34300000000002</v>
@@ -13396,7 +13396,7 @@
         <v>278</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>591</v>
+        <v>1174</v>
       </c>
       <c r="J301" s="0">
         <v>378.32549999999998</v>
@@ -13428,7 +13428,7 @@
         <v>279</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>592</v>
+        <v>1175</v>
       </c>
       <c r="J302" s="0">
         <v>248.1077</v>
@@ -13460,7 +13460,7 @@
         <v>280</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>593</v>
+        <v>1176</v>
       </c>
       <c r="J303" s="0">
         <v>155.72280000000001</v>
@@ -13492,7 +13492,7 @@
         <v>281</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>594</v>
+        <v>1177</v>
       </c>
       <c r="J304" s="0">
         <v>6378.5679</v>
@@ -13524,7 +13524,7 @@
         <v>282</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>595</v>
+        <v>1178</v>
       </c>
       <c r="J305" s="0">
         <v>3677.8054000000002</v>
@@ -13556,7 +13556,7 @@
         <v>283</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>596</v>
+        <v>1179</v>
       </c>
       <c r="J306" s="0">
         <v>990.75639999999999</v>
@@ -13588,7 +13588,7 @@
         <v>284</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>597</v>
+        <v>1180</v>
       </c>
       <c r="J307" s="0">
         <v>912.61609999999996</v>
@@ -13620,7 +13620,7 @@
         <v>285</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>598</v>
+        <v>1181</v>
       </c>
       <c r="J308" s="0">
         <v>448.30200000000002</v>
@@ -13652,7 +13652,7 @@
         <v>286</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>599</v>
+        <v>1182</v>
       </c>
       <c r="J309" s="0">
         <v>415.84109999999998</v>
@@ -13684,7 +13684,7 @@
         <v>287</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>600</v>
+        <v>1183</v>
       </c>
       <c r="J310" s="0">
         <v>380.94420000000002</v>
@@ -13716,7 +13716,7 @@
         <v>288</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>601</v>
+        <v>1184</v>
       </c>
       <c r="J311" s="0">
         <v>359.60860000000002</v>
@@ -13748,7 +13748,7 @@
         <v>289</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>602</v>
+        <v>1185</v>
       </c>
       <c r="J312" s="0">
         <v>338.8168</v>
@@ -13780,7 +13780,7 @@
         <v>290</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>603</v>
+        <v>1186</v>
       </c>
       <c r="J313" s="0">
         <v>320.63470000000001</v>
@@ -13812,7 +13812,7 @@
         <v>291</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>604</v>
+        <v>1187</v>
       </c>
       <c r="J314" s="0">
         <v>287.04489999999999</v>
@@ -13844,7 +13844,7 @@
         <v>292</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>605</v>
+        <v>1188</v>
       </c>
       <c r="J315" s="0">
         <v>107.8788</v>
@@ -13876,7 +13876,7 @@
         <v>293</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>606</v>
+        <v>1189</v>
       </c>
       <c r="J316" s="0">
         <v>5099.2568000000001</v>
@@ -13908,7 +13908,7 @@
         <v>294</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>607</v>
+        <v>1190</v>
       </c>
       <c r="J317" s="0">
         <v>2383.1239999999998</v>
@@ -13940,7 +13940,7 @@
         <v>295</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>608</v>
+        <v>1191</v>
       </c>
       <c r="J318" s="0">
         <v>670.93709999999999</v>
@@ -13972,7 +13972,7 @@
         <v>296</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>609</v>
+        <v>1192</v>
       </c>
       <c r="J319" s="0">
         <v>459.24430000000001</v>
@@ -14004,7 +14004,7 @@
         <v>297</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>610</v>
+        <v>1193</v>
       </c>
       <c r="J320" s="0">
         <v>415.84710000000001</v>
@@ -14036,7 +14036,7 @@
         <v>298</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>611</v>
+        <v>1194</v>
       </c>
       <c r="J321" s="0">
         <v>404.09039999999999</v>
@@ -14068,7 +14068,7 @@
         <v>299</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>612</v>
+        <v>1195</v>
       </c>
       <c r="J322" s="0">
         <v>370.1207</v>
@@ -14100,7 +14100,7 @@
         <v>300</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>613</v>
+        <v>1196</v>
       </c>
       <c r="J323" s="0">
         <v>369.87549999999999</v>
@@ -14132,7 +14132,7 @@
         <v>301</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>614</v>
+        <v>1197</v>
       </c>
       <c r="J324" s="0">
         <v>332.15789999999998</v>
@@ -14164,7 +14164,7 @@
         <v>302</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>615</v>
+        <v>1198</v>
       </c>
       <c r="J325" s="0">
         <v>310.02600000000001</v>
@@ -14196,7 +14196,7 @@
         <v>303</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>616</v>
+        <v>1199</v>
       </c>
       <c r="J326" s="0">
         <v>137.19120000000001</v>
@@ -14228,7 +14228,7 @@
         <v>305</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>618</v>
+        <v>1200</v>
       </c>
       <c r="J327" s="0">
         <v>6147.9931999999999</v>
@@ -14260,7 +14260,7 @@
         <v>306</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>619</v>
+        <v>1201</v>
       </c>
       <c r="J328" s="0">
         <v>4509.7578000000003</v>
@@ -14292,7 +14292,7 @@
         <v>307</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>620</v>
+        <v>1202</v>
       </c>
       <c r="J329" s="0">
         <v>999.82090000000005</v>
@@ -14324,7 +14324,7 @@
         <v>308</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>621</v>
+        <v>1203</v>
       </c>
       <c r="J330" s="0">
         <v>829.32470000000001</v>
@@ -14356,7 +14356,7 @@
         <v>309</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>622</v>
+        <v>1204</v>
       </c>
       <c r="J331" s="0">
         <v>460.868</v>
@@ -14388,7 +14388,7 @@
         <v>310</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>623</v>
+        <v>1205</v>
       </c>
       <c r="J332" s="0">
         <v>418.91930000000002</v>
@@ -14420,7 +14420,7 @@
         <v>311</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>624</v>
+        <v>1206</v>
       </c>
       <c r="J333" s="0">
         <v>377.29809999999998</v>
@@ -14452,7 +14452,7 @@
         <v>312</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>625</v>
+        <v>1207</v>
       </c>
       <c r="J334" s="0">
         <v>376.07799999999998</v>
@@ -14484,7 +14484,7 @@
         <v>313</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>626</v>
+        <v>1208</v>
       </c>
       <c r="J335" s="0">
         <v>345.4522</v>
@@ -14516,7 +14516,7 @@
         <v>314</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>627</v>
+        <v>1209</v>
       </c>
       <c r="J336" s="0">
         <v>333.1805</v>
@@ -14548,7 +14548,7 @@
         <v>315</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>628</v>
+        <v>1210</v>
       </c>
       <c r="J337" s="0">
         <v>297.38940000000002</v>
@@ -14580,7 +14580,7 @@
         <v>316</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>629</v>
+        <v>1211</v>
       </c>
       <c r="J338" s="0">
         <v>196.88849999999999</v>
@@ -14612,7 +14612,7 @@
         <v>317</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>630</v>
+        <v>1212</v>
       </c>
       <c r="J339" s="0">
         <v>5372.8154000000004</v>
@@ -14644,7 +14644,7 @@
         <v>318</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>631</v>
+        <v>1213</v>
       </c>
       <c r="J340" s="0">
         <v>5089.0283</v>
@@ -14676,7 +14676,7 @@
         <v>321</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>634</v>
+        <v>1214</v>
       </c>
       <c r="J341" s="0">
         <v>414.66230000000002</v>
@@ -14708,7 +14708,7 @@
         <v>322</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>635</v>
+        <v>1215</v>
       </c>
       <c r="J342" s="0">
         <v>403.9067</v>
@@ -14740,7 +14740,7 @@
         <v>323</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>636</v>
+        <v>1216</v>
       </c>
       <c r="J343" s="0">
         <v>374.75290000000001</v>
@@ -14772,7 +14772,7 @@
         <v>324</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>637</v>
+        <v>1217</v>
       </c>
       <c r="J344" s="0">
         <v>372.04629999999997</v>
@@ -14804,7 +14804,7 @@
         <v>325</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>638</v>
+        <v>1218</v>
       </c>
       <c r="J345" s="0">
         <v>372.0009</v>
@@ -14836,7 +14836,7 @@
         <v>326</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>639</v>
+        <v>1219</v>
       </c>
       <c r="J346" s="0">
         <v>318.33179999999999</v>
@@ -14868,7 +14868,7 @@
         <v>327</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>640</v>
+        <v>1220</v>
       </c>
       <c r="J347" s="0">
         <v>295.59719999999999</v>
@@ -14900,7 +14900,7 @@
         <v>328</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>641</v>
+        <v>1221</v>
       </c>
       <c r="J348" s="0">
         <v>137.02930000000001</v>
@@ -14932,7 +14932,7 @@
         <v>329</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>642</v>
+        <v>1222</v>
       </c>
       <c r="J349" s="0">
         <v>4746.6201000000001</v>
@@ -14964,7 +14964,7 @@
         <v>330</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>643</v>
+        <v>1223</v>
       </c>
       <c r="J350" s="0">
         <v>4426.7367999999997</v>
@@ -14996,7 +14996,7 @@
         <v>331</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>644</v>
+        <v>1224</v>
       </c>
       <c r="J351" s="0">
         <v>502.13749999999999</v>
@@ -15028,7 +15028,7 @@
         <v>334</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>647</v>
+        <v>1225</v>
       </c>
       <c r="J352" s="0">
         <v>439.52850000000001</v>
@@ -15060,7 +15060,7 @@
         <v>335</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>648</v>
+        <v>1226</v>
       </c>
       <c r="J353" s="0">
         <v>423.6062</v>
@@ -15092,7 +15092,7 @@
         <v>336</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>649</v>
+        <v>1227</v>
       </c>
       <c r="J354" s="0">
         <v>388.16570000000002</v>
@@ -15124,7 +15124,7 @@
         <v>337</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>650</v>
+        <v>1228</v>
       </c>
       <c r="J355" s="0">
         <v>361.62639999999999</v>
@@ -15156,7 +15156,7 @@
         <v>338</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>651</v>
+        <v>1229</v>
       </c>
       <c r="J356" s="0">
         <v>319.28989999999999</v>
@@ -15188,7 +15188,7 @@
         <v>339</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>652</v>
+        <v>1230</v>
       </c>
       <c r="J357" s="0">
         <v>283.29320000000001</v>
@@ -15220,7 +15220,7 @@
         <v>340</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>653</v>
+        <v>1231</v>
       </c>
       <c r="J358" s="0">
         <v>254.66130000000001</v>
